--- a/NVDA.xlsx
+++ b/NVDA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08A2ED9F-DC48-4623-B176-5CF747C4231C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{967C7CD8-9937-4512-8DD0-06AFC0CB4991}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6490" yWindow="8380" windowWidth="27450" windowHeight="11540" activeTab="1" xr2:uid="{EA2824C1-1697-4288-88B1-60A32E5E15B0}"/>
+    <workbookView xWindow="12960" yWindow="3830" windowWidth="13950" windowHeight="11890" activeTab="1" xr2:uid="{EA2824C1-1697-4288-88B1-60A32E5E15B0}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="3" r:id="rId1"/>
@@ -1289,7 +1289,7 @@
     <numFmt numFmtId="165" formatCode="0.0"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -1314,12 +1314,6 @@
       <color theme="10"/>
       <name val="Arial"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1517,16 +1511,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>29</xdr:col>
-      <xdr:colOff>68449</xdr:colOff>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>35793</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>62317</xdr:rowOff>
+      <xdr:rowOff>4260</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>29</xdr:col>
-      <xdr:colOff>68449</xdr:colOff>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>35793</xdr:colOff>
       <xdr:row>162</xdr:row>
-      <xdr:rowOff>141145</xdr:rowOff>
+      <xdr:rowOff>83088</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -1541,8 +1535,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="20592753" y="62317"/>
-          <a:ext cx="0" cy="26058611"/>
+          <a:off x="21252050" y="4260"/>
+          <a:ext cx="0" cy="25994085"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -2093,7 +2087,7 @@
         <v>112</v>
       </c>
       <c r="K2" s="15">
-        <v>194</v>
+        <v>221</v>
       </c>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.25">
@@ -2136,7 +2130,7 @@
       </c>
       <c r="K4" s="2">
         <f>+K2*K3</f>
-        <v>4714200</v>
+        <v>5370300</v>
       </c>
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.25">
@@ -2188,7 +2182,7 @@
       </c>
       <c r="K7" s="2">
         <f>+K4-K5+K6</f>
-        <v>4665875</v>
+        <v>5321975</v>
       </c>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.25">
@@ -2535,31 +2529,31 @@
         <v>45774</v>
       </c>
       <c r="AB2" s="13">
-        <f>+X2+365</f>
+        <f t="shared" ref="AB2:AH2" si="0">+X2+365</f>
         <v>45866</v>
       </c>
       <c r="AC2" s="13">
-        <f>+Y2+365</f>
+        <f t="shared" si="0"/>
         <v>45957</v>
       </c>
       <c r="AD2" s="13">
-        <f>+Z2+365</f>
+        <f t="shared" si="0"/>
         <v>46048</v>
       </c>
       <c r="AE2" s="13">
-        <f>+AA2+365</f>
+        <f t="shared" si="0"/>
         <v>46139</v>
       </c>
       <c r="AF2" s="13">
-        <f>+AB2+365</f>
+        <f t="shared" si="0"/>
         <v>46231</v>
       </c>
       <c r="AG2" s="13">
-        <f>+AC2+365</f>
+        <f t="shared" si="0"/>
         <v>46322</v>
       </c>
       <c r="AH2" s="13">
-        <f>+AD2+365</f>
+        <f t="shared" si="0"/>
         <v>46413</v>
       </c>
       <c r="AI2" s="13"/>
@@ -2661,43 +2655,43 @@
         <v>45683</v>
       </c>
       <c r="BQ2" s="1">
-        <f t="shared" ref="BQ2:BY2" si="0">+BP2+365</f>
+        <f t="shared" ref="BQ2:BY2" si="1">+BP2+365</f>
         <v>46048</v>
       </c>
       <c r="BR2" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>46413</v>
       </c>
       <c r="BS2" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>46778</v>
       </c>
       <c r="BT2" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>47143</v>
       </c>
       <c r="BU2" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>47508</v>
       </c>
       <c r="BV2" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>47873</v>
       </c>
       <c r="BW2" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>48238</v>
       </c>
       <c r="BX2" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>48603</v>
       </c>
       <c r="BY2" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>48968</v>
       </c>
       <c r="BZ2" s="1">
-        <f t="shared" ref="BZ2" si="1">+BY2+365</f>
+        <f t="shared" ref="BZ2" si="2">+BY2+365</f>
         <v>49333</v>
       </c>
     </row>
@@ -3919,7 +3913,7 @@
         <v>11046</v>
       </c>
       <c r="BN14" s="2">
-        <f t="shared" ref="BN14:BN19" si="2">SUM(O14:R14)</f>
+        <f t="shared" ref="BN14:BN19" si="3">SUM(O14:R14)</f>
         <v>15068</v>
       </c>
       <c r="BO14" s="2">
@@ -4053,7 +4047,7 @@
         <v>15868</v>
       </c>
       <c r="BN15" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>11906</v>
       </c>
       <c r="BO15" s="2">
@@ -4121,7 +4115,7 @@
       <c r="BD16" s="5"/>
       <c r="BE16" s="5"/>
     </row>
-    <row r="17" spans="2:74" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:78" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B17" s="2" t="s">
         <v>46</v>
       </c>
@@ -4225,19 +4219,19 @@
         <v>1162</v>
       </c>
       <c r="BN17" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>455</v>
       </c>
       <c r="BO17" s="2">
-        <f t="shared" ref="BO17:BO21" si="3">SUM(S17:V17)</f>
+        <f t="shared" ref="BO17:BO21" si="4">SUM(S17:V17)</f>
         <v>306</v>
       </c>
       <c r="BP17" s="2">
-        <f t="shared" ref="BP17:BP21" si="4">SUM(W17:Z17)</f>
+        <f t="shared" ref="BP17:BP21" si="5">SUM(W17:Z17)</f>
         <v>389</v>
       </c>
     </row>
-    <row r="18" spans="2:74" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:78" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B18" s="2" t="s">
         <v>20</v>
       </c>
@@ -4359,19 +4353,19 @@
         <v>2111</v>
       </c>
       <c r="BN18" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1544</v>
       </c>
       <c r="BO18" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1553</v>
       </c>
       <c r="BP18" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1878</v>
       </c>
     </row>
-    <row r="19" spans="2:74" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:78" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B19" s="2" t="s">
         <v>21</v>
       </c>
@@ -4493,19 +4487,19 @@
         <v>566</v>
       </c>
       <c r="BN19" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>903</v>
       </c>
       <c r="BO19" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1091</v>
       </c>
       <c r="BP19" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1694</v>
       </c>
     </row>
-    <row r="20" spans="2:74" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:78" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B20" s="2" t="s">
         <v>169</v>
       </c>
@@ -4574,15 +4568,15 @@
       <c r="AZ20" s="5"/>
       <c r="BA20" s="5"/>
       <c r="BO20" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>8575</v>
       </c>
       <c r="BP20" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>12990</v>
       </c>
     </row>
-    <row r="21" spans="2:74" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:78" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B21" s="2" t="s">
         <v>168</v>
       </c>
@@ -4651,15 +4645,15 @@
       <c r="AZ21" s="5"/>
       <c r="BA21" s="5"/>
       <c r="BO21" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>38950</v>
       </c>
       <c r="BP21" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>102196</v>
       </c>
     </row>
-    <row r="22" spans="2:74" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:78" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B22" s="2" t="s">
         <v>22</v>
       </c>
@@ -4785,7 +4779,7 @@
         <v>115186</v>
       </c>
     </row>
-    <row r="23" spans="2:74" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:78" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B23" s="2" t="s">
         <v>19</v>
       </c>
@@ -4920,7 +4914,7 @@
         <v>11350</v>
       </c>
     </row>
-    <row r="24" spans="2:74" s="8" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:78" s="8" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="B24" s="8" t="s">
         <v>1</v>
       </c>
@@ -4999,15 +4993,15 @@
         <v>22103</v>
       </c>
       <c r="W24" s="9">
-        <f t="shared" ref="W24:AB24" si="5">+W23+W22+W19+W18+W17</f>
+        <f t="shared" ref="W24:AB24" si="6">+W23+W22+W19+W18+W17</f>
         <v>26044</v>
       </c>
       <c r="X24" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>30040</v>
       </c>
       <c r="Y24" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>35082</v>
       </c>
       <c r="Z24" s="9">
@@ -5015,11 +5009,11 @@
         <v>39331</v>
       </c>
       <c r="AA24" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>44062</v>
       </c>
       <c r="AB24" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>46743</v>
       </c>
       <c r="AC24" s="9">
@@ -5029,10 +5023,10 @@
         <v>68100</v>
       </c>
       <c r="AE24" s="9">
-        <v>78000</v>
+        <v>81615</v>
       </c>
       <c r="AF24" s="9">
-        <v>85000</v>
+        <v>91000</v>
       </c>
       <c r="AG24" s="9">
         <v>95000</v>
@@ -5116,31 +5110,31 @@
         <v>9714</v>
       </c>
       <c r="BJ24" s="8">
-        <f t="shared" ref="BJ24:BP24" si="6">+BJ23+BJ22+BJ19+BJ18+BJ17</f>
+        <f t="shared" ref="BJ24:BP24" si="7">+BJ23+BJ22+BJ19+BJ18+BJ17</f>
         <v>11716</v>
       </c>
       <c r="BK24" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>10918</v>
       </c>
       <c r="BL24" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>16675</v>
       </c>
       <c r="BM24" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>26913</v>
       </c>
       <c r="BN24" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>26977</v>
       </c>
       <c r="BO24" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>60922</v>
       </c>
       <c r="BP24" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>130497</v>
       </c>
       <c r="BQ24" s="8">
@@ -5167,8 +5161,24 @@
         <f>+BU24*1.3</f>
         <v>1650030.7259799999</v>
       </c>
-    </row>
-    <row r="25" spans="2:74" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="BW24" s="8">
+        <f t="shared" ref="BW24:BZ24" si="8">+BV24*1.3</f>
+        <v>2145039.9437739998</v>
+      </c>
+      <c r="BX24" s="8">
+        <f t="shared" si="8"/>
+        <v>2788551.9269061997</v>
+      </c>
+      <c r="BY24" s="8">
+        <f t="shared" si="8"/>
+        <v>3625117.5049780598</v>
+      </c>
+      <c r="BZ24" s="8">
+        <f t="shared" si="8"/>
+        <v>4712652.7564714774</v>
+      </c>
+    </row>
+    <row r="25" spans="2:78" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B25" s="2" t="s">
         <v>4</v>
       </c>
@@ -5256,8 +5266,10 @@
         <v>15157</v>
       </c>
       <c r="AD25" s="2">
-        <f>+AD24-AD26</f>
-        <v>16344</v>
+        <v>17034</v>
+      </c>
+      <c r="AE25" s="2">
+        <v>20458</v>
       </c>
       <c r="AQ25" s="2">
         <v>141.84299999999999</v>
@@ -5342,99 +5354,99 @@
       </c>
       <c r="BQ25" s="2">
         <f>+BQ24-BQ26</f>
-        <v>61785</v>
+        <v>62475</v>
       </c>
       <c r="BR25" s="2">
         <f>+BR24-BR26</f>
         <v>102557.72499999998</v>
       </c>
       <c r="BS25" s="2">
-        <f t="shared" ref="BS25:BT25" si="7">+BS24-BS26</f>
+        <f t="shared" ref="BS25:BT25" si="9">+BS24-BS26</f>
         <v>153426.35659999994</v>
       </c>
       <c r="BT25" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>214796.89923999994</v>
       </c>
       <c r="BU25" s="2">
-        <f t="shared" ref="BU25" si="8">+BU24-BU26</f>
+        <f t="shared" ref="BU25" si="10">+BU24-BU26</f>
         <v>279235.9690119999</v>
       </c>
       <c r="BV25" s="2">
-        <f t="shared" ref="BV25" si="9">+BV24-BV26</f>
+        <f t="shared" ref="BV25" si="11">+BV24-BV26</f>
         <v>363006.75971559994</v>
       </c>
     </row>
-    <row r="26" spans="2:74" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:78" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B26" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C26" s="5">
-        <f t="shared" ref="C26:F26" si="10">+C24-C25</f>
+        <f t="shared" ref="C26:F26" si="12">+C24-C25</f>
         <v>1296</v>
       </c>
       <c r="D26" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>1541</v>
       </c>
       <c r="E26" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>1916</v>
       </c>
       <c r="F26" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>2015</v>
       </c>
       <c r="G26" s="5">
-        <f t="shared" ref="G26:S26" si="11">+G24-G25</f>
+        <f t="shared" ref="G26:S26" si="13">+G24-G25</f>
         <v>2004</v>
       </c>
       <c r="H26" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>2275</v>
       </c>
       <c r="I26" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>2960</v>
       </c>
       <c r="J26" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>3157</v>
       </c>
       <c r="K26" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>3629</v>
       </c>
       <c r="L26" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>4215</v>
       </c>
       <c r="M26" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>4631</v>
       </c>
       <c r="N26" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>4999</v>
       </c>
       <c r="O26" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>5431</v>
       </c>
       <c r="P26" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>2915</v>
       </c>
       <c r="Q26" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>3177</v>
       </c>
       <c r="R26" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>3833</v>
       </c>
       <c r="S26" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>4648</v>
       </c>
       <c r="T26" s="2">
@@ -5442,27 +5454,27 @@
         <v>9462</v>
       </c>
       <c r="U26" s="2">
-        <f t="shared" ref="U26:Z26" si="12">+U24-U25</f>
+        <f t="shared" ref="U26:Z26" si="14">+U24-U25</f>
         <v>13400</v>
       </c>
       <c r="V26" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>16791</v>
       </c>
       <c r="W26" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>20406</v>
       </c>
       <c r="X26" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>22574</v>
       </c>
       <c r="Y26" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>26156</v>
       </c>
       <c r="Z26" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>28723</v>
       </c>
       <c r="AA26" s="2">
@@ -5478,31 +5490,39 @@
         <v>41849</v>
       </c>
       <c r="AD26" s="2">
-        <f>+AD24*0.76</f>
-        <v>51756</v>
+        <f>+AD24-AD25</f>
+        <v>51066</v>
+      </c>
+      <c r="AE26" s="2">
+        <f>+AE24-AE25</f>
+        <v>61157</v>
+      </c>
+      <c r="AF26" s="2">
+        <f>+AF24*0.75</f>
+        <v>68250</v>
       </c>
       <c r="AQ26" s="2">
-        <f t="shared" ref="AQ26:AR26" si="13">+AQ24-AQ25</f>
+        <f t="shared" ref="AQ26:AR26" si="15">+AQ24-AQ25</f>
         <v>232.66200000000001</v>
       </c>
       <c r="AR26" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>462.38499999999999</v>
       </c>
       <c r="AS26" s="2">
-        <f t="shared" ref="AS26:AV26" si="14">+AS24-AS25</f>
+        <f t="shared" ref="AS26:AV26" si="16">+AS24-AS25</f>
         <v>850.23299999999995</v>
       </c>
       <c r="AT26" s="2">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>582.17599999999993</v>
       </c>
       <c r="AU26" s="2">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>528.87799999999993</v>
       </c>
       <c r="AV26" s="2">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>649.48599999999988</v>
       </c>
       <c r="AW26" s="2">
@@ -5526,59 +5546,59 @@
         <v>1176.9230000000002</v>
       </c>
       <c r="BB26" s="2">
-        <f t="shared" ref="BB26:BO26" si="15">+BB24-BB25</f>
+        <f t="shared" ref="BB26:BO26" si="17">+BB24-BB25</f>
         <v>1409.0900000000001</v>
       </c>
       <c r="BC26" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>2056.5169999999998</v>
       </c>
       <c r="BD26" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>2226.3429999999998</v>
       </c>
       <c r="BE26" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>2268</v>
       </c>
       <c r="BF26" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>2599</v>
       </c>
       <c r="BG26" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>2811</v>
       </c>
       <c r="BH26" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>4063</v>
       </c>
       <c r="BI26" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>5822</v>
       </c>
       <c r="BJ26" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>7171</v>
       </c>
       <c r="BK26" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>6768</v>
       </c>
       <c r="BL26" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>10396</v>
       </c>
       <c r="BM26" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>17473</v>
       </c>
       <c r="BN26" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>15359</v>
       </c>
       <c r="BO26" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>44301</v>
       </c>
       <c r="BP26" s="2">
@@ -5587,7 +5607,7 @@
       </c>
       <c r="BQ26" s="2">
         <f>SUM(AA26:AD26)</f>
-        <v>154126</v>
+        <v>153436</v>
       </c>
       <c r="BR26" s="2">
         <f>+BR24*0.75</f>
@@ -5602,15 +5622,15 @@
         <v>761552.64275999984</v>
       </c>
       <c r="BU26" s="2">
-        <f t="shared" ref="BU26:BV26" si="16">+BU24*0.78</f>
+        <f t="shared" ref="BU26:BV26" si="18">+BU24*0.78</f>
         <v>990018.43558799988</v>
       </c>
       <c r="BV26" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>1287023.9662643999</v>
       </c>
     </row>
-    <row r="27" spans="2:74" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:78" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B27" s="2" t="s">
         <v>6</v>
       </c>
@@ -5624,7 +5644,7 @@
         <v>712</v>
       </c>
       <c r="F27" s="5">
-        <f t="shared" ref="F27:F28" si="17">+BK27-E27-D27-C27</f>
+        <f t="shared" ref="F27:F28" si="19">+BK27-E27-D27-C27</f>
         <v>739</v>
       </c>
       <c r="G27" s="5">
@@ -5661,7 +5681,7 @@
         <v>1945</v>
       </c>
       <c r="R27" s="5">
-        <f t="shared" ref="R27:R28" si="18">+BN27-Q27-P27-O27</f>
+        <f t="shared" ref="R27:R28" si="20">+BN27-Q27-P27-O27</f>
         <v>1952</v>
       </c>
       <c r="S27" s="5">
@@ -5698,8 +5718,14 @@
         <v>4705</v>
       </c>
       <c r="AD27" s="2">
-        <f t="shared" ref="AD27" si="19">+Z27*1.2</f>
-        <v>4456.8</v>
+        <v>5512</v>
+      </c>
+      <c r="AE27" s="2">
+        <v>6321</v>
+      </c>
+      <c r="AF27" s="2">
+        <f>+AE27</f>
+        <v>6321</v>
       </c>
       <c r="AT27" s="2">
         <v>224.87299999999999</v>
@@ -5775,30 +5801,30 @@
       </c>
       <c r="BQ27" s="2">
         <f>SUM(AA27:AD27)</f>
-        <v>17441.8</v>
+        <v>18497</v>
       </c>
       <c r="BR27" s="2">
         <f>+BQ27*1.2</f>
-        <v>20930.16</v>
+        <v>22196.399999999998</v>
       </c>
       <c r="BS27" s="2">
-        <f t="shared" ref="BS27:BT27" si="20">+BR27*1.2</f>
-        <v>25116.191999999999</v>
+        <f t="shared" ref="BS27:BT27" si="21">+BR27*1.2</f>
+        <v>26635.679999999997</v>
       </c>
       <c r="BT27" s="2">
-        <f t="shared" si="20"/>
-        <v>30139.430399999997</v>
+        <f t="shared" si="21"/>
+        <v>31962.815999999995</v>
       </c>
       <c r="BU27" s="2">
-        <f t="shared" ref="BU27:BV27" si="21">+BT27*1.2</f>
-        <v>36167.316479999994</v>
+        <f t="shared" ref="BU27:BV27" si="22">+BT27*1.2</f>
+        <v>38355.379199999996</v>
       </c>
       <c r="BV27" s="2">
-        <f t="shared" si="21"/>
-        <v>43400.779775999988</v>
-      </c>
-    </row>
-    <row r="28" spans="2:74" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <f t="shared" si="22"/>
+        <v>46026.455039999993</v>
+      </c>
+    </row>
+    <row r="28" spans="2:78" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B28" s="2" t="s">
         <v>7</v>
       </c>
@@ -5812,7 +5838,7 @@
         <v>277</v>
       </c>
       <c r="F28" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>286</v>
       </c>
       <c r="G28" s="5">
@@ -5849,7 +5875,7 @@
         <v>631</v>
       </c>
       <c r="R28" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>625</v>
       </c>
       <c r="S28" s="5">
@@ -5886,8 +5912,14 @@
         <v>1134</v>
       </c>
       <c r="AD28" s="2">
-        <f>+Z28*1.2</f>
-        <v>1170</v>
+        <v>1282</v>
+      </c>
+      <c r="AE28" s="2">
+        <v>1300</v>
+      </c>
+      <c r="AF28" s="2">
+        <f>+AE28</f>
+        <v>1300</v>
       </c>
       <c r="AT28" s="2">
         <v>151.48500000000001</v>
@@ -5963,79 +5995,79 @@
       </c>
       <c r="BQ28" s="2">
         <f>SUM(AA28:AD28)</f>
-        <v>4467</v>
+        <v>4579</v>
       </c>
       <c r="BR28" s="2">
         <f>+BQ28*1.2</f>
-        <v>5360.4</v>
+        <v>5494.8</v>
       </c>
       <c r="BS28" s="2">
-        <f t="shared" ref="BS28:BT28" si="22">+BR28*1.2</f>
-        <v>6432.48</v>
+        <f t="shared" ref="BS28:BT28" si="23">+BR28*1.2</f>
+        <v>6593.76</v>
       </c>
       <c r="BT28" s="2">
-        <f t="shared" si="22"/>
-        <v>7718.9759999999987</v>
+        <f t="shared" si="23"/>
+        <v>7912.5119999999997</v>
       </c>
       <c r="BU28" s="2">
-        <f t="shared" ref="BU28:BV28" si="23">+BT28*1.2</f>
-        <v>9262.7711999999974</v>
+        <f t="shared" ref="BU28:BV28" si="24">+BT28*1.2</f>
+        <v>9495.0144</v>
       </c>
       <c r="BV28" s="2">
-        <f t="shared" si="23"/>
-        <v>11115.325439999997</v>
-      </c>
-    </row>
-    <row r="29" spans="2:74" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <f t="shared" si="24"/>
+        <v>11394.01728</v>
+      </c>
+    </row>
+    <row r="29" spans="2:78" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B29" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C29" s="5">
-        <f t="shared" ref="C29:F29" si="24">+C27+C28</f>
+        <f t="shared" ref="C29:F29" si="25">+C27+C28</f>
         <v>938</v>
       </c>
       <c r="D29" s="5">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>970</v>
       </c>
       <c r="E29" s="5">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>989</v>
       </c>
       <c r="F29" s="5">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>1025</v>
       </c>
       <c r="G29" s="5">
-        <f t="shared" ref="G29:I29" si="25">+G27+G28</f>
+        <f t="shared" ref="G29:I29" si="26">+G27+G28</f>
         <v>1028</v>
       </c>
       <c r="H29" s="5">
-        <f t="shared" ref="H29" si="26">+H27+H28</f>
+        <f t="shared" ref="H29" si="27">+H27+H28</f>
         <v>1624</v>
       </c>
       <c r="I29" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>1562</v>
       </c>
       <c r="J29" s="5">
-        <f t="shared" ref="J29" si="27">+J27+J28</f>
+        <f t="shared" ref="J29" si="28">+J27+J28</f>
         <v>1650</v>
       </c>
       <c r="K29" s="5">
-        <f t="shared" ref="K29:M29" si="28">+K27+K28</f>
+        <f t="shared" ref="K29:M29" si="29">+K27+K28</f>
         <v>1673</v>
       </c>
       <c r="L29" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>1771</v>
       </c>
       <c r="M29" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>1960</v>
       </c>
       <c r="N29" s="5">
-        <f t="shared" ref="N29" si="29">+N27+N28</f>
+        <f t="shared" ref="N29" si="30">+N27+N28</f>
         <v>2029</v>
       </c>
       <c r="O29" s="5">
@@ -6043,7 +6075,7 @@
         <v>2210</v>
       </c>
       <c r="P29" s="5">
-        <f t="shared" ref="P29" si="30">+P27+P28</f>
+        <f t="shared" ref="P29" si="31">+P27+P28</f>
         <v>2416</v>
       </c>
       <c r="Q29" s="5">
@@ -6063,35 +6095,35 @@
         <v>2662</v>
       </c>
       <c r="U29" s="5">
-        <f t="shared" ref="U29:W29" si="31">+U27+U28</f>
+        <f t="shared" ref="U29:W29" si="32">+U27+U28</f>
         <v>2983</v>
       </c>
       <c r="V29" s="5">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>3176</v>
       </c>
       <c r="W29" s="5">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>3497</v>
       </c>
       <c r="X29" s="5">
-        <f t="shared" ref="X29:Z29" si="32">+X27+X28</f>
+        <f t="shared" ref="X29:Z29" si="33">+X27+X28</f>
         <v>3932</v>
       </c>
       <c r="Y29" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>4287</v>
       </c>
       <c r="Z29" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>4689</v>
       </c>
       <c r="AA29" s="5">
-        <f t="shared" ref="AA29:AD29" si="33">+AA27+AA28</f>
+        <f t="shared" ref="AA29:AF29" si="34">+AA27+AA28</f>
         <v>5030</v>
       </c>
       <c r="AB29" s="5">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>5413</v>
       </c>
       <c r="AC29" s="5">
@@ -6099,11 +6131,17 @@
         <v>5839</v>
       </c>
       <c r="AD29" s="5">
-        <f t="shared" si="33"/>
-        <v>5626.8</v>
-      </c>
-      <c r="AE29" s="5"/>
-      <c r="AF29" s="5"/>
+        <f t="shared" si="34"/>
+        <v>6794</v>
+      </c>
+      <c r="AE29" s="5">
+        <f t="shared" si="34"/>
+        <v>7621</v>
+      </c>
+      <c r="AF29" s="5">
+        <f t="shared" si="34"/>
+        <v>7621</v>
+      </c>
       <c r="AG29" s="5"/>
       <c r="AH29" s="5"/>
       <c r="AI29" s="5"/>
@@ -6115,99 +6153,99 @@
       <c r="AO29" s="5"/>
       <c r="AP29" s="5"/>
       <c r="AQ29" s="2">
-        <f t="shared" ref="AQ29" si="34">+AQ27+AQ28</f>
+        <f t="shared" ref="AQ29" si="35">+AQ27+AQ28</f>
         <v>0</v>
       </c>
       <c r="AR29" s="2">
-        <f t="shared" ref="AR29:AS29" si="35">+AR27+AR28</f>
+        <f t="shared" ref="AR29:AS29" si="36">+AR27+AR28</f>
         <v>0</v>
       </c>
       <c r="AS29" s="2">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="AT29" s="2">
-        <f t="shared" ref="AT29:AU29" si="36">+AT27+AT28</f>
+        <f t="shared" ref="AT29:AU29" si="37">+AT27+AT28</f>
         <v>376.358</v>
       </c>
       <c r="AU29" s="2">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>435.221</v>
       </c>
       <c r="AV29" s="2">
-        <f t="shared" ref="AV29:BA29" si="37">+AV27+AV28</f>
+        <f t="shared" ref="AV29:BA29" si="38">+AV27+AV28</f>
         <v>535.89300000000003</v>
       </c>
       <c r="AW29" s="2">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>559.21100000000001</v>
       </c>
       <c r="AX29" s="2">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>846.99699999999996</v>
       </c>
       <c r="AY29" s="2">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>1032.934</v>
       </c>
       <c r="AZ29" s="2">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>1218.1010000000001</v>
       </c>
       <c r="BA29" s="2">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>1275.8679999999999</v>
       </c>
       <c r="BB29" s="2">
-        <f t="shared" ref="BB29:BN29" si="38">+BB27+BB28</f>
+        <f t="shared" ref="BB29:BN29" si="39">+BB27+BB28</f>
         <v>1210.3430000000001</v>
       </c>
       <c r="BC29" s="2">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>1408.2180000000001</v>
       </c>
       <c r="BD29" s="2">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>1578.1039999999998</v>
       </c>
       <c r="BE29" s="2">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>1772</v>
       </c>
       <c r="BF29" s="2">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>1840</v>
       </c>
       <c r="BG29" s="2">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>1933</v>
       </c>
       <c r="BH29" s="2">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>2126</v>
       </c>
       <c r="BI29" s="2">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>2612</v>
       </c>
       <c r="BJ29" s="2">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>3367</v>
       </c>
       <c r="BK29" s="2">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>3922</v>
       </c>
       <c r="BL29" s="2">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>5864</v>
       </c>
       <c r="BM29" s="2">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>7433</v>
       </c>
       <c r="BN29" s="2">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>9779</v>
       </c>
       <c r="BO29" s="2">
@@ -6219,80 +6257,80 @@
         <v>16405</v>
       </c>
       <c r="BQ29" s="2">
-        <f t="shared" ref="BQ29:BT29" si="39">+BQ27+BQ28</f>
-        <v>21908.799999999999</v>
+        <f t="shared" ref="BQ29:BT29" si="40">+BQ27+BQ28</f>
+        <v>23076</v>
       </c>
       <c r="BR29" s="2">
         <f>+BR27+BR28</f>
-        <v>26290.559999999998</v>
+        <v>27691.199999999997</v>
       </c>
       <c r="BS29" s="2">
-        <f t="shared" si="39"/>
-        <v>31548.671999999999</v>
+        <f t="shared" si="40"/>
+        <v>33229.439999999995</v>
       </c>
       <c r="BT29" s="2">
-        <f t="shared" si="39"/>
-        <v>37858.406399999993</v>
+        <f t="shared" si="40"/>
+        <v>39875.327999999994</v>
       </c>
       <c r="BU29" s="2">
-        <f t="shared" ref="BU29" si="40">+BU27+BU28</f>
-        <v>45430.08767999999</v>
+        <f t="shared" ref="BU29" si="41">+BU27+BU28</f>
+        <v>47850.393599999996</v>
       </c>
       <c r="BV29" s="2">
-        <f t="shared" ref="BV29" si="41">+BV27+BV28</f>
-        <v>54516.105215999982</v>
-      </c>
-    </row>
-    <row r="30" spans="2:74" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <f t="shared" ref="BV29" si="42">+BV27+BV28</f>
+        <v>57420.472319999993</v>
+      </c>
+    </row>
+    <row r="30" spans="2:78" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B30" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C30" s="5">
-        <f t="shared" ref="C30:F30" si="42">+C26-C29</f>
+        <f t="shared" ref="C30:F30" si="43">+C26-C29</f>
         <v>358</v>
       </c>
       <c r="D30" s="5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>571</v>
       </c>
       <c r="E30" s="5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>927</v>
       </c>
       <c r="F30" s="5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>990</v>
       </c>
       <c r="G30" s="5">
-        <f t="shared" ref="G30:I30" si="43">+G26-G29</f>
+        <f t="shared" ref="G30:I30" si="44">+G26-G29</f>
         <v>976</v>
       </c>
       <c r="H30" s="5">
-        <f t="shared" ref="H30" si="44">+H26-H29</f>
+        <f t="shared" ref="H30" si="45">+H26-H29</f>
         <v>651</v>
       </c>
       <c r="I30" s="5">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1398</v>
       </c>
       <c r="J30" s="5">
-        <f t="shared" ref="J30" si="45">+J26-J29</f>
+        <f t="shared" ref="J30" si="46">+J26-J29</f>
         <v>1507</v>
       </c>
       <c r="K30" s="5">
-        <f t="shared" ref="K30:M30" si="46">+K26-K29</f>
+        <f t="shared" ref="K30:M30" si="47">+K26-K29</f>
         <v>1956</v>
       </c>
       <c r="L30" s="5">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>2444</v>
       </c>
       <c r="M30" s="5">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>2671</v>
       </c>
       <c r="N30" s="5">
-        <f t="shared" ref="N30" si="47">+N26-N29</f>
+        <f t="shared" ref="N30" si="48">+N26-N29</f>
         <v>2970</v>
       </c>
       <c r="O30" s="5">
@@ -6300,7 +6338,7 @@
         <v>3221</v>
       </c>
       <c r="P30" s="5">
-        <f t="shared" ref="P30" si="48">+P26-P29</f>
+        <f t="shared" ref="P30" si="49">+P26-P29</f>
         <v>499</v>
       </c>
       <c r="Q30" s="5">
@@ -6320,35 +6358,35 @@
         <v>6800</v>
       </c>
       <c r="U30" s="5">
-        <f t="shared" ref="U30:W30" si="49">+U26-U29</f>
+        <f t="shared" ref="U30:W30" si="50">+U26-U29</f>
         <v>10417</v>
       </c>
       <c r="V30" s="5">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>13615</v>
       </c>
       <c r="W30" s="5">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>16909</v>
       </c>
       <c r="X30" s="5">
-        <f t="shared" ref="X30:Z30" si="50">+X26-X29</f>
+        <f t="shared" ref="X30:Z30" si="51">+X26-X29</f>
         <v>18642</v>
       </c>
       <c r="Y30" s="5">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>21869</v>
       </c>
       <c r="Z30" s="5">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>24034</v>
       </c>
       <c r="AA30" s="5">
-        <f t="shared" ref="AA30:AD30" si="51">+AA26-AA29</f>
+        <f t="shared" ref="AA30:AF30" si="52">+AA26-AA29</f>
         <v>21638</v>
       </c>
       <c r="AB30" s="5">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>28440</v>
       </c>
       <c r="AC30" s="5">
@@ -6356,11 +6394,17 @@
         <v>36010</v>
       </c>
       <c r="AD30" s="5">
-        <f t="shared" si="51"/>
-        <v>46129.2</v>
-      </c>
-      <c r="AE30" s="5"/>
-      <c r="AF30" s="5"/>
+        <f t="shared" si="52"/>
+        <v>44272</v>
+      </c>
+      <c r="AE30" s="5">
+        <f t="shared" si="52"/>
+        <v>53536</v>
+      </c>
+      <c r="AF30" s="5">
+        <f t="shared" si="52"/>
+        <v>60629</v>
+      </c>
       <c r="AG30" s="5"/>
       <c r="AH30" s="5"/>
       <c r="AI30" s="5"/>
@@ -6372,135 +6416,135 @@
       <c r="AO30" s="5"/>
       <c r="AP30" s="5"/>
       <c r="AQ30" s="2">
-        <f t="shared" ref="AQ30" si="52">+AQ26-AQ29</f>
+        <f t="shared" ref="AQ30" si="53">+AQ26-AQ29</f>
         <v>232.66200000000001</v>
       </c>
       <c r="AR30" s="2">
-        <f t="shared" ref="AR30:AS30" si="53">+AR26-AR29</f>
+        <f t="shared" ref="AR30:AS30" si="54">+AR26-AR29</f>
         <v>462.38499999999999</v>
       </c>
       <c r="AS30" s="2">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>850.23299999999995</v>
       </c>
       <c r="AT30" s="2">
-        <f t="shared" ref="AT30:AU30" si="54">+AT26-AT29</f>
+        <f t="shared" ref="AT30:AU30" si="55">+AT26-AT29</f>
         <v>205.81799999999993</v>
       </c>
       <c r="AU30" s="2">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>93.656999999999925</v>
       </c>
       <c r="AV30" s="2">
-        <f t="shared" ref="AV30:BA30" si="55">+AV26-AV29</f>
+        <f t="shared" ref="AV30:BA30" si="56">+AV26-AV29</f>
         <v>113.59299999999985</v>
       </c>
       <c r="AW30" s="2">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>350.82199999999989</v>
       </c>
       <c r="AX30" s="2">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>453.45200000000034</v>
       </c>
       <c r="AY30" s="2">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>836.34599999999978</v>
       </c>
       <c r="AZ30" s="2">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>-43.832000000000335</v>
       </c>
       <c r="BA30" s="2">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>-98.944999999999709</v>
       </c>
       <c r="BB30" s="2">
-        <f t="shared" ref="BB30:BP30" si="56">+BB26-BB29</f>
+        <f t="shared" ref="BB30:BP30" si="57">+BB26-BB29</f>
         <v>198.74700000000007</v>
       </c>
       <c r="BC30" s="2">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>648.29899999999975</v>
       </c>
       <c r="BD30" s="2">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>648.23900000000003</v>
       </c>
       <c r="BE30" s="2">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>496</v>
       </c>
       <c r="BF30" s="2">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>759</v>
       </c>
       <c r="BG30" s="2">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>878</v>
       </c>
       <c r="BH30" s="2">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>1937</v>
       </c>
       <c r="BI30" s="2">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>3210</v>
       </c>
       <c r="BJ30" s="2">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>3804</v>
       </c>
       <c r="BK30" s="2">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>2846</v>
       </c>
       <c r="BL30" s="2">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>4532</v>
       </c>
       <c r="BM30" s="2">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>10040</v>
       </c>
       <c r="BN30" s="2">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>5580</v>
       </c>
       <c r="BO30" s="2">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>32972</v>
       </c>
       <c r="BP30" s="2">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>81454</v>
       </c>
       <c r="BQ30" s="2">
-        <f t="shared" ref="BQ30:BT30" si="57">+BQ26-BQ29</f>
-        <v>132217.20000000001</v>
+        <f t="shared" ref="BQ30:BT30" si="58">+BQ26-BQ29</f>
+        <v>130360</v>
       </c>
       <c r="BR30" s="2">
         <f>+BR26-BR29</f>
-        <v>281382.61499999999</v>
+        <v>279981.97499999998</v>
       </c>
       <c r="BS30" s="2">
-        <f t="shared" si="57"/>
-        <v>512417.50139999995</v>
+        <f t="shared" si="58"/>
+        <v>510736.73339999997</v>
       </c>
       <c r="BT30" s="2">
-        <f t="shared" si="57"/>
-        <v>723694.23635999986</v>
+        <f t="shared" si="58"/>
+        <v>721677.31475999986</v>
       </c>
       <c r="BU30" s="2">
-        <f t="shared" ref="BU30" si="58">+BU26-BU29</f>
-        <v>944588.34790799988</v>
+        <f t="shared" ref="BU30" si="59">+BU26-BU29</f>
+        <v>942168.04198799992</v>
       </c>
       <c r="BV30" s="2">
-        <f t="shared" ref="BV30" si="59">+BV26-BV29</f>
-        <v>1232507.8610483999</v>
-      </c>
-    </row>
-    <row r="31" spans="2:74" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <f t="shared" ref="BV30" si="60">+BV26-BV29</f>
+        <v>1229603.4939444</v>
+      </c>
+    </row>
+    <row r="31" spans="2:78" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B31" s="2" t="s">
         <v>11</v>
       </c>
@@ -6556,7 +6600,7 @@
         <v>12</v>
       </c>
       <c r="R31" s="5">
-        <f t="shared" ref="R31" si="60">+BN31-Q31-P31-O31</f>
+        <f t="shared" ref="R31" si="61">+BN31-Q31-P31-O31</f>
         <v>32</v>
       </c>
       <c r="S31" s="5">
@@ -6602,8 +6646,16 @@
         <v>563</v>
       </c>
       <c r="AD31" s="2">
-        <f>+AC31</f>
-        <v>563</v>
+        <f>568-74</f>
+        <v>494</v>
+      </c>
+      <c r="AE31" s="2">
+        <f>+AD31</f>
+        <v>494</v>
+      </c>
+      <c r="AF31" s="2">
+        <f>+AE31</f>
+        <v>494</v>
       </c>
       <c r="AQ31" s="2">
         <v>23.245999999999999</v>
@@ -6693,115 +6745,115 @@
       </c>
       <c r="BQ31" s="2">
         <f>SUM(AA31:AD31)</f>
-        <v>4164</v>
+        <v>4095</v>
       </c>
       <c r="BR31" s="2">
         <f>+BQ31*1.1</f>
-        <v>4580.4000000000005</v>
+        <v>4504.5</v>
       </c>
       <c r="BS31" s="2">
         <f>+BR31*1.1</f>
-        <v>5038.4400000000014</v>
+        <v>4954.9500000000007</v>
       </c>
       <c r="BT31" s="2">
         <f>+BS31*1.1</f>
-        <v>5542.2840000000024</v>
+        <v>5450.4450000000015</v>
       </c>
       <c r="BU31" s="2">
-        <f t="shared" ref="BU31:BV31" si="61">+BT31*1.1</f>
-        <v>6096.5124000000033</v>
+        <f t="shared" ref="BU31:BV31" si="62">+BT31*1.1</f>
+        <v>5995.4895000000024</v>
       </c>
       <c r="BV31" s="2">
-        <f t="shared" si="61"/>
-        <v>6706.1636400000043</v>
-      </c>
-    </row>
-    <row r="32" spans="2:74" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <f t="shared" si="62"/>
+        <v>6595.0384500000027</v>
+      </c>
+    </row>
+    <row r="32" spans="2:78" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B32" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C32" s="5">
-        <f t="shared" ref="C32:F32" si="62">+C30+C31</f>
+        <f t="shared" ref="C32:F32" si="63">+C30+C31</f>
         <v>389</v>
       </c>
       <c r="D32" s="5">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>606</v>
       </c>
       <c r="E32" s="5">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>959</v>
       </c>
       <c r="F32" s="5">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>1016</v>
       </c>
       <c r="G32" s="5">
-        <f t="shared" ref="G32:T32" si="63">+G30+G31</f>
+        <f t="shared" ref="G32:T32" si="64">+G30+G31</f>
         <v>981</v>
       </c>
       <c r="H32" s="5">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>609</v>
       </c>
       <c r="I32" s="5">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>1348</v>
       </c>
       <c r="J32" s="5">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>1470</v>
       </c>
       <c r="K32" s="5">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>2044</v>
       </c>
       <c r="L32" s="5">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>2394</v>
       </c>
       <c r="M32" s="5">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>2638</v>
       </c>
       <c r="N32" s="5">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>2865</v>
       </c>
       <c r="O32" s="5">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>3158</v>
       </c>
       <c r="P32" s="5">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>475</v>
       </c>
       <c r="Q32" s="5">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>613</v>
       </c>
       <c r="R32" s="5">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>1288</v>
       </c>
       <c r="S32" s="5">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>2209</v>
       </c>
       <c r="T32" s="5">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>6981</v>
       </c>
       <c r="U32" s="5">
-        <f t="shared" ref="U32:AD32" si="64">+U30+U31</f>
+        <f t="shared" ref="U32:AF32" si="65">+U30+U31</f>
         <v>10522</v>
       </c>
       <c r="V32" s="5">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>14106</v>
       </c>
       <c r="W32" s="5">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>17279</v>
       </c>
       <c r="X32" s="5">
@@ -6809,31 +6861,37 @@
         <v>19214</v>
       </c>
       <c r="Y32" s="5">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>22316</v>
       </c>
       <c r="Z32" s="5">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>25217</v>
       </c>
       <c r="AA32" s="5">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>21910</v>
       </c>
       <c r="AB32" s="5">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>31206</v>
       </c>
       <c r="AC32" s="5">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>36573</v>
       </c>
       <c r="AD32" s="5">
-        <f t="shared" si="64"/>
-        <v>46692.2</v>
-      </c>
-      <c r="AE32" s="5"/>
-      <c r="AF32" s="5"/>
+        <f t="shared" si="65"/>
+        <v>44766</v>
+      </c>
+      <c r="AE32" s="5">
+        <f t="shared" si="65"/>
+        <v>54030</v>
+      </c>
+      <c r="AF32" s="5">
+        <f t="shared" si="65"/>
+        <v>61123</v>
+      </c>
       <c r="AG32" s="5"/>
       <c r="AH32" s="5"/>
       <c r="AI32" s="5"/>
@@ -6845,132 +6903,132 @@
       <c r="AO32" s="5"/>
       <c r="AP32" s="5"/>
       <c r="AQ32" s="2">
-        <f t="shared" ref="AQ32" si="65">+AQ30+AQ31</f>
+        <f t="shared" ref="AQ32" si="66">+AQ30+AQ31</f>
         <v>255.90800000000002</v>
       </c>
       <c r="AR32" s="2">
-        <f t="shared" ref="AR32:AS32" si="66">+AR30+AR31</f>
+        <f t="shared" ref="AR32:AS32" si="67">+AR30+AR31</f>
         <v>485.63099999999997</v>
       </c>
       <c r="AS32" s="2">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>873.47899999999993</v>
       </c>
       <c r="AT32" s="2">
-        <f t="shared" ref="AT32:AU32" si="67">+AT30+AT31</f>
+        <f t="shared" ref="AT32:AU32" si="68">+AT30+AT31</f>
         <v>229.06399999999994</v>
       </c>
       <c r="AU32" s="2">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>112.21799999999993</v>
       </c>
       <c r="AV32" s="2">
-        <f t="shared" ref="AV32:BA32" si="68">+AV30+AV31</f>
+        <f t="shared" ref="AV32:BA32" si="69">+AV30+AV31</f>
         <v>125.01499999999984</v>
       </c>
       <c r="AW32" s="2">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>371.51999999999987</v>
       </c>
       <c r="AX32" s="2">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>495.27200000000033</v>
       </c>
       <c r="AY32" s="2">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>900.63499999999976</v>
       </c>
       <c r="AZ32" s="2">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>-1.3790000000003317</v>
       </c>
       <c r="BA32" s="2">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>-75.829999999999714</v>
       </c>
       <c r="BB32" s="2">
-        <f t="shared" ref="BB32:BP32" si="69">+BB30+BB31</f>
+        <f t="shared" ref="BB32:BP32" si="70">+BB30+BB31</f>
         <v>214.16900000000007</v>
       </c>
       <c r="BC32" s="2">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>663.39599999999973</v>
       </c>
       <c r="BD32" s="2">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>662.03899999999999</v>
       </c>
       <c r="BE32" s="2">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>510</v>
       </c>
       <c r="BF32" s="2">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>773</v>
       </c>
       <c r="BG32" s="2">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>874</v>
       </c>
       <c r="BH32" s="2">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>1908</v>
       </c>
       <c r="BI32" s="2">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>3196</v>
       </c>
       <c r="BJ32" s="2">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>3896</v>
       </c>
       <c r="BK32" s="2">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>2970</v>
       </c>
       <c r="BL32" s="2">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>4409</v>
       </c>
       <c r="BM32" s="2">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>9940</v>
       </c>
       <c r="BN32" s="2">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>5537</v>
       </c>
       <c r="BO32" s="2">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>33818</v>
       </c>
       <c r="BP32" s="2">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>84026</v>
       </c>
       <c r="BQ32" s="2">
-        <f t="shared" ref="BQ32:BT32" si="70">+BQ30+BQ31</f>
-        <v>136381.20000000001</v>
+        <f t="shared" ref="BQ32:BT32" si="71">+BQ30+BQ31</f>
+        <v>134455</v>
       </c>
       <c r="BR32" s="2">
         <f>+BR30+BR31</f>
-        <v>285963.01500000001</v>
+        <v>284486.47499999998</v>
       </c>
       <c r="BS32" s="2">
-        <f t="shared" si="70"/>
-        <v>517455.94139999995</v>
+        <f t="shared" si="71"/>
+        <v>515691.68339999998</v>
       </c>
       <c r="BT32" s="2">
-        <f t="shared" si="70"/>
-        <v>729236.52035999985</v>
+        <f t="shared" si="71"/>
+        <v>727127.75975999981</v>
       </c>
       <c r="BU32" s="2">
-        <f t="shared" ref="BU32" si="71">+BU30+BU31</f>
-        <v>950684.86030799989</v>
+        <f t="shared" ref="BU32" si="72">+BU30+BU31</f>
+        <v>948163.53148799995</v>
       </c>
       <c r="BV32" s="2">
-        <f t="shared" ref="BV32" si="72">+BV30+BV31</f>
-        <v>1239214.0246883999</v>
+        <f t="shared" ref="BV32" si="73">+BV30+BV31</f>
+        <v>1236198.5323944001</v>
       </c>
     </row>
     <row r="33" spans="2:170" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7024,7 +7082,7 @@
         <v>-67</v>
       </c>
       <c r="R33" s="5">
-        <f t="shared" ref="R33" si="73">+BN33-Q33-P33-O33</f>
+        <f t="shared" ref="R33" si="74">+BN33-Q33-P33-O33</f>
         <v>61</v>
       </c>
       <c r="S33" s="5">
@@ -7061,8 +7119,15 @@
         <v>6026</v>
       </c>
       <c r="AD33" s="2">
-        <f>+AD32*0.15</f>
-        <v>7003.829999999999</v>
+        <v>7437</v>
+      </c>
+      <c r="AE33" s="2">
+        <f>+AE32*0.2</f>
+        <v>10806</v>
+      </c>
+      <c r="AF33" s="2">
+        <f>+AF32*0.2</f>
+        <v>12224.6</v>
       </c>
       <c r="AQ33" s="2">
         <v>59.758000000000003</v>
@@ -7147,27 +7212,27 @@
       </c>
       <c r="BQ33" s="2">
         <f>SUM(AA33:AD33)</f>
-        <v>20948.829999999998</v>
+        <v>21382</v>
       </c>
       <c r="BR33" s="2">
         <f>+BR32*0.2</f>
-        <v>57192.603000000003</v>
+        <v>56897.294999999998</v>
       </c>
       <c r="BS33" s="2">
-        <f t="shared" ref="BS33:BT33" si="74">+BS32*0.2</f>
-        <v>103491.18828</v>
+        <f t="shared" ref="BS33:BT33" si="75">+BS32*0.2</f>
+        <v>103138.33668000001</v>
       </c>
       <c r="BT33" s="2">
-        <f t="shared" si="74"/>
-        <v>145847.30407199997</v>
+        <f t="shared" si="75"/>
+        <v>145425.55195199998</v>
       </c>
       <c r="BU33" s="2">
-        <f t="shared" ref="BU33" si="75">+BU32*0.2</f>
-        <v>190136.97206159998</v>
+        <f t="shared" ref="BU33" si="76">+BU32*0.2</f>
+        <v>189632.7062976</v>
       </c>
       <c r="BV33" s="2">
-        <f t="shared" ref="BV33" si="76">+BV32*0.2</f>
-        <v>247842.80493767999</v>
+        <f t="shared" ref="BV33" si="77">+BV32*0.2</f>
+        <v>247239.70647888002</v>
       </c>
     </row>
     <row r="34" spans="2:170" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7175,71 +7240,71 @@
         <v>8</v>
       </c>
       <c r="C34" s="5">
-        <f t="shared" ref="C34:F34" si="77">+C32-C33</f>
+        <f t="shared" ref="C34:F34" si="78">+C32-C33</f>
         <v>394</v>
       </c>
       <c r="D34" s="5">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>552</v>
       </c>
       <c r="E34" s="5">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>899</v>
       </c>
       <c r="F34" s="5">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>951</v>
       </c>
       <c r="G34" s="5">
-        <f t="shared" ref="G34:S34" si="78">+G32-G33</f>
+        <f t="shared" ref="G34:S34" si="79">+G32-G33</f>
         <v>917</v>
       </c>
       <c r="H34" s="5">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>622</v>
       </c>
       <c r="I34" s="5">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>1336</v>
       </c>
       <c r="J34" s="5">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>1457</v>
       </c>
       <c r="K34" s="5">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>1912</v>
       </c>
       <c r="L34" s="5">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>2374</v>
       </c>
       <c r="M34" s="5">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>2464</v>
       </c>
       <c r="N34" s="5">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>3003</v>
       </c>
       <c r="O34" s="5">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>2971</v>
       </c>
       <c r="P34" s="5">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>656</v>
       </c>
       <c r="Q34" s="5">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>680</v>
       </c>
       <c r="R34" s="5">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>1227</v>
       </c>
       <c r="S34" s="5">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>2043</v>
       </c>
       <c r="T34" s="2">
@@ -7247,7 +7312,7 @@
         <v>6188</v>
       </c>
       <c r="U34" s="2">
-        <f t="shared" ref="U34" si="79">U32-U33</f>
+        <f t="shared" ref="U34" si="80">U32-U33</f>
         <v>9243</v>
       </c>
       <c r="V34" s="2">
@@ -7259,544 +7324,552 @@
         <v>14881</v>
       </c>
       <c r="X34" s="2">
-        <f t="shared" ref="X34:AD34" si="80">+X32-X33</f>
+        <f t="shared" ref="X34:AF34" si="81">+X32-X33</f>
         <v>16599</v>
       </c>
       <c r="Y34" s="2">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>19309</v>
       </c>
       <c r="Z34" s="2">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>22091</v>
       </c>
       <c r="AA34" s="2">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>18775</v>
       </c>
       <c r="AB34" s="2">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>26422</v>
       </c>
       <c r="AC34" s="2">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>30547</v>
       </c>
       <c r="AD34" s="2">
-        <f t="shared" si="80"/>
-        <v>39688.369999999995</v>
+        <f t="shared" si="81"/>
+        <v>37329</v>
+      </c>
+      <c r="AE34" s="2">
+        <f t="shared" si="81"/>
+        <v>43224</v>
+      </c>
+      <c r="AF34" s="2">
+        <f t="shared" si="81"/>
+        <v>48898.400000000001</v>
       </c>
       <c r="AQ34" s="2">
-        <f t="shared" ref="AQ34" si="81">+AQ32-AQ33</f>
+        <f t="shared" ref="AQ34" si="82">+AQ32-AQ33</f>
         <v>196.15</v>
       </c>
       <c r="AR34" s="2">
-        <f t="shared" ref="AR34:AS34" si="82">+AR32-AR33</f>
+        <f t="shared" ref="AR34:AS34" si="83">+AR32-AR33</f>
         <v>425.87299999999999</v>
       </c>
       <c r="AS34" s="2">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>813.72099999999989</v>
       </c>
       <c r="AT34" s="2">
-        <f t="shared" ref="AT34:AU34" si="83">+AT32-AT33</f>
+        <f t="shared" ref="AT34:AU34" si="84">+AT32-AT33</f>
         <v>169.30599999999993</v>
       </c>
       <c r="AU34" s="2">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>99.963999999999928</v>
       </c>
       <c r="AV34" s="2">
-        <f t="shared" ref="AV34:BA34" si="84">+AV32-AV33</f>
+        <f t="shared" ref="AV34:BA34" si="85">+AV32-AV33</f>
         <v>99.925999999999846</v>
       </c>
       <c r="AW34" s="2">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>315.90799999999984</v>
       </c>
       <c r="AX34" s="2">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>448.92200000000031</v>
       </c>
       <c r="AY34" s="2">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>796.93899999999974</v>
       </c>
       <c r="AZ34" s="2">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>-1.3790000000003317</v>
       </c>
       <c r="BA34" s="2">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>-75.829999999999714</v>
       </c>
       <c r="BB34" s="2">
-        <f t="shared" ref="BB34:BP34" si="85">+BB32-BB33</f>
+        <f t="shared" ref="BB34:BP34" si="86">+BB32-BB33</f>
         <v>196.14600000000007</v>
       </c>
       <c r="BC34" s="2">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>581.08999999999969</v>
       </c>
       <c r="BD34" s="2">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>562.53599999999994</v>
       </c>
       <c r="BE34" s="2">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>440</v>
       </c>
       <c r="BF34" s="2">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>649</v>
       </c>
       <c r="BG34" s="2">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>745</v>
       </c>
       <c r="BH34" s="2">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>1669</v>
       </c>
       <c r="BI34" s="2">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>3047</v>
       </c>
       <c r="BJ34" s="2">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>4141</v>
       </c>
       <c r="BK34" s="2">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>2796</v>
       </c>
       <c r="BL34" s="2">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>4332</v>
       </c>
       <c r="BM34" s="2">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>9752</v>
       </c>
       <c r="BN34" s="2">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>5537</v>
       </c>
       <c r="BO34" s="2">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>29759</v>
       </c>
       <c r="BP34" s="2">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>72880</v>
       </c>
       <c r="BQ34" s="2">
-        <f t="shared" ref="BQ34:BT34" si="86">+BQ32-BQ33</f>
-        <v>115432.37000000001</v>
+        <f t="shared" ref="BQ34:BT34" si="87">+BQ32-BQ33</f>
+        <v>113073</v>
       </c>
       <c r="BR34" s="2">
         <f>+BR32-BR33</f>
-        <v>228770.41200000001</v>
+        <v>227589.18</v>
       </c>
       <c r="BS34" s="2">
-        <f t="shared" si="86"/>
-        <v>413964.75311999995</v>
+        <f t="shared" si="87"/>
+        <v>412553.34671999997</v>
       </c>
       <c r="BT34" s="2">
-        <f t="shared" si="86"/>
-        <v>583389.21628799988</v>
+        <f t="shared" si="87"/>
+        <v>581702.2078079998</v>
       </c>
       <c r="BU34" s="2">
-        <f t="shared" ref="BU34" si="87">+BU32-BU33</f>
-        <v>760547.88824639993</v>
+        <f t="shared" ref="BU34" si="88">+BU32-BU33</f>
+        <v>758530.82519040001</v>
       </c>
       <c r="BV34" s="2">
-        <f t="shared" ref="BV34" si="88">+BV32-BV33</f>
-        <v>991371.21975071984</v>
+        <f t="shared" ref="BV34" si="89">+BV32-BV33</f>
+        <v>988958.82591552008</v>
       </c>
       <c r="BW34" s="2">
-        <f t="shared" ref="BW34:DB34" si="89">BV34*(1+$BY$44)</f>
-        <v>991371.21975071984</v>
+        <f t="shared" ref="BW34:DB34" si="90">BV34*(1+$BY$44)</f>
+        <v>988958.82591552008</v>
       </c>
       <c r="BX34" s="2">
-        <f t="shared" si="89"/>
-        <v>991371.21975071984</v>
+        <f t="shared" si="90"/>
+        <v>988958.82591552008</v>
       </c>
       <c r="BY34" s="2">
-        <f t="shared" si="89"/>
-        <v>991371.21975071984</v>
+        <f t="shared" si="90"/>
+        <v>988958.82591552008</v>
       </c>
       <c r="BZ34" s="2">
-        <f t="shared" si="89"/>
-        <v>991371.21975071984</v>
+        <f t="shared" si="90"/>
+        <v>988958.82591552008</v>
       </c>
       <c r="CA34" s="2">
-        <f t="shared" si="89"/>
-        <v>991371.21975071984</v>
+        <f t="shared" si="90"/>
+        <v>988958.82591552008</v>
       </c>
       <c r="CB34" s="2">
-        <f t="shared" si="89"/>
-        <v>991371.21975071984</v>
+        <f t="shared" si="90"/>
+        <v>988958.82591552008</v>
       </c>
       <c r="CC34" s="2">
-        <f t="shared" si="89"/>
-        <v>991371.21975071984</v>
+        <f t="shared" si="90"/>
+        <v>988958.82591552008</v>
       </c>
       <c r="CD34" s="2">
-        <f t="shared" si="89"/>
-        <v>991371.21975071984</v>
+        <f t="shared" si="90"/>
+        <v>988958.82591552008</v>
       </c>
       <c r="CE34" s="2">
-        <f t="shared" si="89"/>
-        <v>991371.21975071984</v>
+        <f t="shared" si="90"/>
+        <v>988958.82591552008</v>
       </c>
       <c r="CF34" s="2">
-        <f t="shared" si="89"/>
-        <v>991371.21975071984</v>
+        <f t="shared" si="90"/>
+        <v>988958.82591552008</v>
       </c>
       <c r="CG34" s="2">
-        <f t="shared" si="89"/>
-        <v>991371.21975071984</v>
+        <f t="shared" si="90"/>
+        <v>988958.82591552008</v>
       </c>
       <c r="CH34" s="2">
-        <f t="shared" si="89"/>
-        <v>991371.21975071984</v>
+        <f t="shared" si="90"/>
+        <v>988958.82591552008</v>
       </c>
       <c r="CI34" s="2">
-        <f t="shared" si="89"/>
-        <v>991371.21975071984</v>
+        <f t="shared" si="90"/>
+        <v>988958.82591552008</v>
       </c>
       <c r="CJ34" s="2">
-        <f t="shared" si="89"/>
-        <v>991371.21975071984</v>
+        <f t="shared" si="90"/>
+        <v>988958.82591552008</v>
       </c>
       <c r="CK34" s="2">
-        <f t="shared" si="89"/>
-        <v>991371.21975071984</v>
+        <f t="shared" si="90"/>
+        <v>988958.82591552008</v>
       </c>
       <c r="CL34" s="2">
-        <f t="shared" si="89"/>
-        <v>991371.21975071984</v>
+        <f t="shared" si="90"/>
+        <v>988958.82591552008</v>
       </c>
       <c r="CM34" s="2">
-        <f t="shared" si="89"/>
-        <v>991371.21975071984</v>
+        <f t="shared" si="90"/>
+        <v>988958.82591552008</v>
       </c>
       <c r="CN34" s="2">
-        <f t="shared" si="89"/>
-        <v>991371.21975071984</v>
+        <f t="shared" si="90"/>
+        <v>988958.82591552008</v>
       </c>
       <c r="CO34" s="2">
-        <f t="shared" si="89"/>
-        <v>991371.21975071984</v>
+        <f t="shared" si="90"/>
+        <v>988958.82591552008</v>
       </c>
       <c r="CP34" s="2">
-        <f t="shared" si="89"/>
-        <v>991371.21975071984</v>
+        <f t="shared" si="90"/>
+        <v>988958.82591552008</v>
       </c>
       <c r="CQ34" s="2">
-        <f t="shared" si="89"/>
-        <v>991371.21975071984</v>
+        <f t="shared" si="90"/>
+        <v>988958.82591552008</v>
       </c>
       <c r="CR34" s="2">
-        <f t="shared" si="89"/>
-        <v>991371.21975071984</v>
+        <f t="shared" si="90"/>
+        <v>988958.82591552008</v>
       </c>
       <c r="CS34" s="2">
-        <f t="shared" si="89"/>
-        <v>991371.21975071984</v>
+        <f t="shared" si="90"/>
+        <v>988958.82591552008</v>
       </c>
       <c r="CT34" s="2">
-        <f t="shared" si="89"/>
-        <v>991371.21975071984</v>
+        <f t="shared" si="90"/>
+        <v>988958.82591552008</v>
       </c>
       <c r="CU34" s="2">
-        <f t="shared" si="89"/>
-        <v>991371.21975071984</v>
+        <f t="shared" si="90"/>
+        <v>988958.82591552008</v>
       </c>
       <c r="CV34" s="2">
-        <f t="shared" si="89"/>
-        <v>991371.21975071984</v>
+        <f t="shared" si="90"/>
+        <v>988958.82591552008</v>
       </c>
       <c r="CW34" s="2">
-        <f t="shared" si="89"/>
-        <v>991371.21975071984</v>
+        <f t="shared" si="90"/>
+        <v>988958.82591552008</v>
       </c>
       <c r="CX34" s="2">
-        <f t="shared" si="89"/>
-        <v>991371.21975071984</v>
+        <f t="shared" si="90"/>
+        <v>988958.82591552008</v>
       </c>
       <c r="CY34" s="2">
-        <f t="shared" si="89"/>
-        <v>991371.21975071984</v>
+        <f t="shared" si="90"/>
+        <v>988958.82591552008</v>
       </c>
       <c r="CZ34" s="2">
-        <f t="shared" si="89"/>
-        <v>991371.21975071984</v>
+        <f t="shared" si="90"/>
+        <v>988958.82591552008</v>
       </c>
       <c r="DA34" s="2">
-        <f t="shared" si="89"/>
-        <v>991371.21975071984</v>
+        <f t="shared" si="90"/>
+        <v>988958.82591552008</v>
       </c>
       <c r="DB34" s="2">
-        <f t="shared" si="89"/>
-        <v>991371.21975071984</v>
+        <f t="shared" si="90"/>
+        <v>988958.82591552008</v>
       </c>
       <c r="DC34" s="2">
-        <f t="shared" ref="DC34:EH34" si="90">DB34*(1+$BY$44)</f>
-        <v>991371.21975071984</v>
+        <f t="shared" ref="DC34:EH34" si="91">DB34*(1+$BY$44)</f>
+        <v>988958.82591552008</v>
       </c>
       <c r="DD34" s="2">
-        <f t="shared" si="90"/>
-        <v>991371.21975071984</v>
+        <f t="shared" si="91"/>
+        <v>988958.82591552008</v>
       </c>
       <c r="DE34" s="2">
-        <f t="shared" si="90"/>
-        <v>991371.21975071984</v>
+        <f t="shared" si="91"/>
+        <v>988958.82591552008</v>
       </c>
       <c r="DF34" s="2">
-        <f t="shared" si="90"/>
-        <v>991371.21975071984</v>
+        <f t="shared" si="91"/>
+        <v>988958.82591552008</v>
       </c>
       <c r="DG34" s="2">
-        <f t="shared" si="90"/>
-        <v>991371.21975071984</v>
+        <f t="shared" si="91"/>
+        <v>988958.82591552008</v>
       </c>
       <c r="DH34" s="2">
-        <f t="shared" si="90"/>
-        <v>991371.21975071984</v>
+        <f t="shared" si="91"/>
+        <v>988958.82591552008</v>
       </c>
       <c r="DI34" s="2">
-        <f t="shared" si="90"/>
-        <v>991371.21975071984</v>
+        <f t="shared" si="91"/>
+        <v>988958.82591552008</v>
       </c>
       <c r="DJ34" s="2">
-        <f t="shared" si="90"/>
-        <v>991371.21975071984</v>
+        <f t="shared" si="91"/>
+        <v>988958.82591552008</v>
       </c>
       <c r="DK34" s="2">
-        <f t="shared" si="90"/>
-        <v>991371.21975071984</v>
+        <f t="shared" si="91"/>
+        <v>988958.82591552008</v>
       </c>
       <c r="DL34" s="2">
-        <f t="shared" si="90"/>
-        <v>991371.21975071984</v>
+        <f t="shared" si="91"/>
+        <v>988958.82591552008</v>
       </c>
       <c r="DM34" s="2">
-        <f t="shared" si="90"/>
-        <v>991371.21975071984</v>
+        <f t="shared" si="91"/>
+        <v>988958.82591552008</v>
       </c>
       <c r="DN34" s="2">
-        <f t="shared" si="90"/>
-        <v>991371.21975071984</v>
+        <f t="shared" si="91"/>
+        <v>988958.82591552008</v>
       </c>
       <c r="DO34" s="2">
-        <f t="shared" si="90"/>
-        <v>991371.21975071984</v>
+        <f t="shared" si="91"/>
+        <v>988958.82591552008</v>
       </c>
       <c r="DP34" s="2">
-        <f t="shared" si="90"/>
-        <v>991371.21975071984</v>
+        <f t="shared" si="91"/>
+        <v>988958.82591552008</v>
       </c>
       <c r="DQ34" s="2">
-        <f t="shared" si="90"/>
-        <v>991371.21975071984</v>
+        <f t="shared" si="91"/>
+        <v>988958.82591552008</v>
       </c>
       <c r="DR34" s="2">
-        <f t="shared" si="90"/>
-        <v>991371.21975071984</v>
+        <f t="shared" si="91"/>
+        <v>988958.82591552008</v>
       </c>
       <c r="DS34" s="2">
-        <f t="shared" si="90"/>
-        <v>991371.21975071984</v>
+        <f t="shared" si="91"/>
+        <v>988958.82591552008</v>
       </c>
       <c r="DT34" s="2">
-        <f t="shared" si="90"/>
-        <v>991371.21975071984</v>
+        <f t="shared" si="91"/>
+        <v>988958.82591552008</v>
       </c>
       <c r="DU34" s="2">
-        <f t="shared" si="90"/>
-        <v>991371.21975071984</v>
+        <f t="shared" si="91"/>
+        <v>988958.82591552008</v>
       </c>
       <c r="DV34" s="2">
-        <f t="shared" si="90"/>
-        <v>991371.21975071984</v>
+        <f t="shared" si="91"/>
+        <v>988958.82591552008</v>
       </c>
       <c r="DW34" s="2">
-        <f t="shared" si="90"/>
-        <v>991371.21975071984</v>
+        <f t="shared" si="91"/>
+        <v>988958.82591552008</v>
       </c>
       <c r="DX34" s="2">
-        <f t="shared" si="90"/>
-        <v>991371.21975071984</v>
+        <f t="shared" si="91"/>
+        <v>988958.82591552008</v>
       </c>
       <c r="DY34" s="2">
-        <f t="shared" si="90"/>
-        <v>991371.21975071984</v>
+        <f t="shared" si="91"/>
+        <v>988958.82591552008</v>
       </c>
       <c r="DZ34" s="2">
-        <f t="shared" si="90"/>
-        <v>991371.21975071984</v>
+        <f t="shared" si="91"/>
+        <v>988958.82591552008</v>
       </c>
       <c r="EA34" s="2">
-        <f t="shared" si="90"/>
-        <v>991371.21975071984</v>
+        <f t="shared" si="91"/>
+        <v>988958.82591552008</v>
       </c>
       <c r="EB34" s="2">
-        <f t="shared" si="90"/>
-        <v>991371.21975071984</v>
+        <f t="shared" si="91"/>
+        <v>988958.82591552008</v>
       </c>
       <c r="EC34" s="2">
-        <f t="shared" si="90"/>
-        <v>991371.21975071984</v>
+        <f t="shared" si="91"/>
+        <v>988958.82591552008</v>
       </c>
       <c r="ED34" s="2">
-        <f t="shared" si="90"/>
-        <v>991371.21975071984</v>
+        <f t="shared" si="91"/>
+        <v>988958.82591552008</v>
       </c>
       <c r="EE34" s="2">
-        <f t="shared" si="90"/>
-        <v>991371.21975071984</v>
+        <f t="shared" si="91"/>
+        <v>988958.82591552008</v>
       </c>
       <c r="EF34" s="2">
-        <f t="shared" si="90"/>
-        <v>991371.21975071984</v>
+        <f t="shared" si="91"/>
+        <v>988958.82591552008</v>
       </c>
       <c r="EG34" s="2">
-        <f t="shared" si="90"/>
-        <v>991371.21975071984</v>
+        <f t="shared" si="91"/>
+        <v>988958.82591552008</v>
       </c>
       <c r="EH34" s="2">
-        <f t="shared" si="90"/>
-        <v>991371.21975071984</v>
+        <f t="shared" si="91"/>
+        <v>988958.82591552008</v>
       </c>
       <c r="EI34" s="2">
-        <f t="shared" ref="EI34:FN34" si="91">EH34*(1+$BY$44)</f>
-        <v>991371.21975071984</v>
+        <f t="shared" ref="EI34:FN34" si="92">EH34*(1+$BY$44)</f>
+        <v>988958.82591552008</v>
       </c>
       <c r="EJ34" s="2">
-        <f t="shared" si="91"/>
-        <v>991371.21975071984</v>
+        <f t="shared" si="92"/>
+        <v>988958.82591552008</v>
       </c>
       <c r="EK34" s="2">
-        <f t="shared" si="91"/>
-        <v>991371.21975071984</v>
+        <f t="shared" si="92"/>
+        <v>988958.82591552008</v>
       </c>
       <c r="EL34" s="2">
-        <f t="shared" si="91"/>
-        <v>991371.21975071984</v>
+        <f t="shared" si="92"/>
+        <v>988958.82591552008</v>
       </c>
       <c r="EM34" s="2">
-        <f t="shared" si="91"/>
-        <v>991371.21975071984</v>
+        <f t="shared" si="92"/>
+        <v>988958.82591552008</v>
       </c>
       <c r="EN34" s="2">
-        <f t="shared" si="91"/>
-        <v>991371.21975071984</v>
+        <f t="shared" si="92"/>
+        <v>988958.82591552008</v>
       </c>
       <c r="EO34" s="2">
-        <f t="shared" si="91"/>
-        <v>991371.21975071984</v>
+        <f t="shared" si="92"/>
+        <v>988958.82591552008</v>
       </c>
       <c r="EP34" s="2">
-        <f t="shared" si="91"/>
-        <v>991371.21975071984</v>
+        <f t="shared" si="92"/>
+        <v>988958.82591552008</v>
       </c>
       <c r="EQ34" s="2">
-        <f t="shared" si="91"/>
-        <v>991371.21975071984</v>
+        <f t="shared" si="92"/>
+        <v>988958.82591552008</v>
       </c>
       <c r="ER34" s="2">
-        <f t="shared" si="91"/>
-        <v>991371.21975071984</v>
+        <f t="shared" si="92"/>
+        <v>988958.82591552008</v>
       </c>
       <c r="ES34" s="2">
-        <f t="shared" si="91"/>
-        <v>991371.21975071984</v>
+        <f t="shared" si="92"/>
+        <v>988958.82591552008</v>
       </c>
       <c r="ET34" s="2">
-        <f t="shared" si="91"/>
-        <v>991371.21975071984</v>
+        <f t="shared" si="92"/>
+        <v>988958.82591552008</v>
       </c>
       <c r="EU34" s="2">
-        <f t="shared" si="91"/>
-        <v>991371.21975071984</v>
+        <f t="shared" si="92"/>
+        <v>988958.82591552008</v>
       </c>
       <c r="EV34" s="2">
-        <f t="shared" si="91"/>
-        <v>991371.21975071984</v>
+        <f t="shared" si="92"/>
+        <v>988958.82591552008</v>
       </c>
       <c r="EW34" s="2">
-        <f t="shared" si="91"/>
-        <v>991371.21975071984</v>
+        <f t="shared" si="92"/>
+        <v>988958.82591552008</v>
       </c>
       <c r="EX34" s="2">
-        <f t="shared" si="91"/>
-        <v>991371.21975071984</v>
+        <f t="shared" si="92"/>
+        <v>988958.82591552008</v>
       </c>
       <c r="EY34" s="2">
-        <f t="shared" si="91"/>
-        <v>991371.21975071984</v>
+        <f t="shared" si="92"/>
+        <v>988958.82591552008</v>
       </c>
       <c r="EZ34" s="2">
-        <f t="shared" si="91"/>
-        <v>991371.21975071984</v>
+        <f t="shared" si="92"/>
+        <v>988958.82591552008</v>
       </c>
       <c r="FA34" s="2">
-        <f t="shared" si="91"/>
-        <v>991371.21975071984</v>
+        <f t="shared" si="92"/>
+        <v>988958.82591552008</v>
       </c>
       <c r="FB34" s="2">
-        <f t="shared" si="91"/>
-        <v>991371.21975071984</v>
+        <f t="shared" si="92"/>
+        <v>988958.82591552008</v>
       </c>
       <c r="FC34" s="2">
-        <f t="shared" si="91"/>
-        <v>991371.21975071984</v>
+        <f t="shared" si="92"/>
+        <v>988958.82591552008</v>
       </c>
       <c r="FD34" s="2">
-        <f t="shared" si="91"/>
-        <v>991371.21975071984</v>
+        <f t="shared" si="92"/>
+        <v>988958.82591552008</v>
       </c>
       <c r="FE34" s="2">
-        <f t="shared" si="91"/>
-        <v>991371.21975071984</v>
+        <f t="shared" si="92"/>
+        <v>988958.82591552008</v>
       </c>
       <c r="FF34" s="2">
-        <f t="shared" si="91"/>
-        <v>991371.21975071984</v>
+        <f t="shared" si="92"/>
+        <v>988958.82591552008</v>
       </c>
       <c r="FG34" s="2">
-        <f t="shared" si="91"/>
-        <v>991371.21975071984</v>
+        <f t="shared" si="92"/>
+        <v>988958.82591552008</v>
       </c>
       <c r="FH34" s="2">
-        <f t="shared" si="91"/>
-        <v>991371.21975071984</v>
+        <f t="shared" si="92"/>
+        <v>988958.82591552008</v>
       </c>
       <c r="FI34" s="2">
-        <f t="shared" si="91"/>
-        <v>991371.21975071984</v>
+        <f t="shared" si="92"/>
+        <v>988958.82591552008</v>
       </c>
       <c r="FJ34" s="2">
-        <f t="shared" si="91"/>
-        <v>991371.21975071984</v>
+        <f t="shared" si="92"/>
+        <v>988958.82591552008</v>
       </c>
       <c r="FK34" s="2">
-        <f t="shared" si="91"/>
-        <v>991371.21975071984</v>
+        <f t="shared" si="92"/>
+        <v>988958.82591552008</v>
       </c>
       <c r="FL34" s="2">
-        <f t="shared" si="91"/>
-        <v>991371.21975071984</v>
+        <f t="shared" si="92"/>
+        <v>988958.82591552008</v>
       </c>
       <c r="FM34" s="2">
-        <f t="shared" si="91"/>
-        <v>991371.21975071984</v>
+        <f t="shared" si="92"/>
+        <v>988958.82591552008</v>
       </c>
       <c r="FN34" s="2">
-        <f t="shared" si="91"/>
-        <v>991371.21975071984</v>
+        <f t="shared" si="92"/>
+        <v>988958.82591552008</v>
       </c>
     </row>
     <row r="35" spans="2:170" x14ac:dyDescent="0.25">
@@ -7804,119 +7877,125 @@
         <v>12</v>
       </c>
       <c r="C35" s="6">
-        <f t="shared" ref="C35:F35" si="92">+C34/C36</f>
+        <f t="shared" ref="C35:F35" si="93">+C34/C36</f>
         <v>0.15990259740259741</v>
       </c>
       <c r="D35" s="6">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>0.22402597402597402</v>
       </c>
       <c r="E35" s="6">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>0.36367313915857608</v>
       </c>
       <c r="F35" s="6">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>0.38470873786407767</v>
       </c>
       <c r="G35" s="6">
-        <f t="shared" ref="G35:T35" si="93">+G34/G36</f>
+        <f t="shared" ref="G35:T35" si="94">+G34/G36</f>
         <v>0.36856913183279744</v>
       </c>
       <c r="H35" s="6">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>0.24840255591054314</v>
       </c>
       <c r="I35" s="6">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>0.53015873015873016</v>
       </c>
       <c r="J35" s="6">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>0.57725832012678291</v>
       </c>
       <c r="K35" s="6">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>0.75632911392405067</v>
       </c>
       <c r="L35" s="6">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>0.93759873617693523</v>
       </c>
       <c r="M35" s="6">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>0.97084318360914101</v>
       </c>
       <c r="N35" s="6">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>1.1799607072691551</v>
       </c>
       <c r="O35" s="6">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>1.1710681907765077</v>
       </c>
       <c r="P35" s="6">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>0.26073131955484896</v>
       </c>
       <c r="Q35" s="6">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>0.27210884353741499</v>
       </c>
       <c r="R35" s="6">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>4.894295971280415E-2</v>
       </c>
       <c r="S35" s="6">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>8.2048192771084341E-2</v>
       </c>
       <c r="T35" s="6">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>0.24757941906057454</v>
       </c>
       <c r="U35" s="6">
-        <f t="shared" ref="U35:W35" si="94">+U34/U36</f>
+        <f t="shared" ref="U35:W35" si="95">+U34/U36</f>
         <v>3.7060946271050521</v>
       </c>
       <c r="V35" s="6">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>0.49337349397590363</v>
       </c>
       <c r="W35" s="6">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>5.978706307754118</v>
       </c>
       <c r="X35" s="6">
-        <f t="shared" ref="X35:AD35" si="95">+X34/X36</f>
+        <f t="shared" ref="X35:AF35" si="96">+X34/X36</f>
         <v>0.66802157115260785</v>
       </c>
       <c r="Y35" s="6">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>0.77940582869136998</v>
       </c>
       <c r="Z35" s="6">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>0.8941552659273051</v>
       </c>
       <c r="AA35" s="6">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>0.7628702612652879</v>
       </c>
       <c r="AB35" s="6">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>1.0770422305560086</v>
       </c>
       <c r="AC35" s="6">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>1.2476820651064005</v>
       </c>
       <c r="AD35" s="6">
-        <f t="shared" si="95"/>
-        <v>1.6210582853408486</v>
-      </c>
-      <c r="AE35" s="6"/>
-      <c r="AF35" s="6"/>
+        <f t="shared" si="96"/>
+        <v>1.5278732809430255</v>
+      </c>
+      <c r="AE35" s="6">
+        <f t="shared" si="96"/>
+        <v>1.769155206286837</v>
+      </c>
+      <c r="AF35" s="6">
+        <f t="shared" si="96"/>
+        <v>2.0014079895219385</v>
+      </c>
       <c r="AG35" s="6"/>
       <c r="AH35" s="6"/>
       <c r="AI35" s="6"/>
@@ -7928,132 +8007,132 @@
       <c r="AO35" s="6"/>
       <c r="AP35" s="6"/>
       <c r="AQ35" s="15">
-        <f t="shared" ref="AQ35" si="96">+AQ34/AQ36</f>
+        <f t="shared" ref="AQ35" si="97">+AQ34/AQ36</f>
         <v>1.1648346427701863</v>
       </c>
       <c r="AR35" s="15">
-        <f t="shared" ref="AR35:AS35" si="97">+AR34/AR36</f>
+        <f t="shared" ref="AR35:AS35" si="98">+AR34/AR36</f>
         <v>2.5290421810882875</v>
       </c>
       <c r="AS35" s="15">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>4.8322733130237001</v>
       </c>
       <c r="AT35" s="15">
-        <f t="shared" ref="AT35:AU35" si="98">+AT34/AT36</f>
+        <f t="shared" ref="AT35:AU35" si="99">+AT34/AT36</f>
         <v>1.0054218405753204</v>
       </c>
       <c r="AU35" s="15">
-        <f t="shared" si="98"/>
+        <f t="shared" si="99"/>
         <v>0.57880688101814015</v>
       </c>
       <c r="AV35" s="15">
-        <f t="shared" ref="AV35:BA35" si="99">+AV34/AV36</f>
+        <f t="shared" ref="AV35:BA35" si="100">+AV34/AV36</f>
         <v>0.56596699101711534</v>
       </c>
       <c r="AW35" s="15">
-        <f t="shared" si="99"/>
+        <f t="shared" si="100"/>
         <v>0.62055905867562389</v>
       </c>
       <c r="AX35" s="15">
-        <f t="shared" si="99"/>
+        <f t="shared" si="100"/>
         <v>0.76444003977822339</v>
       </c>
       <c r="AY35" s="15">
-        <f t="shared" si="99"/>
+        <f t="shared" si="100"/>
         <v>1.3134942610575999</v>
       </c>
       <c r="AZ35" s="15">
-        <f t="shared" si="99"/>
+        <f t="shared" si="100"/>
         <v>-2.515844896976848E-3</v>
       </c>
       <c r="BA35" s="15">
-        <f t="shared" si="99"/>
+        <f t="shared" si="100"/>
         <v>-0.13797959874375373</v>
       </c>
       <c r="BB35" s="15">
-        <f t="shared" ref="BB35" si="100">+BB34/BB36</f>
+        <f t="shared" ref="BB35" si="101">+BB34/BB36</f>
         <v>0.33319403958660349</v>
       </c>
       <c r="BC35" s="15">
-        <f t="shared" ref="BC35:BD35" si="101">+BC34/BC36</f>
+        <f t="shared" ref="BC35:BD35" si="102">+BC34/BC36</f>
         <v>0.94276012336725723</v>
       </c>
       <c r="BD35" s="15">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>0.90011952822354169</v>
       </c>
       <c r="BE35" s="15">
-        <f t="shared" ref="BE35:BF35" si="102">+BE34/BE36</f>
+        <f t="shared" ref="BE35:BF35" si="103">+BE34/BE36</f>
         <v>0.73949579831932777</v>
       </c>
       <c r="BF35" s="15">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>1.152753108348135</v>
       </c>
       <c r="BG35" s="15">
-        <f t="shared" ref="BG35:BH35" si="103">+BG34/BG36</f>
+        <f t="shared" ref="BG35:BH35" si="104">+BG34/BG36</f>
         <v>1.3093145869947276</v>
       </c>
       <c r="BH35" s="15">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v>2.5716486902927582</v>
       </c>
       <c r="BI35" s="15">
-        <f t="shared" ref="BI35:BJ35" si="104">+BI34/BI36</f>
+        <f t="shared" ref="BI35:BJ35" si="105">+BI34/BI36</f>
         <v>4.8212025316455698</v>
       </c>
       <c r="BJ35" s="15">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>6.6256000000000004</v>
       </c>
       <c r="BK35" s="15">
-        <f t="shared" ref="BK35:BL35" si="105">+BK34/BK36</f>
+        <f t="shared" ref="BK35:BL35" si="106">+BK34/BK36</f>
         <v>1.1310679611650485</v>
       </c>
       <c r="BL35" s="15">
-        <f t="shared" si="105"/>
+        <f t="shared" si="106"/>
         <v>1.7258964143426294</v>
       </c>
       <c r="BM35" s="15">
-        <f t="shared" ref="BM35:BT35" si="106">+BM34/BM36</f>
+        <f t="shared" ref="BM35:BT35" si="107">+BM34/BM36</f>
         <v>3.8469428007889546</v>
       </c>
       <c r="BN35" s="15">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>0.22086158755484642</v>
       </c>
       <c r="BO35" s="15">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>1.1932237369687249</v>
       </c>
       <c r="BP35" s="15">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>2.9382357684244478</v>
       </c>
       <c r="BQ35" s="15">
-        <f t="shared" si="106"/>
-        <v>4.7062907582382865</v>
+        <f t="shared" si="107"/>
+        <v>4.6124946460258212</v>
       </c>
       <c r="BR35" s="15">
         <f>+BR34/BR36</f>
-        <v>9.3271937131150047</v>
+        <v>9.28385975647066</v>
       </c>
       <c r="BS35" s="15">
-        <f t="shared" si="106"/>
-        <v>16.877748346023299</v>
+        <f t="shared" si="107"/>
+        <v>16.828952118950006</v>
       </c>
       <c r="BT35" s="15">
-        <f t="shared" si="106"/>
-        <v>23.785349612696077</v>
+        <f t="shared" si="107"/>
+        <v>23.728903620632678</v>
       </c>
       <c r="BU35" s="15">
-        <f t="shared" ref="BU35:BV35" si="107">+BU34/BU36</f>
-        <v>31.008282145222147</v>
+        <f t="shared" ref="BU35:BV35" si="108">+BU34/BU36</f>
+        <v>30.942129155822066</v>
       </c>
       <c r="BV35" s="15">
-        <f t="shared" si="107"/>
-        <v>40.419175396781938</v>
+        <f t="shared" si="108"/>
+        <v>40.341790610272291</v>
       </c>
       <c r="BW35" s="15"/>
     </row>
@@ -8152,11 +8231,16 @@
         <v>24483</v>
       </c>
       <c r="AD36" s="2">
-        <f>+AC36</f>
-        <v>24483</v>
-      </c>
-      <c r="AE36" s="2"/>
-      <c r="AF36" s="2"/>
+        <v>24432</v>
+      </c>
+      <c r="AE36" s="2">
+        <f>+AD36</f>
+        <v>24432</v>
+      </c>
+      <c r="AF36" s="2">
+        <f>+AE36</f>
+        <v>24432</v>
+      </c>
       <c r="AG36" s="2"/>
       <c r="AH36" s="2"/>
       <c r="AI36" s="2"/>
@@ -8247,27 +8331,27 @@
       </c>
       <c r="BQ36" s="2">
         <f>AVERAGE(AA36:AD36)</f>
-        <v>24527.25</v>
+        <v>24514.5</v>
       </c>
       <c r="BR36" s="2">
         <f>+BQ36</f>
-        <v>24527.25</v>
+        <v>24514.5</v>
       </c>
       <c r="BS36" s="2">
         <f>+BR36</f>
-        <v>24527.25</v>
+        <v>24514.5</v>
       </c>
       <c r="BT36" s="2">
         <f>+BS36</f>
-        <v>24527.25</v>
+        <v>24514.5</v>
       </c>
       <c r="BU36" s="2">
-        <f t="shared" ref="BU36:BV36" si="108">+BT36</f>
-        <v>24527.25</v>
+        <f t="shared" ref="BU36:BV36" si="109">+BT36</f>
+        <v>24514.5</v>
       </c>
       <c r="BV36" s="2">
-        <f t="shared" si="108"/>
-        <v>24527.25</v>
+        <f t="shared" si="109"/>
+        <v>24514.5</v>
       </c>
       <c r="BW36" s="2"/>
     </row>
@@ -8280,67 +8364,67 @@
       <c r="E38" s="29"/>
       <c r="F38" s="29"/>
       <c r="G38" s="17">
-        <f t="shared" ref="G38" si="109">+G24/C24-1</f>
+        <f t="shared" ref="G38" si="110">+G24/C24-1</f>
         <v>0.38738738738738743</v>
       </c>
       <c r="H38" s="17">
-        <f t="shared" ref="H38" si="110">+H24/D24-1</f>
+        <f t="shared" ref="H38" si="111">+H24/D24-1</f>
         <v>0.49903063202791786</v>
       </c>
       <c r="I38" s="17">
-        <f t="shared" ref="I38" si="111">+I24/E24-1</f>
+        <f t="shared" ref="I38" si="112">+I24/E24-1</f>
         <v>0.56801592568015935</v>
       </c>
       <c r="J38" s="17">
-        <f t="shared" ref="J38" si="112">+J24/F24-1</f>
+        <f t="shared" ref="J38" si="113">+J24/F24-1</f>
         <v>0.61127214170692423</v>
       </c>
       <c r="K38" s="17">
-        <f t="shared" ref="K38:M38" si="113">+K24/G24-1</f>
+        <f t="shared" ref="K38:M38" si="114">+K24/G24-1</f>
         <v>0.83798701298701306</v>
       </c>
       <c r="L38" s="17">
-        <f t="shared" si="113"/>
+        <f t="shared" si="114"/>
         <v>0.68313502327987585</v>
       </c>
       <c r="M38" s="17">
-        <f t="shared" si="113"/>
+        <f t="shared" si="114"/>
         <v>0.50296233601354201</v>
       </c>
       <c r="N38" s="17">
-        <f t="shared" ref="N38:V38" si="114">+N24/J24-1</f>
+        <f t="shared" ref="N38:V38" si="115">+N24/J24-1</f>
         <v>0.52768338996602049</v>
       </c>
       <c r="O38" s="17">
-        <f t="shared" si="114"/>
+        <f t="shared" si="115"/>
         <v>0.46405228758169925</v>
       </c>
       <c r="P38" s="17">
-        <f t="shared" si="114"/>
+        <f t="shared" si="115"/>
         <v>3.0275088366374714E-2</v>
       </c>
       <c r="Q38" s="17">
-        <f t="shared" si="114"/>
+        <f t="shared" si="115"/>
         <v>-0.16500070392791777</v>
       </c>
       <c r="R38" s="17">
-        <f t="shared" si="114"/>
+        <f t="shared" si="115"/>
         <v>-0.20829517205285886</v>
       </c>
       <c r="S38" s="17">
-        <f t="shared" si="114"/>
+        <f t="shared" si="115"/>
         <v>-0.13223938223938225</v>
       </c>
       <c r="T38" s="17">
-        <f t="shared" si="114"/>
+        <f t="shared" si="115"/>
         <v>1.0147673031026252</v>
       </c>
       <c r="U38" s="17">
-        <f t="shared" si="114"/>
+        <f t="shared" si="115"/>
         <v>2.0551340414769852</v>
       </c>
       <c r="V38" s="17">
-        <f t="shared" si="114"/>
+        <f t="shared" si="115"/>
         <v>2.6527846636919516</v>
       </c>
       <c r="W38" s="17">
@@ -8348,19 +8432,19 @@
         <v>2.6212458286985538</v>
       </c>
       <c r="X38" s="17">
-        <f t="shared" ref="X38" si="115">+X24/T24-1</f>
+        <f t="shared" ref="X38" si="116">+X24/T24-1</f>
         <v>1.2240319834160065</v>
       </c>
       <c r="Y38" s="17">
-        <f t="shared" ref="Y38" si="116">+Y24/U24-1</f>
+        <f t="shared" ref="Y38" si="117">+Y24/U24-1</f>
         <v>0.93609271523178816</v>
       </c>
       <c r="Z38" s="17">
-        <f t="shared" ref="Z38:AA38" si="117">+Z24/V24-1</f>
+        <f t="shared" ref="Z38:AA38" si="118">+Z24/V24-1</f>
         <v>0.77944170474596208</v>
       </c>
       <c r="AA38" s="17">
-        <f t="shared" si="117"/>
+        <f t="shared" si="118"/>
         <v>0.69182921210259551</v>
       </c>
       <c r="AB38" s="17">
@@ -8376,19 +8460,19 @@
         <v>0.73145864585187259</v>
       </c>
       <c r="AE38" s="17">
-        <f t="shared" ref="AE38:AH38" si="118">+AE24/AA24-1</f>
-        <v>0.77023285370614136</v>
+        <f t="shared" ref="AE38:AH38" si="119">+AE24/AA24-1</f>
+        <v>0.85227633788752222</v>
       </c>
       <c r="AF38" s="17">
-        <f t="shared" si="118"/>
-        <v>0.81845410007915631</v>
+        <f t="shared" si="119"/>
+        <v>0.94681556596709671</v>
       </c>
       <c r="AG38" s="17">
-        <f t="shared" si="118"/>
+        <f t="shared" si="119"/>
         <v>0.66649124653545244</v>
       </c>
       <c r="AH38" s="17">
-        <f t="shared" si="118"/>
+        <f t="shared" si="119"/>
         <v>0.46842878120411169</v>
       </c>
       <c r="AI38" s="17"/>
@@ -8397,119 +8481,119 @@
       <c r="AL38" s="17"/>
       <c r="AM38" s="17"/>
       <c r="AN38" s="17">
-        <f t="shared" ref="AN38" si="119">+AN24/AM24-1</f>
+        <f t="shared" ref="AN38" si="120">+AN24/AM24-1</f>
         <v>6.4312372188139069</v>
       </c>
       <c r="AO38" s="17">
-        <f t="shared" ref="AO38" si="120">+AO24/AN24-1</f>
+        <f t="shared" ref="AO38" si="121">+AO24/AN24-1</f>
         <v>-0.54249939802552372</v>
       </c>
       <c r="AP38" s="17">
-        <f t="shared" ref="AP38" si="121">+AP24/AO24-1</f>
+        <f t="shared" ref="AP38" si="122">+AP24/AO24-1</f>
         <v>10.897518796992481</v>
       </c>
       <c r="AQ38" s="17">
-        <f t="shared" ref="AQ38" si="122">+AQ24/AP24-1</f>
+        <f t="shared" ref="AQ38" si="123">+AQ24/AP24-1</f>
         <v>1.3667347080644854</v>
       </c>
       <c r="AR38" s="17">
-        <f t="shared" ref="AR38" si="123">+AR24/AQ24-1</f>
+        <f t="shared" ref="AR38" si="124">+AR24/AQ24-1</f>
         <v>0.96329555012616663</v>
       </c>
       <c r="AS38" s="17">
-        <f t="shared" ref="AS38" si="124">+AS24/AR24-1</f>
+        <f t="shared" ref="AS38" si="125">+AS24/AR24-1</f>
         <v>0.86255685032858942</v>
       </c>
       <c r="AT38" s="17">
-        <f t="shared" ref="AT38" si="125">+AT24/AS24-1</f>
+        <f t="shared" ref="AT38" si="126">+AT24/AS24-1</f>
         <v>0.39429531549043384</v>
       </c>
       <c r="AU38" s="17">
-        <f t="shared" ref="AU38:AW38" si="126">+AU24/AT24-1</f>
+        <f t="shared" ref="AU38:AW38" si="127">+AU24/AT24-1</f>
         <v>-4.5302121504288917E-2</v>
       </c>
       <c r="AV38" s="17">
-        <f t="shared" si="126"/>
+        <f t="shared" si="127"/>
         <v>0.10262953627235039</v>
       </c>
       <c r="AW38" s="17">
-        <f t="shared" si="126"/>
+        <f t="shared" si="127"/>
         <v>0.18191442628056365</v>
       </c>
       <c r="AX38" s="17">
-        <f t="shared" ref="AX38" si="127">+AX24/AW24-1</f>
+        <f t="shared" ref="AX38" si="128">+AX24/AW24-1</f>
         <v>0.29174045234073365</v>
       </c>
       <c r="AY38" s="17">
-        <f t="shared" ref="AY38" si="128">+AY24/AX24-1</f>
+        <f t="shared" ref="AY38" si="129">+AY24/AX24-1</f>
         <v>0.33534238951032824</v>
       </c>
       <c r="AZ38" s="17">
-        <f t="shared" ref="AZ38" si="129">+AZ24/AY24-1</f>
+        <f t="shared" ref="AZ38" si="130">+AZ24/AY24-1</f>
         <v>-0.16423230661857646</v>
       </c>
       <c r="BA38" s="17">
-        <f t="shared" ref="BA38" si="130">+BA24/AZ24-1</f>
+        <f t="shared" ref="BA38" si="131">+BA24/AZ24-1</f>
         <v>-2.8735197565797566E-2</v>
       </c>
       <c r="BB38" s="17">
-        <f t="shared" ref="BB38" si="131">+BB24/BA24-1</f>
+        <f t="shared" ref="BB38" si="132">+BB24/BA24-1</f>
         <v>6.5193923242380381E-2</v>
       </c>
       <c r="BC38" s="17">
-        <f t="shared" ref="BC38:BV38" si="132">+BC24/BB24-1</f>
+        <f t="shared" ref="BC38:BV38" si="133">+BC24/BB24-1</f>
         <v>0.12830407960468571</v>
       </c>
       <c r="BD38" s="17">
-        <f t="shared" si="132"/>
+        <f t="shared" si="133"/>
         <v>7.0593782282331041E-2</v>
       </c>
       <c r="BE38" s="17">
-        <f t="shared" si="132"/>
+        <f t="shared" si="133"/>
         <v>-3.5082575203397748E-2</v>
       </c>
       <c r="BF38" s="17">
-        <f t="shared" si="132"/>
+        <f t="shared" si="133"/>
         <v>0.13365617433414045</v>
       </c>
       <c r="BG38" s="17">
-        <f t="shared" si="132"/>
+        <f t="shared" si="133"/>
         <v>7.0055531824006811E-2</v>
       </c>
       <c r="BH38" s="17">
-        <f t="shared" si="132"/>
+        <f t="shared" si="133"/>
         <v>0.37924151696606789</v>
       </c>
       <c r="BI38" s="17">
-        <f t="shared" si="132"/>
+        <f t="shared" si="133"/>
         <v>0.40578871201157751</v>
       </c>
       <c r="BJ38" s="17">
-        <f t="shared" si="132"/>
+        <f t="shared" si="133"/>
         <v>0.20609429689108505</v>
       </c>
       <c r="BK38" s="17">
-        <f t="shared" si="132"/>
+        <f t="shared" si="133"/>
         <v>-6.8111983612154314E-2</v>
       </c>
       <c r="BL38" s="17">
-        <f t="shared" si="132"/>
+        <f t="shared" si="133"/>
         <v>0.52729437625938824</v>
       </c>
       <c r="BM38" s="17">
-        <f t="shared" si="132"/>
+        <f t="shared" si="133"/>
         <v>0.61397301349325328</v>
       </c>
       <c r="BN38" s="17">
-        <f t="shared" si="132"/>
+        <f t="shared" si="133"/>
         <v>2.378032920893336E-3</v>
       </c>
       <c r="BO38" s="17">
-        <f t="shared" si="132"/>
+        <f t="shared" si="133"/>
         <v>1.2582941023835117</v>
       </c>
       <c r="BP38" s="17">
-        <f t="shared" si="132"/>
+        <f t="shared" si="133"/>
         <v>1.1420340763599355</v>
       </c>
       <c r="BQ38" s="17">
@@ -8521,19 +8605,19 @@
         <v>0.89999999999999991</v>
       </c>
       <c r="BS38" s="17">
-        <f t="shared" si="132"/>
+        <f t="shared" si="133"/>
         <v>0.7</v>
       </c>
       <c r="BT38" s="17">
-        <f t="shared" si="132"/>
+        <f t="shared" si="133"/>
         <v>0.39999999999999991</v>
       </c>
       <c r="BU38" s="17">
-        <f t="shared" si="132"/>
+        <f t="shared" si="133"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="BV38" s="17">
-        <f t="shared" si="132"/>
+        <f t="shared" si="133"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="BW38" s="17"/>
@@ -8544,79 +8628,79 @@
         <v>72</v>
       </c>
       <c r="D39" s="7">
-        <f t="shared" ref="D39" si="133">+D24/C24-1</f>
+        <f t="shared" ref="D39" si="134">+D24/C24-1</f>
         <v>0.16171171171171173</v>
       </c>
       <c r="E39" s="7">
-        <f t="shared" ref="E39" si="134">+E24/D24-1</f>
+        <f t="shared" ref="E39" si="135">+E24/D24-1</f>
         <v>0.16867002714230317</v>
       </c>
       <c r="F39" s="7">
-        <f t="shared" ref="F39" si="135">+F24/E24-1</f>
+        <f t="shared" ref="F39" si="136">+F24/E24-1</f>
         <v>3.0192435301924281E-2</v>
       </c>
       <c r="G39" s="10">
-        <f t="shared" ref="G39:H39" si="136">+G24/F24-1</f>
+        <f t="shared" ref="G39:H39" si="137">+G24/F24-1</f>
         <v>-8.0515297906602612E-3</v>
       </c>
       <c r="H39" s="10">
-        <f t="shared" si="136"/>
+        <f t="shared" si="137"/>
         <v>0.2551948051948052</v>
       </c>
       <c r="I39" s="10">
-        <f t="shared" ref="I39" si="137">+I24/H24-1</f>
+        <f t="shared" ref="I39" si="138">+I24/H24-1</f>
         <v>0.22245214692188298</v>
       </c>
       <c r="J39" s="10">
-        <f t="shared" ref="J39" si="138">+J24/I24-1</f>
+        <f t="shared" ref="J39" si="139">+J24/I24-1</f>
         <v>5.8611933982225972E-2</v>
       </c>
       <c r="K39" s="10">
-        <f t="shared" ref="K39:V39" si="139">+K24/J24-1</f>
+        <f t="shared" ref="K39:V39" si="140">+K24/J24-1</f>
         <v>0.13152108734759138</v>
       </c>
       <c r="L39" s="10">
-        <f t="shared" si="139"/>
+        <f t="shared" si="140"/>
         <v>0.14944356120826718</v>
       </c>
       <c r="M39" s="10">
-        <f t="shared" si="139"/>
+        <f t="shared" si="140"/>
         <v>9.1593668357153879E-2</v>
       </c>
       <c r="N39" s="10">
-        <f t="shared" si="139"/>
+        <f t="shared" si="140"/>
         <v>7.6024215120371608E-2</v>
       </c>
       <c r="O39" s="10">
-        <f t="shared" si="139"/>
+        <f t="shared" si="140"/>
         <v>8.4390945963626951E-2</v>
       </c>
       <c r="P39" s="10">
-        <f t="shared" si="139"/>
+        <f t="shared" si="140"/>
         <v>-0.19111969111969107</v>
       </c>
       <c r="Q39" s="10">
-        <f t="shared" si="139"/>
+        <f t="shared" si="140"/>
         <v>-0.11530429594272074</v>
       </c>
       <c r="R39" s="10">
-        <f t="shared" si="139"/>
+        <f t="shared" si="140"/>
         <v>2.0232675771370667E-2</v>
       </c>
       <c r="S39" s="10">
-        <f t="shared" si="139"/>
+        <f t="shared" si="140"/>
         <v>0.1885638737398776</v>
       </c>
       <c r="T39" s="10">
-        <f t="shared" si="139"/>
+        <f t="shared" si="140"/>
         <v>0.87805895439377091</v>
       </c>
       <c r="U39" s="10">
-        <f t="shared" si="139"/>
+        <f t="shared" si="140"/>
         <v>0.34152661582882948</v>
       </c>
       <c r="V39" s="10">
-        <f t="shared" si="139"/>
+        <f t="shared" si="140"/>
         <v>0.21981236203090515</v>
       </c>
       <c r="W39" s="10">
@@ -8624,27 +8708,27 @@
         <v>0.17830158801972584</v>
       </c>
       <c r="X39" s="10">
-        <f t="shared" ref="X39" si="140">+X24/W24-1</f>
+        <f t="shared" ref="X39" si="141">+X24/W24-1</f>
         <v>0.1534326524343419</v>
       </c>
       <c r="Y39" s="10">
-        <f t="shared" ref="Y39" si="141">+Y24/X24-1</f>
+        <f t="shared" ref="Y39" si="142">+Y24/X24-1</f>
         <v>0.16784287616511318</v>
       </c>
       <c r="Z39" s="10">
-        <f t="shared" ref="Z39" si="142">+Z24/Y24-1</f>
+        <f t="shared" ref="Z39" si="143">+Z24/Y24-1</f>
         <v>0.12111624194743742</v>
       </c>
       <c r="AA39" s="10">
-        <f t="shared" ref="AA39" si="143">+AA24/Z24-1</f>
+        <f t="shared" ref="AA39" si="144">+AA24/Z24-1</f>
         <v>0.12028679667437903</v>
       </c>
       <c r="AB39" s="10">
-        <f t="shared" ref="AB39" si="144">+AB24/AA24-1</f>
+        <f t="shared" ref="AB39" si="145">+AB24/AA24-1</f>
         <v>6.0846080522899637E-2</v>
       </c>
       <c r="AC39" s="10">
-        <f t="shared" ref="AC39" si="145">+AC24/AB24-1</f>
+        <f t="shared" ref="AC39" si="146">+AC24/AB24-1</f>
         <v>0.21956228740132211</v>
       </c>
       <c r="AD39" s="10">
@@ -8685,75 +8769,75 @@
       </c>
       <c r="D40" s="10"/>
       <c r="E40" s="10">
-        <f t="shared" ref="E40" si="146">+E22/D22-1</f>
+        <f t="shared" ref="E40" si="147">+E22/D22-1</f>
         <v>0.10839694656488552</v>
       </c>
       <c r="F40" s="10">
-        <f t="shared" ref="F40" si="147">+F22/E22-1</f>
+        <f t="shared" ref="F40" si="148">+F22/E22-1</f>
         <v>0.33333333333333326</v>
       </c>
       <c r="G40" s="10">
-        <f t="shared" ref="G40" si="148">+G22/F22-1</f>
+        <f t="shared" ref="G40" si="149">+G22/F22-1</f>
         <v>0.17871900826446274</v>
       </c>
       <c r="H40" s="10">
-        <f t="shared" ref="H40" si="149">+H22/G22-1</f>
+        <f t="shared" ref="H40" si="150">+H22/G22-1</f>
         <v>0.5354951796669587</v>
       </c>
       <c r="I40" s="10">
-        <f t="shared" ref="I40" si="150">+I22/H22-1</f>
+        <f t="shared" ref="I40" si="151">+I22/H22-1</f>
         <v>8.4474885844748826E-2</v>
       </c>
       <c r="J40" s="10">
-        <f t="shared" ref="J40" si="151">+J22/I22-1</f>
+        <f t="shared" ref="J40" si="152">+J22/I22-1</f>
         <v>1.5789473684211242E-3</v>
       </c>
       <c r="K40" s="10">
-        <f t="shared" ref="K40" si="152">+K22/J22-1</f>
+        <f t="shared" ref="K40" si="153">+K22/J22-1</f>
         <v>7.7246452968996238E-2</v>
       </c>
       <c r="L40" s="10">
-        <f t="shared" ref="L40:V40" si="153">+L22/K22-1</f>
+        <f t="shared" ref="L40:V40" si="154">+L22/K22-1</f>
         <v>0.15414634146341455</v>
       </c>
       <c r="M40" s="10">
-        <f t="shared" si="153"/>
+        <f t="shared" si="154"/>
         <v>0.24091293322062546</v>
       </c>
       <c r="N40" s="10">
-        <f t="shared" si="153"/>
+        <f t="shared" si="154"/>
         <v>0.11035422343324242</v>
       </c>
       <c r="O40" s="10">
-        <f t="shared" si="153"/>
+        <f t="shared" si="154"/>
         <v>0.15030674846625769</v>
       </c>
       <c r="P40" s="10">
-        <f t="shared" si="153"/>
+        <f t="shared" si="154"/>
         <v>1.4933333333333243E-2</v>
       </c>
       <c r="Q40" s="10">
-        <f t="shared" si="153"/>
+        <f t="shared" si="154"/>
         <v>7.0940620073567384E-3</v>
       </c>
       <c r="R40" s="10">
-        <f t="shared" si="153"/>
+        <f t="shared" si="154"/>
         <v>-5.5570049569527824E-2</v>
       </c>
       <c r="S40" s="10">
-        <f t="shared" si="153"/>
+        <f t="shared" si="154"/>
         <v>0.18342541436464099</v>
       </c>
       <c r="T40" s="10">
-        <f t="shared" si="153"/>
+        <f t="shared" si="154"/>
         <v>1.4096638655462184</v>
       </c>
       <c r="U40" s="10">
-        <f t="shared" si="153"/>
+        <f t="shared" si="154"/>
         <v>0.40598663179308336</v>
       </c>
       <c r="V40" s="10">
-        <f t="shared" si="153"/>
+        <f t="shared" si="154"/>
         <v>0.2680170869505305</v>
       </c>
       <c r="W40" s="10">
@@ -8761,31 +8845,31 @@
         <v>0.22598348185177142</v>
       </c>
       <c r="X40" s="10">
-        <f t="shared" ref="X40" si="154">+X22/W22-1</f>
+        <f t="shared" ref="X40" si="155">+X22/W22-1</f>
         <v>0.16438416877188322</v>
       </c>
       <c r="Y40" s="10">
-        <f t="shared" ref="Y40" si="155">+Y22/X22-1</f>
+        <f t="shared" ref="Y40" si="156">+Y22/X22-1</f>
         <v>0.17124695493300846</v>
       </c>
       <c r="Z40" s="10">
-        <f t="shared" ref="Z40" si="156">+Z22/Y22-1</f>
+        <f t="shared" ref="Z40" si="157">+Z22/Y22-1</f>
         <v>0.15628351369796234</v>
       </c>
       <c r="AA40" s="10">
-        <f t="shared" ref="AA40" si="157">+AA22/Z22-1</f>
+        <f t="shared" ref="AA40" si="158">+AA22/Z22-1</f>
         <v>9.9269252388982654E-2</v>
       </c>
       <c r="AB40" s="10">
-        <f t="shared" ref="AB40" si="158">+AB22/AA22-1</f>
+        <f t="shared" ref="AB40" si="159">+AB22/AA22-1</f>
         <v>5.0726119860912355E-2</v>
       </c>
       <c r="AC40" s="10">
-        <f t="shared" ref="AC40" si="159">+AC22/AB22-1</f>
+        <f t="shared" ref="AC40" si="160">+AC22/AB22-1</f>
         <v>0.24586334436441493</v>
       </c>
       <c r="AD40" s="10">
-        <f t="shared" ref="AD40" si="160">+AD22/AC22-1</f>
+        <f t="shared" ref="AD40" si="161">+AD22/AC22-1</f>
         <v>0.1466210937500001</v>
       </c>
       <c r="AE40" s="10"/>
@@ -8821,116 +8905,116 @@
         <v>5</v>
       </c>
       <c r="C41" s="7">
-        <f t="shared" ref="C41:F41" si="161">C26/C24</f>
+        <f t="shared" ref="C41:F41" si="162">C26/C24</f>
         <v>0.58378378378378382</v>
       </c>
       <c r="D41" s="7">
-        <f t="shared" si="161"/>
+        <f t="shared" si="162"/>
         <v>0.59751841799146954</v>
       </c>
       <c r="E41" s="7">
-        <f t="shared" si="161"/>
+        <f t="shared" si="162"/>
         <v>0.63570006635700071</v>
       </c>
       <c r="F41" s="7">
-        <f t="shared" si="161"/>
+        <f t="shared" si="162"/>
         <v>0.64895330112721417</v>
       </c>
       <c r="G41" s="7">
-        <f t="shared" ref="G41:H41" si="162">G26/G24</f>
+        <f t="shared" ref="G41:H41" si="163">G26/G24</f>
         <v>0.6506493506493507</v>
       </c>
       <c r="H41" s="7">
-        <f t="shared" si="162"/>
+        <f t="shared" si="163"/>
         <v>0.58846352819451631</v>
       </c>
       <c r="I41" s="7">
-        <f t="shared" ref="I41:U41" si="163">I26/I24</f>
+        <f t="shared" ref="I41:U41" si="164">I26/I24</f>
         <v>0.62632247143461706</v>
       </c>
       <c r="J41" s="7">
-        <f t="shared" si="163"/>
+        <f t="shared" si="164"/>
         <v>0.6310213871676994</v>
       </c>
       <c r="K41" s="7">
-        <f t="shared" si="163"/>
+        <f t="shared" si="164"/>
         <v>0.6410528175234057</v>
       </c>
       <c r="L41" s="7">
-        <f t="shared" si="163"/>
+        <f t="shared" si="164"/>
         <v>0.64776394651913327</v>
       </c>
       <c r="M41" s="7">
-        <f t="shared" si="163"/>
+        <f t="shared" si="164"/>
         <v>0.65197803744896521</v>
       </c>
       <c r="N41" s="7">
-        <f t="shared" si="163"/>
+        <f t="shared" si="164"/>
         <v>0.65406254088708626</v>
       </c>
       <c r="O41" s="7">
-        <f t="shared" si="163"/>
+        <f t="shared" si="164"/>
         <v>0.65528474903474898</v>
       </c>
       <c r="P41" s="7">
-        <f t="shared" si="163"/>
+        <f t="shared" si="164"/>
         <v>0.43481503579952269</v>
       </c>
       <c r="Q41" s="7">
-        <f t="shared" si="163"/>
+        <f t="shared" si="164"/>
         <v>0.53566009104704093</v>
       </c>
       <c r="R41" s="7">
-        <f t="shared" si="163"/>
+        <f t="shared" si="164"/>
         <v>0.63344901669145592</v>
       </c>
       <c r="S41" s="7">
-        <f t="shared" si="163"/>
+        <f t="shared" si="164"/>
         <v>0.64627363737486099</v>
       </c>
       <c r="T41" s="7">
-        <f t="shared" si="163"/>
+        <f t="shared" si="164"/>
         <v>0.7005256533649219</v>
       </c>
       <c r="U41" s="7">
-        <f t="shared" si="163"/>
+        <f t="shared" si="164"/>
         <v>0.73951434878587197</v>
       </c>
       <c r="V41" s="7">
-        <f t="shared" ref="V41:X41" si="164">V26/V24</f>
+        <f t="shared" ref="V41:X41" si="165">V26/V24</f>
         <v>0.75967063294575399</v>
       </c>
       <c r="W41" s="7">
-        <f t="shared" si="164"/>
+        <f t="shared" si="165"/>
         <v>0.78352019659038552</v>
       </c>
       <c r="X41" s="7">
-        <f t="shared" si="164"/>
+        <f t="shared" si="165"/>
         <v>0.75146471371504664</v>
       </c>
       <c r="Y41" s="7">
-        <f t="shared" ref="Y41:AD41" si="165">Y26/Y24</f>
+        <f t="shared" ref="Y41:AD41" si="166">Y26/Y24</f>
         <v>0.74556752750698363</v>
       </c>
       <c r="Z41" s="7">
-        <f t="shared" si="165"/>
+        <f t="shared" si="166"/>
         <v>0.73028908494571709</v>
       </c>
       <c r="AA41" s="7">
-        <f t="shared" si="165"/>
+        <f t="shared" si="166"/>
         <v>0.60523807362353044</v>
       </c>
       <c r="AB41" s="7">
-        <f t="shared" si="165"/>
+        <f t="shared" si="166"/>
         <v>0.72423678411740799</v>
       </c>
       <c r="AC41" s="7">
-        <f t="shared" si="165"/>
+        <f t="shared" si="166"/>
         <v>0.7341157071185489</v>
       </c>
       <c r="AD41" s="7">
-        <f t="shared" si="165"/>
-        <v>0.76</v>
+        <f t="shared" si="166"/>
+        <v>0.74986784140969165</v>
       </c>
       <c r="AE41" s="7"/>
       <c r="AF41" s="7"/>
@@ -8941,147 +9025,147 @@
       <c r="AK41" s="7"/>
       <c r="AL41" s="7"/>
       <c r="AM41" s="7">
-        <f t="shared" ref="AM41:AP41" si="166">AM26/AM24</f>
+        <f t="shared" ref="AM41:AP41" si="167">AM26/AM24</f>
         <v>0</v>
       </c>
       <c r="AN41" s="7">
-        <f t="shared" si="166"/>
+        <f t="shared" si="167"/>
         <v>0</v>
       </c>
       <c r="AO41" s="7">
-        <f t="shared" si="166"/>
+        <f t="shared" si="167"/>
         <v>0</v>
       </c>
       <c r="AP41" s="7">
-        <f t="shared" si="166"/>
+        <f t="shared" si="167"/>
         <v>0</v>
       </c>
       <c r="AQ41" s="7">
-        <f t="shared" ref="AQ41" si="167">AQ26/AQ24</f>
+        <f t="shared" ref="AQ41" si="168">AQ26/AQ24</f>
         <v>0.62125205270957662</v>
       </c>
       <c r="AR41" s="7">
-        <f t="shared" ref="AR41:AS41" si="168">AR26/AR24</f>
+        <f t="shared" ref="AR41:AS41" si="169">AR26/AR24</f>
         <v>0.62886935848892367</v>
       </c>
       <c r="AS41" s="7">
-        <f t="shared" si="168"/>
+        <f t="shared" si="169"/>
         <v>0.6208477580029077</v>
       </c>
       <c r="AT41" s="7">
-        <f t="shared" ref="AT41:BA41" si="169">AT26/AT24</f>
+        <f t="shared" ref="AT41:BA41" si="170">AT26/AT24</f>
         <v>0.30489246362952205</v>
       </c>
       <c r="AU41" s="7">
-        <f t="shared" si="169"/>
+        <f t="shared" si="170"/>
         <v>0.29012285066197824</v>
       </c>
       <c r="AV41" s="7">
-        <f t="shared" si="169"/>
+        <f t="shared" si="170"/>
         <v>0.3231220581950644</v>
       </c>
       <c r="AW41" s="7">
-        <f t="shared" si="169"/>
+        <f t="shared" si="170"/>
         <v>0.38306098404377342</v>
       </c>
       <c r="AX41" s="7">
-        <f t="shared" si="169"/>
+        <f t="shared" si="170"/>
         <v>0.42376866830402143</v>
       </c>
       <c r="AY41" s="7">
-        <f t="shared" si="169"/>
+        <f t="shared" si="170"/>
         <v>0.45616004451103742</v>
       </c>
       <c r="AZ41" s="7">
-        <f t="shared" si="169"/>
+        <f t="shared" si="170"/>
         <v>0.34286637785672341</v>
       </c>
       <c r="BA41" s="7">
-        <f t="shared" si="169"/>
+        <f t="shared" si="170"/>
         <v>0.35380804432359475</v>
       </c>
       <c r="BB41" s="7">
-        <f t="shared" ref="BB41" si="170">BB26/BB24</f>
+        <f t="shared" ref="BB41" si="171">BB26/BB24</f>
         <v>0.39767629636591112</v>
       </c>
       <c r="BC41" s="7">
-        <f t="shared" ref="BC41:BD41" si="171">BC26/BC24</f>
+        <f t="shared" ref="BC41:BD41" si="172">BC26/BC24</f>
         <v>0.51439544964519135</v>
       </c>
       <c r="BD41" s="7">
-        <f t="shared" si="171"/>
+        <f t="shared" si="172"/>
         <v>0.52015427464260089</v>
       </c>
       <c r="BE41" s="7">
-        <f t="shared" ref="BE41:BV41" si="172">BE26/BE24</f>
+        <f t="shared" ref="BE41:BV41" si="173">BE26/BE24</f>
         <v>0.54915254237288136</v>
       </c>
       <c r="BF41" s="7">
-        <f t="shared" si="172"/>
+        <f t="shared" si="173"/>
         <v>0.55510465612985904</v>
       </c>
       <c r="BG41" s="7">
-        <f t="shared" si="172"/>
+        <f t="shared" si="173"/>
         <v>0.56107784431137719</v>
       </c>
       <c r="BH41" s="7">
-        <f t="shared" si="172"/>
+        <f t="shared" si="173"/>
         <v>0.58798842257597683</v>
       </c>
       <c r="BI41" s="7">
-        <f t="shared" si="172"/>
+        <f t="shared" si="173"/>
         <v>0.59934115709285563</v>
       </c>
       <c r="BJ41" s="7">
-        <f t="shared" si="172"/>
+        <f t="shared" si="173"/>
         <v>0.61206896551724133</v>
       </c>
       <c r="BK41" s="7">
-        <f t="shared" si="172"/>
+        <f t="shared" si="173"/>
         <v>0.61989375343469499</v>
       </c>
       <c r="BL41" s="7">
-        <f t="shared" si="172"/>
+        <f t="shared" si="173"/>
         <v>0.62344827586206897</v>
       </c>
       <c r="BM41" s="7">
-        <f t="shared" si="172"/>
+        <f t="shared" si="173"/>
         <v>0.64924014416824583</v>
       </c>
       <c r="BN41" s="7">
-        <f t="shared" si="172"/>
+        <f t="shared" si="173"/>
         <v>0.56933684249545913</v>
       </c>
       <c r="BO41" s="7">
-        <f t="shared" si="172"/>
+        <f t="shared" si="173"/>
         <v>0.72717573290436954</v>
       </c>
       <c r="BP41" s="7">
-        <f t="shared" si="172"/>
+        <f t="shared" si="173"/>
         <v>0.74989463359310937</v>
       </c>
       <c r="BQ41" s="7">
-        <f t="shared" si="172"/>
-        <v>0.71384042498992639</v>
+        <f t="shared" si="173"/>
+        <v>0.71064466377349922</v>
       </c>
       <c r="BR41" s="7">
-        <f t="shared" si="172"/>
+        <f t="shared" si="173"/>
         <v>0.75</v>
       </c>
       <c r="BS41" s="7">
-        <f t="shared" si="172"/>
+        <f t="shared" si="173"/>
         <v>0.78</v>
       </c>
       <c r="BT41" s="7">
-        <f t="shared" si="172"/>
+        <f t="shared" si="173"/>
         <v>0.78</v>
       </c>
       <c r="BU41" s="7">
-        <f t="shared" si="172"/>
+        <f t="shared" si="173"/>
         <v>0.78</v>
       </c>
       <c r="BV41" s="7">
-        <f t="shared" si="172"/>
+        <f t="shared" si="173"/>
         <v>0.78</v>
       </c>
     </row>
@@ -9090,83 +9174,83 @@
         <v>24</v>
       </c>
       <c r="C42" s="7">
-        <f t="shared" ref="C42:F42" si="173">C22/C24</f>
+        <f t="shared" ref="C42:F42" si="174">C22/C24</f>
         <v>0.28558558558558561</v>
       </c>
       <c r="D42" s="7">
-        <f t="shared" si="173"/>
+        <f t="shared" si="174"/>
         <v>0.25397440868553706</v>
       </c>
       <c r="E42" s="7">
-        <f t="shared" si="173"/>
+        <f t="shared" si="174"/>
         <v>0.24087591240875914</v>
       </c>
       <c r="F42" s="7">
-        <f t="shared" si="173"/>
+        <f t="shared" si="174"/>
         <v>0.3117552334943639</v>
       </c>
       <c r="G42" s="7">
-        <f t="shared" ref="G42:I42" si="174">G22/G24</f>
+        <f t="shared" ref="G42:I42" si="175">G22/G24</f>
         <v>0.37045454545454548</v>
       </c>
       <c r="H42" s="7">
-        <f t="shared" si="174"/>
+        <f t="shared" si="175"/>
         <v>0.45318158303155714</v>
       </c>
       <c r="I42" s="7">
-        <f t="shared" si="174"/>
+        <f t="shared" si="175"/>
         <v>0.40203131612357174</v>
       </c>
       <c r="J42" s="7">
-        <f t="shared" ref="J42:O42" si="175">J22/J24</f>
+        <f t="shared" ref="J42:O42" si="176">J22/J24</f>
         <v>0.38037177693383972</v>
       </c>
       <c r="K42" s="7">
-        <f t="shared" si="175"/>
+        <f t="shared" si="176"/>
         <v>0.36212683271506801</v>
       </c>
       <c r="L42" s="7">
-        <f t="shared" si="175"/>
+        <f t="shared" si="176"/>
         <v>0.36360842169970803</v>
       </c>
       <c r="M42" s="7">
-        <f t="shared" si="175"/>
+        <f t="shared" si="176"/>
         <v>0.41334647332113189</v>
       </c>
       <c r="N42" s="7">
-        <f t="shared" si="175"/>
+        <f t="shared" si="176"/>
         <v>0.42653408347507521</v>
       </c>
       <c r="O42" s="7">
-        <f t="shared" si="175"/>
+        <f t="shared" si="176"/>
         <v>0.45246138996138996</v>
       </c>
       <c r="P42" s="7">
-        <f t="shared" ref="P42:U42" si="176">P22/P24</f>
+        <f t="shared" ref="P42:U42" si="177">P22/P24</f>
         <v>0.56772076372315039</v>
       </c>
       <c r="Q42" s="7">
-        <f t="shared" si="176"/>
+        <f t="shared" si="177"/>
         <v>0.64626538526386779</v>
       </c>
       <c r="R42" s="7">
-        <f t="shared" si="176"/>
+        <f t="shared" si="177"/>
         <v>0.59824822343414308</v>
       </c>
       <c r="S42" s="7">
-        <f t="shared" si="176"/>
+        <f t="shared" si="177"/>
         <v>0.59566184649610676</v>
       </c>
       <c r="T42" s="7">
-        <f t="shared" si="176"/>
+        <f t="shared" si="177"/>
         <v>0.76427037832235134</v>
       </c>
       <c r="U42" s="7">
-        <f t="shared" si="176"/>
+        <f t="shared" si="177"/>
         <v>0.80099337748344368</v>
       </c>
       <c r="V42" s="7">
-        <f t="shared" ref="V42:AD42" si="177">V22/V24</f>
+        <f t="shared" ref="V42:AD42" si="178">V22/V24</f>
         <v>0.8326471519703208</v>
       </c>
       <c r="W42" s="7">
@@ -9174,31 +9258,31 @@
         <v>0.86634157579480875</v>
       </c>
       <c r="X42" s="7">
-        <f t="shared" si="177"/>
+        <f t="shared" si="178"/>
         <v>0.87456724367509986</v>
       </c>
       <c r="Y42" s="7">
-        <f t="shared" si="177"/>
+        <f t="shared" si="178"/>
         <v>0.87711646998460746</v>
       </c>
       <c r="Z42" s="7">
-        <f t="shared" si="177"/>
+        <f t="shared" si="178"/>
         <v>0.90462993567415018</v>
       </c>
       <c r="AA42" s="7">
-        <f t="shared" si="177"/>
+        <f t="shared" si="178"/>
         <v>0.88765829966864873</v>
       </c>
       <c r="AB42" s="7">
-        <f t="shared" si="177"/>
+        <f t="shared" si="178"/>
         <v>0.87919046702180004</v>
       </c>
       <c r="AC42" s="7">
-        <f t="shared" si="177"/>
+        <f t="shared" si="178"/>
         <v>0.89815107181700171</v>
       </c>
       <c r="AD42" s="7">
-        <f t="shared" si="177"/>
+        <f t="shared" si="178"/>
         <v>0.86207048458149782</v>
       </c>
       <c r="AE42" s="7"/>
@@ -9255,75 +9339,81 @@
         <v>5704</v>
       </c>
       <c r="L44" s="2">
-        <f t="shared" ref="L44:M44" si="178">+L45-L58</f>
+        <f t="shared" ref="L44:M44" si="179">+L45-L58</f>
         <v>7711</v>
       </c>
       <c r="M44" s="2">
-        <f t="shared" si="178"/>
+        <f t="shared" si="179"/>
         <v>8354</v>
       </c>
       <c r="N44" s="2">
-        <f t="shared" ref="N44:V44" si="179">+N45-N58</f>
+        <f t="shared" ref="N44:V44" si="180">+N45-N58</f>
         <v>10262</v>
       </c>
       <c r="O44" s="2">
-        <f t="shared" si="179"/>
+        <f t="shared" si="180"/>
         <v>9391</v>
       </c>
       <c r="P44" s="2">
-        <f t="shared" si="179"/>
+        <f t="shared" si="180"/>
         <v>6088</v>
       </c>
       <c r="Q44" s="2">
-        <f t="shared" si="179"/>
+        <f t="shared" si="180"/>
         <v>2193</v>
       </c>
       <c r="R44" s="2">
-        <f t="shared" si="179"/>
+        <f t="shared" si="180"/>
         <v>2343</v>
       </c>
       <c r="S44" s="2">
-        <f t="shared" si="179"/>
+        <f t="shared" si="180"/>
         <v>4366</v>
       </c>
       <c r="T44" s="2">
-        <f t="shared" si="179"/>
+        <f t="shared" si="180"/>
         <v>6318</v>
       </c>
       <c r="U44" s="2">
-        <f t="shared" si="179"/>
+        <f t="shared" si="180"/>
         <v>8575</v>
       </c>
       <c r="V44" s="2">
-        <f t="shared" si="179"/>
+        <f t="shared" si="180"/>
         <v>16275</v>
       </c>
       <c r="W44" s="2">
-        <f t="shared" ref="W44:AB44" si="180">+W45-W58</f>
+        <f t="shared" ref="W44:AD44" si="181">+W45-W58</f>
         <v>21728</v>
       </c>
       <c r="X44" s="2">
-        <f t="shared" si="180"/>
+        <f t="shared" si="181"/>
         <v>26339</v>
       </c>
       <c r="Y44" s="2">
-        <f t="shared" si="180"/>
+        <f t="shared" si="181"/>
         <v>30025</v>
       </c>
       <c r="Z44" s="2">
-        <f t="shared" si="180"/>
+        <f t="shared" si="181"/>
         <v>34747</v>
       </c>
       <c r="AA44" s="2">
-        <f t="shared" si="180"/>
+        <f t="shared" si="181"/>
         <v>45227</v>
       </c>
       <c r="AB44" s="2">
-        <f t="shared" si="180"/>
+        <f t="shared" si="181"/>
         <v>48325</v>
       </c>
-      <c r="AC44" s="2"/>
-      <c r="AD44" s="2"/>
+      <c r="AC44" s="2">
+        <f t="shared" si="181"/>
+        <v>52141</v>
+      </c>
+      <c r="AD44" s="2">
+        <f t="shared" si="181"/>
+        <v>76339</v>
+      </c>
       <c r="AE44" s="2"/>
       <c r="AF44" s="2"/>
       <c r="AG44" s="2"/>
@@ -9473,6 +9563,14 @@
         <f>11639+45152</f>
         <v>56791</v>
       </c>
+      <c r="AC45" s="2">
+        <f>11486+49122</f>
+        <v>60608</v>
+      </c>
+      <c r="AD45" s="2">
+        <f>51951+10605+22251</f>
+        <v>84807</v>
+      </c>
       <c r="BL45" s="2">
         <f>+J45</f>
         <v>11561</v>
@@ -9574,24 +9672,30 @@
       <c r="AB46" s="2">
         <v>27808</v>
       </c>
+      <c r="AC46" s="2">
+        <v>33391</v>
+      </c>
+      <c r="AD46" s="2">
+        <v>38466</v>
+      </c>
       <c r="BL46" s="2">
-        <f t="shared" ref="BL46:BL53" si="181">+J46</f>
+        <f t="shared" ref="BL46:BL53" si="182">+J46</f>
         <v>2429</v>
       </c>
       <c r="BM46" s="2">
-        <f t="shared" ref="BM46:BM53" si="182">+N46</f>
+        <f t="shared" ref="BM46:BM53" si="183">+N46</f>
         <v>4650</v>
       </c>
       <c r="BN46" s="2">
-        <f t="shared" ref="BN46:BN53" si="183">+R46</f>
+        <f t="shared" ref="BN46:BN53" si="184">+R46</f>
         <v>3827</v>
       </c>
       <c r="BO46" s="2">
-        <f t="shared" ref="BO46:BO53" si="184">+V46</f>
+        <f t="shared" ref="BO46:BO53" si="185">+V46</f>
         <v>9999</v>
       </c>
       <c r="BP46" s="2">
-        <f t="shared" ref="BP46:BP53" si="185">+Z46</f>
+        <f t="shared" ref="BP46:BP53" si="186">+Z46</f>
         <v>23065</v>
       </c>
       <c r="BX46" t="s">
@@ -9599,7 +9703,7 @@
       </c>
       <c r="BY46" s="2">
         <f>NPV(BY45,BQ34:FN34)+Main!K5-Main!K6</f>
-        <v>10055436.442725606</v>
+        <v>10027994.742872769</v>
       </c>
     </row>
     <row r="47" spans="2:170" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9676,24 +9780,30 @@
       <c r="AB47" s="2">
         <v>14962</v>
       </c>
+      <c r="AC47" s="2">
+        <v>19784</v>
+      </c>
+      <c r="AD47" s="2">
+        <v>21403</v>
+      </c>
       <c r="BL47" s="2">
-        <f t="shared" si="181"/>
+        <f t="shared" si="182"/>
         <v>1826</v>
       </c>
       <c r="BM47" s="2">
-        <f t="shared" si="182"/>
+        <f t="shared" si="183"/>
         <v>2605</v>
       </c>
       <c r="BN47" s="2">
-        <f t="shared" si="183"/>
+        <f t="shared" si="184"/>
         <v>5159</v>
       </c>
       <c r="BO47" s="2">
-        <f t="shared" si="184"/>
+        <f t="shared" si="185"/>
         <v>5282</v>
       </c>
       <c r="BP47" s="2">
-        <f t="shared" si="185"/>
+        <f t="shared" si="186"/>
         <v>10080</v>
       </c>
       <c r="BX47" t="s">
@@ -9701,7 +9811,7 @@
       </c>
       <c r="BY47" s="15">
         <f>BY46/Main!K3</f>
-        <v>413.80396883644471</v>
+        <v>412.67468077665717</v>
       </c>
     </row>
     <row r="48" spans="2:170" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9778,24 +9888,30 @@
       <c r="AB48" s="2">
         <v>2658</v>
       </c>
+      <c r="AC48" s="2">
+        <v>2709</v>
+      </c>
+      <c r="AD48" s="2">
+        <v>3180</v>
+      </c>
       <c r="BL48" s="2">
-        <f t="shared" si="181"/>
+        <f t="shared" si="182"/>
         <v>239</v>
       </c>
       <c r="BM48" s="2">
-        <f t="shared" si="182"/>
+        <f t="shared" si="183"/>
         <v>366</v>
       </c>
       <c r="BN48" s="2">
-        <f t="shared" si="183"/>
+        <f t="shared" si="184"/>
         <v>791</v>
       </c>
       <c r="BO48" s="2">
-        <f t="shared" si="184"/>
+        <f t="shared" si="185"/>
         <v>3080</v>
       </c>
       <c r="BP48" s="2">
-        <f t="shared" si="185"/>
+        <f t="shared" si="186"/>
         <v>3771</v>
       </c>
     </row>
@@ -9873,24 +9989,30 @@
       <c r="AB49" s="2">
         <v>9141</v>
       </c>
+      <c r="AC49" s="2">
+        <v>9780</v>
+      </c>
+      <c r="AD49" s="2">
+        <v>10383</v>
+      </c>
       <c r="BL49" s="2">
-        <f t="shared" si="181"/>
+        <f t="shared" si="182"/>
         <v>2149</v>
       </c>
       <c r="BM49" s="2">
-        <f t="shared" si="182"/>
+        <f t="shared" si="183"/>
         <v>2778</v>
       </c>
       <c r="BN49" s="2">
-        <f t="shared" si="183"/>
+        <f t="shared" si="184"/>
         <v>3807</v>
       </c>
       <c r="BO49" s="2">
-        <f t="shared" si="184"/>
+        <f t="shared" si="185"/>
         <v>3914</v>
       </c>
       <c r="BP49" s="2">
-        <f t="shared" si="185"/>
+        <f t="shared" si="186"/>
         <v>6283</v>
       </c>
     </row>
@@ -9968,24 +10090,30 @@
       <c r="AB50" s="2">
         <v>2084</v>
       </c>
+      <c r="AC50" s="2">
+        <v>2281</v>
+      </c>
+      <c r="AD50" s="2">
+        <v>2867</v>
+      </c>
       <c r="BL50" s="2">
-        <f t="shared" si="181"/>
+        <f t="shared" si="182"/>
         <v>707</v>
       </c>
       <c r="BM50" s="2">
-        <f t="shared" si="182"/>
+        <f t="shared" si="183"/>
         <v>829</v>
       </c>
       <c r="BN50" s="2">
-        <f t="shared" si="183"/>
+        <f t="shared" si="184"/>
         <v>1038</v>
       </c>
       <c r="BO50" s="2">
-        <f t="shared" si="184"/>
+        <f t="shared" si="185"/>
         <v>1346</v>
       </c>
       <c r="BP50" s="2">
-        <f t="shared" si="185"/>
+        <f t="shared" si="186"/>
         <v>1793</v>
       </c>
     </row>
@@ -10085,24 +10213,32 @@
         <f>5755+755</f>
         <v>6510</v>
       </c>
+      <c r="AC51" s="2">
+        <f>6261+936</f>
+        <v>7197</v>
+      </c>
+      <c r="AD51" s="2">
+        <f>20832+3306</f>
+        <v>24138</v>
+      </c>
       <c r="BL51" s="2">
-        <f t="shared" si="181"/>
+        <f t="shared" si="182"/>
         <v>6930</v>
       </c>
       <c r="BM51" s="2">
-        <f t="shared" si="182"/>
+        <f t="shared" si="183"/>
         <v>6688</v>
       </c>
       <c r="BN51" s="2">
-        <f t="shared" si="183"/>
+        <f t="shared" si="184"/>
         <v>6048</v>
       </c>
       <c r="BO51" s="2">
-        <f t="shared" si="184"/>
+        <f t="shared" si="185"/>
         <v>5542</v>
       </c>
       <c r="BP51" s="2">
-        <f t="shared" si="185"/>
+        <f t="shared" si="186"/>
         <v>5995</v>
       </c>
     </row>
@@ -10180,24 +10316,30 @@
       <c r="AB52" s="2">
         <v>13570</v>
       </c>
+      <c r="AC52" s="2">
+        <v>13674</v>
+      </c>
+      <c r="AD52" s="2">
+        <v>13258</v>
+      </c>
       <c r="BL52" s="2">
-        <f t="shared" si="181"/>
+        <f t="shared" si="182"/>
         <v>806</v>
       </c>
       <c r="BM52" s="2">
-        <f t="shared" si="182"/>
+        <f t="shared" si="183"/>
         <v>1222</v>
       </c>
       <c r="BN52" s="2">
-        <f t="shared" si="183"/>
+        <f t="shared" si="184"/>
         <v>3396</v>
       </c>
       <c r="BO52" s="2">
-        <f t="shared" si="184"/>
+        <f t="shared" si="185"/>
         <v>6081</v>
       </c>
       <c r="BP52" s="2">
-        <f t="shared" si="185"/>
+        <f t="shared" si="186"/>
         <v>10979</v>
       </c>
     </row>
@@ -10275,24 +10417,30 @@
       <c r="AB53" s="2">
         <v>7216</v>
       </c>
+      <c r="AC53" s="2">
+        <v>11724</v>
+      </c>
+      <c r="AD53" s="2">
+        <v>8301</v>
+      </c>
       <c r="BL53" s="2">
-        <f t="shared" si="181"/>
+        <f t="shared" si="182"/>
         <v>2144</v>
       </c>
       <c r="BM53" s="2">
-        <f t="shared" si="182"/>
+        <f t="shared" si="183"/>
         <v>3841</v>
       </c>
       <c r="BN53" s="2">
-        <f t="shared" si="183"/>
+        <f t="shared" si="184"/>
         <v>3820</v>
       </c>
       <c r="BO53" s="2">
-        <f t="shared" si="184"/>
+        <f t="shared" si="185"/>
         <v>4500</v>
       </c>
       <c r="BP53" s="2">
-        <f t="shared" si="185"/>
+        <f t="shared" si="186"/>
         <v>6425</v>
       </c>
     </row>
@@ -10304,92 +10452,100 @@
       <c r="D54" s="5"/>
       <c r="E54" s="5"/>
       <c r="G54" s="2">
-        <f t="shared" ref="G54:M54" si="186">SUM(G45:G53)</f>
+        <f t="shared" ref="G54:M54" si="187">SUM(G45:G53)</f>
         <v>23254</v>
       </c>
       <c r="H54" s="2">
-        <f t="shared" si="186"/>
+        <f t="shared" si="187"/>
         <v>25180</v>
       </c>
       <c r="I54" s="2">
-        <f t="shared" si="186"/>
+        <f t="shared" si="187"/>
         <v>26881</v>
       </c>
       <c r="J54" s="2">
-        <f t="shared" si="186"/>
+        <f t="shared" si="187"/>
         <v>28791</v>
       </c>
       <c r="K54" s="2">
-        <f t="shared" si="186"/>
+        <f t="shared" si="187"/>
         <v>30796</v>
       </c>
       <c r="L54" s="2">
-        <f t="shared" si="186"/>
+        <f t="shared" si="187"/>
         <v>38650</v>
       </c>
       <c r="M54" s="2">
-        <f t="shared" si="186"/>
+        <f t="shared" si="187"/>
         <v>40632</v>
       </c>
       <c r="N54" s="2">
-        <f t="shared" ref="N54:Q54" si="187">SUM(N45:N53)</f>
+        <f t="shared" ref="N54:Q54" si="188">SUM(N45:N53)</f>
         <v>44187</v>
       </c>
       <c r="O54" s="2">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>45212</v>
       </c>
       <c r="P54" s="2">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>43476</v>
       </c>
       <c r="Q54" s="2">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>40488</v>
       </c>
       <c r="R54" s="2">
-        <f t="shared" ref="R54:S54" si="188">SUM(R45:R53)</f>
+        <f t="shared" ref="R54:S54" si="189">SUM(R45:R53)</f>
         <v>41182</v>
       </c>
       <c r="S54" s="2">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>44460</v>
       </c>
       <c r="T54" s="2">
-        <f t="shared" ref="T54:AB54" si="189">SUM(T45:T53)</f>
+        <f t="shared" ref="T54:AD54" si="190">SUM(T45:T53)</f>
         <v>49555</v>
       </c>
       <c r="U54" s="2">
-        <f t="shared" si="189"/>
+        <f t="shared" si="190"/>
         <v>54148</v>
       </c>
       <c r="V54" s="2">
-        <f t="shared" si="189"/>
+        <f t="shared" si="190"/>
         <v>65728</v>
       </c>
       <c r="W54" s="2">
-        <f t="shared" si="189"/>
+        <f t="shared" si="190"/>
         <v>77072</v>
       </c>
       <c r="X54" s="2">
-        <f t="shared" si="189"/>
+        <f t="shared" si="190"/>
         <v>85227</v>
       </c>
       <c r="Y54" s="2">
-        <f t="shared" si="189"/>
+        <f t="shared" si="190"/>
         <v>96013</v>
       </c>
       <c r="Z54" s="2">
-        <f t="shared" si="189"/>
+        <f t="shared" si="190"/>
         <v>111601</v>
       </c>
       <c r="AA54" s="2">
-        <f t="shared" si="189"/>
+        <f t="shared" si="190"/>
         <v>125254</v>
       </c>
       <c r="AB54" s="2">
-        <f t="shared" si="189"/>
+        <f t="shared" si="190"/>
         <v>140740</v>
+      </c>
+      <c r="AC54" s="2">
+        <f t="shared" si="190"/>
+        <v>161148</v>
+      </c>
+      <c r="AD54" s="2">
+        <f t="shared" si="190"/>
+        <v>206803</v>
       </c>
       <c r="BL54" s="2">
         <f>SUM(BL45:BL53)</f>
@@ -10504,24 +10660,30 @@
       <c r="AB56" s="2">
         <v>9064</v>
       </c>
+      <c r="AC56" s="2">
+        <v>8624</v>
+      </c>
+      <c r="AD56" s="2">
+        <v>9812</v>
+      </c>
       <c r="BL56" s="2">
-        <f t="shared" ref="BL56:BL61" si="190">+J56</f>
+        <f t="shared" ref="BL56:BL61" si="191">+J56</f>
         <v>1201</v>
       </c>
       <c r="BM56" s="2">
-        <f t="shared" ref="BM56:BM61" si="191">+N56</f>
+        <f t="shared" ref="BM56:BM61" si="192">+N56</f>
         <v>1783</v>
       </c>
       <c r="BN56" s="2">
-        <f t="shared" ref="BN56:BN61" si="192">+R56</f>
+        <f t="shared" ref="BN56:BN61" si="193">+R56</f>
         <v>1193</v>
       </c>
       <c r="BO56" s="2">
-        <f t="shared" ref="BO56:BO61" si="193">+V56</f>
+        <f t="shared" ref="BO56:BO61" si="194">+V56</f>
         <v>2699</v>
       </c>
       <c r="BP56" s="2">
-        <f t="shared" ref="BP56:BP61" si="194">+Z56</f>
+        <f t="shared" ref="BP56:BP61" si="195">+Z56</f>
         <v>6310</v>
       </c>
     </row>
@@ -10599,24 +10761,30 @@
       <c r="AB57" s="2">
         <v>15193</v>
       </c>
+      <c r="AC57" s="2">
+        <v>16452</v>
+      </c>
+      <c r="AD57" s="2">
+        <v>21352</v>
+      </c>
       <c r="BL57" s="2">
-        <f t="shared" si="190"/>
+        <f t="shared" si="191"/>
         <v>1725</v>
       </c>
       <c r="BM57" s="2">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>2552</v>
       </c>
       <c r="BN57" s="2">
-        <f t="shared" si="192"/>
+        <f t="shared" si="193"/>
         <v>4120</v>
       </c>
       <c r="BO57" s="2">
-        <f t="shared" si="193"/>
+        <f t="shared" si="194"/>
         <v>6682</v>
       </c>
       <c r="BP57" s="2">
-        <f t="shared" si="194"/>
+        <f t="shared" si="195"/>
         <v>11737</v>
       </c>
     </row>
@@ -10706,24 +10874,32 @@
       <c r="AB58" s="2">
         <v>8466</v>
       </c>
+      <c r="AC58" s="2">
+        <f>999+7468</f>
+        <v>8467</v>
+      </c>
+      <c r="AD58" s="2">
+        <f>999+7469</f>
+        <v>8468</v>
+      </c>
       <c r="BL58" s="2">
-        <f t="shared" si="190"/>
+        <f t="shared" si="191"/>
         <v>6963</v>
       </c>
       <c r="BM58" s="2">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>10946</v>
       </c>
       <c r="BN58" s="2">
-        <f t="shared" si="192"/>
+        <f t="shared" si="193"/>
         <v>10953</v>
       </c>
       <c r="BO58" s="2">
-        <f t="shared" si="193"/>
+        <f t="shared" si="194"/>
         <v>9709</v>
       </c>
       <c r="BP58" s="2">
-        <f t="shared" si="194"/>
+        <f t="shared" si="195"/>
         <v>8463</v>
       </c>
     </row>
@@ -10802,24 +10978,30 @@
       <c r="AB59" s="2">
         <v>1831</v>
       </c>
+      <c r="AC59" s="2">
+        <v>2014</v>
+      </c>
+      <c r="AD59" s="2">
+        <v>2572</v>
+      </c>
       <c r="BL59" s="2">
-        <f t="shared" si="190"/>
+        <f t="shared" si="191"/>
         <v>634</v>
       </c>
       <c r="BM59" s="2">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>741</v>
       </c>
       <c r="BN59" s="2">
-        <f t="shared" si="192"/>
+        <f t="shared" si="193"/>
         <v>902</v>
       </c>
       <c r="BO59" s="2">
-        <f t="shared" si="193"/>
+        <f t="shared" si="194"/>
         <v>1119</v>
       </c>
       <c r="BP59" s="2">
-        <f t="shared" si="194"/>
+        <f t="shared" si="195"/>
         <v>1519</v>
       </c>
     </row>
@@ -10897,24 +11079,30 @@
       <c r="AB60" s="2">
         <v>6055</v>
       </c>
+      <c r="AC60" s="2">
+        <v>6694</v>
+      </c>
+      <c r="AD60" s="2">
+        <v>7306</v>
+      </c>
       <c r="BL60" s="2">
-        <f t="shared" si="190"/>
+        <f t="shared" si="191"/>
         <v>1375</v>
       </c>
       <c r="BM60" s="2">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>1553</v>
       </c>
       <c r="BN60" s="2">
-        <f t="shared" si="192"/>
+        <f t="shared" si="193"/>
         <v>1913</v>
       </c>
       <c r="BO60" s="2">
-        <f t="shared" si="193"/>
+        <f t="shared" si="194"/>
         <v>2541</v>
       </c>
       <c r="BP60" s="2">
-        <f t="shared" si="194"/>
+        <f t="shared" si="195"/>
         <v>4245</v>
       </c>
     </row>
@@ -10992,24 +11180,30 @@
       <c r="AB61" s="2">
         <v>100131</v>
       </c>
+      <c r="AC61" s="2">
+        <v>118897</v>
+      </c>
+      <c r="AD61" s="2">
+        <v>157293</v>
+      </c>
       <c r="BL61" s="2">
-        <f t="shared" si="190"/>
+        <f t="shared" si="191"/>
         <v>16893</v>
       </c>
       <c r="BM61" s="2">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>26612</v>
       </c>
       <c r="BN61" s="2">
-        <f t="shared" si="192"/>
+        <f t="shared" si="193"/>
         <v>22101</v>
       </c>
       <c r="BO61" s="2">
-        <f t="shared" si="193"/>
+        <f t="shared" si="194"/>
         <v>42978</v>
       </c>
       <c r="BP61" s="2">
-        <f t="shared" si="194"/>
+        <f t="shared" si="195"/>
         <v>79327</v>
       </c>
     </row>
@@ -11021,96 +11215,104 @@
       <c r="D62" s="5"/>
       <c r="E62" s="5"/>
       <c r="F62" s="2">
-        <f t="shared" ref="F62" si="195">SUM(F56:F61)</f>
+        <f t="shared" ref="F62" si="196">SUM(F56:F61)</f>
         <v>0</v>
       </c>
       <c r="G62" s="2">
-        <f t="shared" ref="G62:M62" si="196">SUM(G56:G61)</f>
+        <f t="shared" ref="G62:M62" si="197">SUM(G56:G61)</f>
         <v>23254</v>
       </c>
       <c r="H62" s="2">
-        <f t="shared" si="196"/>
+        <f t="shared" si="197"/>
         <v>25180</v>
       </c>
       <c r="I62" s="2">
-        <f t="shared" si="196"/>
+        <f t="shared" si="197"/>
         <v>26881</v>
       </c>
       <c r="J62" s="2">
-        <f t="shared" si="196"/>
+        <f t="shared" si="197"/>
         <v>28791</v>
       </c>
       <c r="K62" s="2">
-        <f t="shared" si="196"/>
+        <f t="shared" si="197"/>
         <v>30796</v>
       </c>
       <c r="L62" s="2">
-        <f t="shared" si="196"/>
+        <f t="shared" si="197"/>
         <v>38650</v>
       </c>
       <c r="M62" s="2">
-        <f t="shared" si="196"/>
+        <f t="shared" si="197"/>
         <v>40632</v>
       </c>
       <c r="N62" s="2">
-        <f t="shared" ref="N62:Q62" si="197">SUM(N56:N61)</f>
+        <f t="shared" ref="N62:Q62" si="198">SUM(N56:N61)</f>
         <v>44187</v>
       </c>
       <c r="O62" s="2">
-        <f t="shared" si="197"/>
+        <f t="shared" si="198"/>
         <v>45212</v>
       </c>
       <c r="P62" s="2">
-        <f t="shared" si="197"/>
+        <f t="shared" si="198"/>
         <v>43476</v>
       </c>
       <c r="Q62" s="2">
-        <f t="shared" si="197"/>
+        <f t="shared" si="198"/>
         <v>40488</v>
       </c>
       <c r="R62" s="2">
-        <f t="shared" ref="R62:S62" si="198">SUM(R56:R61)</f>
+        <f t="shared" ref="R62:S62" si="199">SUM(R56:R61)</f>
         <v>41182</v>
       </c>
       <c r="S62" s="2">
-        <f t="shared" si="198"/>
+        <f t="shared" si="199"/>
         <v>44460</v>
       </c>
       <c r="T62" s="2">
-        <f t="shared" ref="T62:AB62" si="199">SUM(T56:T61)</f>
+        <f t="shared" ref="T62:AD62" si="200">SUM(T56:T61)</f>
         <v>49555</v>
       </c>
       <c r="U62" s="2">
-        <f t="shared" si="199"/>
+        <f t="shared" si="200"/>
         <v>54148</v>
       </c>
       <c r="V62" s="2">
-        <f t="shared" si="199"/>
+        <f t="shared" si="200"/>
         <v>65728</v>
       </c>
       <c r="W62" s="2">
-        <f t="shared" si="199"/>
+        <f t="shared" si="200"/>
         <v>77072</v>
       </c>
       <c r="X62" s="2">
-        <f t="shared" si="199"/>
+        <f t="shared" si="200"/>
         <v>85227</v>
       </c>
       <c r="Y62" s="2">
-        <f t="shared" si="199"/>
+        <f t="shared" si="200"/>
         <v>96013</v>
       </c>
       <c r="Z62" s="2">
-        <f t="shared" si="199"/>
+        <f t="shared" si="200"/>
         <v>111601</v>
       </c>
       <c r="AA62" s="2">
-        <f t="shared" si="199"/>
+        <f t="shared" si="200"/>
         <v>125254</v>
       </c>
       <c r="AB62" s="2">
-        <f t="shared" si="199"/>
+        <f t="shared" si="200"/>
         <v>140740</v>
+      </c>
+      <c r="AC62" s="2">
+        <f t="shared" si="200"/>
+        <v>161148</v>
+      </c>
+      <c r="AD62" s="2">
+        <f t="shared" si="200"/>
+        <v>206803</v>
       </c>
       <c r="BL62" s="2">
         <f>SUM(BL56:BL61)</f>
@@ -11146,96 +11348,104 @@
       <c r="D64" s="5"/>
       <c r="E64" s="5"/>
       <c r="F64" s="5">
-        <f t="shared" ref="F64:K64" si="200">F34</f>
+        <f t="shared" ref="F64:K64" si="201">F34</f>
         <v>951</v>
       </c>
       <c r="G64" s="5">
-        <f t="shared" si="200"/>
+        <f t="shared" si="201"/>
         <v>917</v>
       </c>
       <c r="H64" s="5">
-        <f t="shared" si="200"/>
+        <f t="shared" si="201"/>
         <v>622</v>
       </c>
       <c r="I64" s="5">
-        <f t="shared" si="200"/>
+        <f t="shared" si="201"/>
         <v>1336</v>
       </c>
       <c r="J64" s="5">
-        <f t="shared" si="200"/>
+        <f t="shared" si="201"/>
         <v>1457</v>
       </c>
       <c r="K64" s="5">
-        <f t="shared" si="200"/>
+        <f t="shared" si="201"/>
         <v>1912</v>
       </c>
       <c r="L64" s="5">
-        <f t="shared" ref="L64:R64" si="201">L34</f>
+        <f t="shared" ref="L64:R64" si="202">L34</f>
         <v>2374</v>
       </c>
       <c r="M64" s="5">
-        <f t="shared" si="201"/>
+        <f t="shared" si="202"/>
         <v>2464</v>
       </c>
       <c r="N64" s="5">
-        <f t="shared" si="201"/>
+        <f t="shared" si="202"/>
         <v>3003</v>
       </c>
       <c r="O64" s="5">
-        <f t="shared" si="201"/>
+        <f t="shared" si="202"/>
         <v>2971</v>
       </c>
       <c r="P64" s="5">
-        <f t="shared" si="201"/>
+        <f t="shared" si="202"/>
         <v>656</v>
       </c>
       <c r="Q64" s="5">
-        <f t="shared" si="201"/>
+        <f t="shared" si="202"/>
         <v>680</v>
       </c>
       <c r="R64" s="5">
-        <f t="shared" si="201"/>
+        <f t="shared" si="202"/>
         <v>1227</v>
       </c>
       <c r="S64" s="5">
-        <f t="shared" ref="S64:AB64" si="202">S34</f>
+        <f t="shared" ref="S64:AD64" si="203">S34</f>
         <v>2043</v>
       </c>
       <c r="T64" s="5">
-        <f t="shared" si="202"/>
+        <f t="shared" si="203"/>
         <v>6188</v>
       </c>
       <c r="U64" s="5">
-        <f t="shared" si="202"/>
+        <f t="shared" si="203"/>
         <v>9243</v>
       </c>
       <c r="V64" s="5">
-        <f t="shared" si="202"/>
+        <f t="shared" si="203"/>
         <v>12285</v>
       </c>
       <c r="W64" s="5">
-        <f t="shared" si="202"/>
+        <f t="shared" si="203"/>
         <v>14881</v>
       </c>
       <c r="X64" s="5">
-        <f t="shared" si="202"/>
+        <f t="shared" si="203"/>
         <v>16599</v>
       </c>
       <c r="Y64" s="5">
-        <f t="shared" si="202"/>
+        <f t="shared" si="203"/>
         <v>19309</v>
       </c>
       <c r="Z64" s="5">
-        <f t="shared" si="202"/>
+        <f t="shared" si="203"/>
         <v>22091</v>
       </c>
       <c r="AA64" s="5">
-        <f t="shared" si="202"/>
+        <f t="shared" si="203"/>
         <v>18775</v>
       </c>
       <c r="AB64" s="5">
-        <f t="shared" si="202"/>
+        <f t="shared" si="203"/>
         <v>26422</v>
+      </c>
+      <c r="AC64" s="5">
+        <f>AC34</f>
+        <v>30547</v>
+      </c>
+      <c r="AD64" s="5">
+        <f t="shared" si="203"/>
+        <v>37329</v>
       </c>
       <c r="AJ64" s="5"/>
       <c r="AK64" s="5"/>
@@ -11375,6 +11585,13 @@
         <f>45197-AA65</f>
         <v>26422</v>
       </c>
+      <c r="AC65" s="2">
+        <f>77107-AB65-AA65</f>
+        <v>31910</v>
+      </c>
+      <c r="AD65" s="2">
+        <v>42960</v>
+      </c>
       <c r="AJ65" s="5"/>
       <c r="AK65" s="5"/>
       <c r="AL65" s="5"/>
@@ -11406,7 +11623,7 @@
         <v>4332</v>
       </c>
       <c r="BM65" s="2">
-        <f t="shared" ref="BM65:BM72" si="203">SUM(K65:N65)</f>
+        <f t="shared" ref="BM65:BM72" si="204">SUM(K65:N65)</f>
         <v>9752</v>
       </c>
       <c r="BN65" s="2">
@@ -11440,7 +11657,7 @@
         <v>0</v>
       </c>
       <c r="J66" s="5">
-        <f t="shared" ref="J66:J72" si="204">+BL66-I66-H66-G66</f>
+        <f t="shared" ref="J66:J72" si="205">+BL66-I66-H66-G66</f>
         <v>0</v>
       </c>
       <c r="K66" s="5">
@@ -11508,19 +11725,19 @@
         <v>0</v>
       </c>
       <c r="BM66" s="2">
-        <f t="shared" si="203"/>
+        <f t="shared" si="204"/>
         <v>0</v>
       </c>
       <c r="BN66" s="2">
-        <f t="shared" ref="BN66:BN72" si="205">SUM(O66:R66)</f>
+        <f t="shared" ref="BN66:BN72" si="206">SUM(O66:R66)</f>
         <v>1353</v>
       </c>
       <c r="BO66" s="2">
-        <f t="shared" ref="BO66:BO72" si="206">SUM(S66:V66)</f>
+        <f t="shared" ref="BO66:BO72" si="207">SUM(S66:V66)</f>
         <v>0</v>
       </c>
       <c r="BP66" s="2">
-        <f t="shared" ref="BP66:BP72" si="207">SUM(W66:Z66)</f>
+        <f t="shared" ref="BP66:BP72" si="208">SUM(W66:Z66)</f>
         <v>0</v>
       </c>
     </row>
@@ -11544,7 +11761,7 @@
         <v>383</v>
       </c>
       <c r="J67" s="5">
-        <f t="shared" si="204"/>
+        <f t="shared" si="205"/>
         <v>416</v>
       </c>
       <c r="K67" s="5">
@@ -11613,6 +11830,13 @@
         <f>3099-AA67</f>
         <v>1625</v>
       </c>
+      <c r="AC67" s="2">
+        <f>4753-AB67-AA67</f>
+        <v>1654</v>
+      </c>
+      <c r="AD67" s="2">
+        <v>1633</v>
+      </c>
       <c r="BJ67" s="2">
         <v>557</v>
       </c>
@@ -11623,19 +11847,19 @@
         <v>1397</v>
       </c>
       <c r="BM67" s="2">
-        <f t="shared" si="203"/>
+        <f t="shared" si="204"/>
         <v>2004</v>
       </c>
       <c r="BN67" s="2">
-        <f t="shared" si="205"/>
+        <f t="shared" si="206"/>
         <v>2709</v>
       </c>
       <c r="BO67" s="2">
-        <f t="shared" si="206"/>
+        <f t="shared" si="207"/>
         <v>3549</v>
       </c>
       <c r="BP67" s="2">
-        <f t="shared" si="207"/>
+        <f t="shared" si="208"/>
         <v>4737</v>
       </c>
     </row>
@@ -11659,7 +11883,7 @@
         <v>299</v>
       </c>
       <c r="J68" s="5">
-        <f t="shared" si="204"/>
+        <f t="shared" si="205"/>
         <v>288</v>
       </c>
       <c r="K68" s="5">
@@ -11728,6 +11952,13 @@
         <f>1280-AA68</f>
         <v>669</v>
       </c>
+      <c r="AC68" s="2">
+        <f>2031-AB68-AA68</f>
+        <v>751</v>
+      </c>
+      <c r="AD68" s="2">
+        <v>811</v>
+      </c>
       <c r="BJ68" s="2">
         <v>262</v>
       </c>
@@ -11738,19 +11969,19 @@
         <v>1098</v>
       </c>
       <c r="BM68" s="2">
-        <f t="shared" si="203"/>
+        <f t="shared" si="204"/>
         <v>1174</v>
       </c>
       <c r="BN68" s="2">
-        <f t="shared" si="205"/>
+        <f t="shared" si="206"/>
         <v>1544</v>
       </c>
       <c r="BO68" s="2">
-        <f t="shared" si="206"/>
+        <f t="shared" si="207"/>
         <v>1508</v>
       </c>
       <c r="BP68" s="2">
-        <f t="shared" si="207"/>
+        <f t="shared" si="208"/>
         <v>1864</v>
       </c>
     </row>
@@ -11772,7 +12003,7 @@
         <v>0</v>
       </c>
       <c r="J69" s="5">
-        <f t="shared" si="204"/>
+        <f t="shared" si="205"/>
         <v>0</v>
       </c>
       <c r="K69" s="5">
@@ -11841,6 +12072,13 @@
         <f>-2073-AA69</f>
         <v>-2248</v>
       </c>
+      <c r="AC69" s="2">
+        <f>-3426-AB69-AA69</f>
+        <v>-1353</v>
+      </c>
+      <c r="AD69" s="2">
+        <v>-5491</v>
+      </c>
       <c r="BJ69" s="2">
         <v>0</v>
       </c>
@@ -11851,19 +12089,19 @@
         <v>0</v>
       </c>
       <c r="BM69" s="2">
-        <f t="shared" si="203"/>
+        <f t="shared" si="204"/>
         <v>-100</v>
       </c>
       <c r="BN69" s="2">
-        <f t="shared" si="205"/>
+        <f t="shared" si="206"/>
         <v>45</v>
       </c>
       <c r="BO69" s="2">
-        <f t="shared" si="206"/>
+        <f t="shared" si="207"/>
         <v>-238</v>
       </c>
       <c r="BP69" s="2">
-        <f t="shared" si="207"/>
+        <f t="shared" si="208"/>
         <v>-1029</v>
       </c>
     </row>
@@ -11887,7 +12125,7 @@
         <v>-53</v>
       </c>
       <c r="J70" s="5">
-        <f t="shared" si="204"/>
+        <f t="shared" si="205"/>
         <v>-165</v>
       </c>
       <c r="K70" s="5">
@@ -11956,6 +12194,13 @@
         <f>-2160-AA70</f>
         <v>17</v>
       </c>
+      <c r="AC70" s="2">
+        <f>-2035-AB70-AA70</f>
+        <v>125</v>
+      </c>
+      <c r="AD70" s="2">
+        <v>611</v>
+      </c>
       <c r="BJ70" s="2">
         <v>-315</v>
       </c>
@@ -11966,19 +12211,19 @@
         <v>-282</v>
       </c>
       <c r="BM70" s="2">
-        <f t="shared" si="203"/>
+        <f t="shared" si="204"/>
         <v>-406</v>
       </c>
       <c r="BN70" s="2">
-        <f t="shared" si="205"/>
+        <f t="shared" si="206"/>
         <v>-2164</v>
       </c>
       <c r="BO70" s="2">
-        <f t="shared" si="206"/>
+        <f t="shared" si="207"/>
         <v>-2489</v>
       </c>
       <c r="BP70" s="2">
-        <f t="shared" si="207"/>
+        <f t="shared" si="208"/>
         <v>-4477</v>
       </c>
     </row>
@@ -12002,7 +12247,7 @@
         <v>3</v>
       </c>
       <c r="J71" s="5">
-        <f t="shared" si="204"/>
+        <f t="shared" si="205"/>
         <v>-18</v>
       </c>
       <c r="K71" s="5">
@@ -12071,6 +12316,13 @@
         <f>-196-AA71</f>
         <v>-98</v>
       </c>
+      <c r="AC71" s="2">
+        <f>-276-AB71-AA71</f>
+        <v>-80</v>
+      </c>
+      <c r="AD71" s="2">
+        <v>-9</v>
+      </c>
       <c r="BJ71" s="2">
         <v>-45</v>
       </c>
@@ -12081,19 +12333,19 @@
         <v>-20</v>
       </c>
       <c r="BM71" s="2">
-        <f t="shared" si="203"/>
+        <f t="shared" si="204"/>
         <v>47</v>
       </c>
       <c r="BN71" s="2">
-        <f t="shared" si="205"/>
+        <f t="shared" si="206"/>
         <v>-7</v>
       </c>
       <c r="BO71" s="2">
-        <f t="shared" si="206"/>
+        <f t="shared" si="207"/>
         <v>-278</v>
       </c>
       <c r="BP71" s="2">
-        <f t="shared" si="207"/>
+        <f t="shared" si="208"/>
         <v>-503</v>
       </c>
     </row>
@@ -12118,7 +12370,7 @@
         <v>-689</v>
       </c>
       <c r="J72" s="5">
-        <f t="shared" si="204"/>
+        <f t="shared" si="205"/>
         <v>89</v>
       </c>
       <c r="K72" s="5">
@@ -12193,6 +12445,14 @@
         <f>-4743-4880+946+2255+3075+979-AA72</f>
         <v>-11022</v>
       </c>
+      <c r="AC72" s="2">
+        <f>-10325-9703+857+2032+4204+1311-AB72-AA72</f>
+        <v>-9256</v>
+      </c>
+      <c r="AD72" s="2">
+        <f>-5073-1621-281+1064+1053+533</f>
+        <v>-4325</v>
+      </c>
       <c r="BJ72" s="2">
         <f>-149-776-55-135+256+2</f>
         <v>-857</v>
@@ -12206,19 +12466,19 @@
         <v>-703</v>
       </c>
       <c r="BM72" s="2">
-        <f t="shared" si="203"/>
+        <f t="shared" si="204"/>
         <v>-3363</v>
       </c>
       <c r="BN72" s="2">
-        <f t="shared" si="205"/>
+        <f t="shared" si="206"/>
         <v>-2207</v>
       </c>
       <c r="BO72" s="2">
-        <f t="shared" si="206"/>
+        <f t="shared" si="207"/>
         <v>-3722</v>
       </c>
       <c r="BP72" s="2">
-        <f t="shared" si="207"/>
+        <f t="shared" si="208"/>
         <v>-9384</v>
       </c>
     </row>
@@ -12231,92 +12491,100 @@
       <c r="E73" s="5"/>
       <c r="F73" s="5"/>
       <c r="G73" s="5">
-        <f t="shared" ref="G73:AB73" si="208">SUM(G65:G72)</f>
+        <f t="shared" ref="G73:AD73" si="209">SUM(G65:G72)</f>
         <v>909</v>
       </c>
       <c r="H73" s="5">
-        <f t="shared" si="208"/>
+        <f t="shared" si="209"/>
         <v>1567</v>
       </c>
       <c r="I73" s="5">
-        <f t="shared" si="208"/>
+        <f t="shared" si="209"/>
         <v>1279</v>
       </c>
       <c r="J73" s="5">
-        <f t="shared" si="208"/>
+        <f t="shared" si="209"/>
         <v>2067</v>
       </c>
       <c r="K73" s="5">
-        <f t="shared" si="208"/>
+        <f t="shared" si="209"/>
         <v>1874</v>
       </c>
       <c r="L73" s="5">
-        <f t="shared" si="208"/>
+        <f t="shared" si="209"/>
         <v>2682</v>
       </c>
       <c r="M73" s="5">
-        <f t="shared" si="208"/>
+        <f t="shared" si="209"/>
         <v>1519</v>
       </c>
       <c r="N73" s="5">
-        <f t="shared" si="208"/>
+        <f t="shared" si="209"/>
         <v>3033</v>
       </c>
       <c r="O73" s="5">
-        <f t="shared" si="208"/>
+        <f t="shared" si="209"/>
         <v>1731</v>
       </c>
       <c r="P73" s="5">
-        <f t="shared" si="208"/>
+        <f t="shared" si="209"/>
         <v>1270</v>
       </c>
       <c r="Q73" s="5">
-        <f t="shared" si="208"/>
+        <f t="shared" si="209"/>
         <v>392</v>
       </c>
       <c r="R73" s="5">
-        <f t="shared" si="208"/>
+        <f t="shared" si="209"/>
         <v>2248</v>
       </c>
       <c r="S73" s="5">
-        <f t="shared" si="208"/>
+        <f t="shared" si="209"/>
         <v>2911</v>
       </c>
       <c r="T73" s="5">
-        <f t="shared" si="208"/>
+        <f t="shared" si="209"/>
         <v>6348</v>
       </c>
       <c r="U73" s="5">
-        <f t="shared" si="208"/>
+        <f t="shared" si="209"/>
         <v>7332</v>
       </c>
       <c r="V73" s="5">
-        <f t="shared" si="208"/>
+        <f t="shared" si="209"/>
         <v>11499</v>
       </c>
       <c r="W73" s="5">
-        <f t="shared" si="208"/>
+        <f t="shared" si="209"/>
         <v>15345</v>
       </c>
       <c r="X73" s="5">
-        <f t="shared" si="208"/>
+        <f t="shared" si="209"/>
         <v>14488</v>
       </c>
       <c r="Y73" s="5">
-        <f t="shared" si="208"/>
+        <f t="shared" si="209"/>
         <v>17627</v>
       </c>
       <c r="Z73" s="5">
-        <f t="shared" si="208"/>
+        <f t="shared" si="209"/>
         <v>16628</v>
       </c>
       <c r="AA73" s="5">
-        <f t="shared" si="208"/>
+        <f t="shared" si="209"/>
         <v>27414</v>
       </c>
       <c r="AB73" s="5">
-        <f t="shared" si="208"/>
+        <f t="shared" si="209"/>
         <v>15365</v>
+      </c>
+      <c r="AC73" s="5">
+        <f t="shared" si="209"/>
+        <v>23751</v>
+      </c>
+      <c r="AD73" s="5">
+        <f t="shared" si="209"/>
+        <v>36190</v>
       </c>
       <c r="AJ73" s="5"/>
       <c r="AK73" s="5"/>
@@ -12340,31 +12608,31 @@
       <c r="BC73" s="5"/>
       <c r="BD73" s="5"/>
       <c r="BJ73" s="2">
-        <f t="shared" ref="BJ73:BP73" si="209">SUM(BJ65:BJ72)</f>
+        <f t="shared" ref="BJ73:BP73" si="210">SUM(BJ65:BJ72)</f>
         <v>3743</v>
       </c>
       <c r="BK73" s="2">
-        <f t="shared" si="209"/>
+        <f t="shared" si="210"/>
         <v>4761</v>
       </c>
       <c r="BL73" s="2">
-        <f t="shared" si="209"/>
+        <f t="shared" si="210"/>
         <v>5822</v>
       </c>
       <c r="BM73" s="2">
-        <f t="shared" si="209"/>
+        <f t="shared" si="210"/>
         <v>9108</v>
       </c>
       <c r="BN73" s="2">
-        <f t="shared" si="209"/>
+        <f t="shared" si="210"/>
         <v>5641</v>
       </c>
       <c r="BO73" s="2">
-        <f t="shared" si="209"/>
+        <f t="shared" si="210"/>
         <v>28090</v>
       </c>
       <c r="BP73" s="2">
-        <f t="shared" si="209"/>
+        <f t="shared" si="210"/>
         <v>64088</v>
       </c>
     </row>
@@ -12395,7 +12663,7 @@
         <v>-175</v>
       </c>
       <c r="J75" s="5">
-        <f t="shared" ref="J75:J77" si="210">+BL75-I75-H75-G75</f>
+        <f t="shared" ref="J75:J77" si="211">+BL75-I75-H75-G75</f>
         <v>-2846</v>
       </c>
       <c r="K75" s="5">
@@ -12470,6 +12738,14 @@
         <f>6252+487+70-14358-995-AA75</f>
         <v>-4938</v>
       </c>
+      <c r="AC75" s="2">
+        <f>8980+487+72-20076-AB75-AA75</f>
+        <v>-1993</v>
+      </c>
+      <c r="AD75" s="2">
+        <f>14670+2246+12-20540-12800</f>
+        <v>-16412</v>
+      </c>
       <c r="BJ75" s="2">
         <f>7232+428-11148-9</f>
         <v>-3497</v>
@@ -12487,15 +12763,15 @@
         <v>-8591</v>
       </c>
       <c r="BN75" s="2">
-        <f t="shared" ref="BN75:BN77" si="211">SUM(O75:R75)</f>
+        <f t="shared" ref="BN75:BN77" si="212">SUM(O75:R75)</f>
         <v>9257</v>
       </c>
       <c r="BO75" s="2">
-        <f t="shared" ref="BO75:BO80" si="212">SUM(S75:V75)</f>
+        <f t="shared" ref="BO75:BO80" si="213">SUM(S75:V75)</f>
         <v>-9414</v>
       </c>
       <c r="BP75" s="2">
-        <f t="shared" ref="BP75:BP80" si="213">SUM(W75:Z75)</f>
+        <f t="shared" ref="BP75:BP80" si="214">SUM(W75:Z75)</f>
         <v>-16178</v>
       </c>
     </row>
@@ -12519,7 +12795,7 @@
         <v>-473</v>
       </c>
       <c r="J76" s="5">
-        <f t="shared" si="210"/>
+        <f t="shared" si="211"/>
         <v>-283</v>
       </c>
       <c r="K76" s="5">
@@ -12588,6 +12864,13 @@
         <f>-3122-AA76</f>
         <v>-1895</v>
       </c>
+      <c r="AC76" s="2">
+        <f>-4758-AB76-AA76-4702</f>
+        <v>-6338</v>
+      </c>
+      <c r="AD76" s="2">
+        <v>-1284</v>
+      </c>
       <c r="BJ76" s="2">
         <v>-600</v>
       </c>
@@ -12602,15 +12885,15 @@
         <v>-976</v>
       </c>
       <c r="BN76" s="2">
-        <f t="shared" si="211"/>
+        <f t="shared" si="212"/>
         <v>-1833</v>
       </c>
       <c r="BO76" s="2">
-        <f t="shared" si="212"/>
+        <f t="shared" si="213"/>
         <v>-1069</v>
       </c>
       <c r="BP76" s="2">
-        <f t="shared" si="213"/>
+        <f t="shared" si="214"/>
         <v>-3236</v>
       </c>
     </row>
@@ -12634,7 +12917,7 @@
         <v>-1353</v>
       </c>
       <c r="J77" s="5">
-        <f t="shared" si="210"/>
+        <f t="shared" si="211"/>
         <v>0</v>
       </c>
       <c r="K77" s="5">
@@ -12702,6 +12985,14 @@
         <f>-677-AA77</f>
         <v>-294</v>
       </c>
+      <c r="AC77" s="2">
+        <f>-1370-AB77-AA77</f>
+        <v>-693</v>
+      </c>
+      <c r="AD77" s="2">
+        <f>-13000-165</f>
+        <v>-13165</v>
+      </c>
       <c r="BJ77" s="2">
         <v>0</v>
       </c>
@@ -12716,15 +13007,15 @@
         <v>-263</v>
       </c>
       <c r="BN77" s="2">
-        <f t="shared" si="211"/>
+        <f t="shared" si="212"/>
         <v>-49</v>
       </c>
       <c r="BO77" s="2">
-        <f t="shared" si="212"/>
+        <f t="shared" si="213"/>
         <v>-83</v>
       </c>
       <c r="BP77" s="2">
-        <f t="shared" si="213"/>
+        <f t="shared" si="214"/>
         <v>-1007</v>
       </c>
     </row>
@@ -12737,92 +13028,100 @@
       <c r="E78" s="5"/>
       <c r="F78" s="5"/>
       <c r="G78" s="5">
-        <f t="shared" ref="G78:N78" si="214">SUM(G75:G77)</f>
+        <f t="shared" ref="G78:N78" si="215">SUM(G75:G77)</f>
         <v>-1055</v>
       </c>
       <c r="H78" s="5">
-        <f t="shared" si="214"/>
+        <f t="shared" si="215"/>
         <v>-13490</v>
       </c>
       <c r="I78" s="5">
-        <f t="shared" si="214"/>
+        <f t="shared" si="215"/>
         <v>-2001</v>
       </c>
       <c r="J78" s="5">
-        <f t="shared" si="214"/>
+        <f t="shared" si="215"/>
         <v>-3129</v>
       </c>
       <c r="K78" s="5">
-        <f t="shared" si="214"/>
+        <f t="shared" si="215"/>
         <v>-1272</v>
       </c>
       <c r="L78" s="5">
-        <f t="shared" si="214"/>
+        <f t="shared" si="215"/>
         <v>-2533</v>
       </c>
       <c r="M78" s="5">
-        <f t="shared" si="214"/>
+        <f t="shared" si="215"/>
         <v>-4439</v>
       </c>
       <c r="N78" s="5">
-        <f t="shared" si="214"/>
+        <f t="shared" si="215"/>
         <v>-1586</v>
       </c>
       <c r="O78" s="5">
-        <f t="shared" ref="O78:S78" si="215">SUM(O75:O77)</f>
+        <f t="shared" ref="O78:S78" si="216">SUM(O75:O77)</f>
         <v>2612</v>
       </c>
       <c r="P78" s="5">
-        <f t="shared" si="215"/>
+        <f t="shared" si="216"/>
         <v>1618</v>
       </c>
       <c r="Q78" s="5">
-        <f t="shared" si="215"/>
+        <f t="shared" si="216"/>
         <v>3148</v>
       </c>
       <c r="R78" s="5">
-        <f t="shared" si="215"/>
+        <f t="shared" si="216"/>
         <v>-3</v>
       </c>
       <c r="S78" s="5">
-        <f t="shared" si="215"/>
+        <f t="shared" si="216"/>
         <v>-841</v>
       </c>
       <c r="T78" s="5">
-        <f t="shared" ref="T78:AB78" si="216">SUM(T75:T77)</f>
+        <f t="shared" ref="T78:AD78" si="217">SUM(T75:T77)</f>
         <v>-446</v>
       </c>
       <c r="U78" s="5">
-        <f t="shared" si="216"/>
+        <f t="shared" si="217"/>
         <v>-3170</v>
       </c>
       <c r="V78" s="5">
-        <f t="shared" si="216"/>
+        <f t="shared" si="217"/>
         <v>-6109</v>
       </c>
       <c r="W78" s="5">
-        <f t="shared" si="216"/>
+        <f t="shared" si="217"/>
         <v>-5693</v>
       </c>
       <c r="X78" s="5">
-        <f t="shared" si="216"/>
+        <f t="shared" si="217"/>
         <v>-3184</v>
       </c>
       <c r="Y78" s="5">
-        <f t="shared" si="216"/>
+        <f t="shared" si="217"/>
         <v>-4346</v>
       </c>
       <c r="Z78" s="5">
-        <f t="shared" si="216"/>
+        <f t="shared" si="217"/>
         <v>-7198</v>
       </c>
       <c r="AA78" s="5">
-        <f t="shared" si="216"/>
+        <f t="shared" si="217"/>
         <v>-5216</v>
       </c>
       <c r="AB78" s="5">
-        <f t="shared" si="216"/>
+        <f t="shared" si="217"/>
         <v>-7127</v>
+      </c>
+      <c r="AC78" s="5">
+        <f t="shared" si="217"/>
+        <v>-9024</v>
+      </c>
+      <c r="AD78" s="5">
+        <f t="shared" si="217"/>
+        <v>-30861</v>
       </c>
       <c r="AJ78" s="5"/>
       <c r="AK78" s="5"/>
@@ -12846,11 +13145,11 @@
       <c r="BC78" s="5"/>
       <c r="BD78" s="5"/>
       <c r="BJ78" s="2">
-        <f t="shared" ref="BJ78:BK78" si="217">SUM(BJ75:BJ77)</f>
+        <f t="shared" ref="BJ78:BK78" si="218">SUM(BJ75:BJ77)</f>
         <v>-4097</v>
       </c>
       <c r="BK78" s="2">
-        <f t="shared" si="217"/>
+        <f t="shared" si="218"/>
         <v>6145</v>
       </c>
       <c r="BL78" s="2">
@@ -12897,7 +13196,7 @@
         <v>96</v>
       </c>
       <c r="J80" s="5">
-        <f t="shared" ref="J80:J85" si="218">+BL80-I80-H80-G80</f>
+        <f t="shared" ref="J80:J85" si="219">+BL80-I80-H80-G80</f>
         <v>4</v>
       </c>
       <c r="K80" s="5">
@@ -12967,6 +13266,13 @@
         <f>370-AA80</f>
         <v>0</v>
       </c>
+      <c r="AC80" s="2">
+        <f>643-AB80-AA80</f>
+        <v>273</v>
+      </c>
+      <c r="AD80" s="2">
+        <v>-2139</v>
+      </c>
       <c r="BJ80" s="2">
         <v>137</v>
       </c>
@@ -12977,19 +13283,19 @@
         <v>194</v>
       </c>
       <c r="BM80" s="2">
-        <f t="shared" ref="BM80:BM85" si="219">SUM(K80:N80)</f>
+        <f t="shared" ref="BM80:BM85" si="220">SUM(K80:N80)</f>
         <v>281</v>
       </c>
       <c r="BN80" s="2">
-        <f t="shared" ref="BN80:BN85" si="220">SUM(O80:R80)</f>
+        <f t="shared" ref="BN80:BN85" si="221">SUM(O80:R80)</f>
         <v>355</v>
       </c>
       <c r="BO80" s="2">
-        <f t="shared" si="212"/>
+        <f t="shared" si="213"/>
         <v>403</v>
       </c>
       <c r="BP80" s="2">
-        <f t="shared" si="213"/>
+        <f t="shared" si="214"/>
         <v>489</v>
       </c>
     </row>
@@ -13013,7 +13319,7 @@
         <v>-298</v>
       </c>
       <c r="J81" s="5">
-        <f t="shared" si="218"/>
+        <f t="shared" si="219"/>
         <v>-226</v>
       </c>
       <c r="K81" s="5">
@@ -13082,6 +13388,13 @@
         <f>-3380-AA81</f>
         <v>-1848</v>
       </c>
+      <c r="AC81" s="2">
+        <f>-5809-AB81-AA81</f>
+        <v>-2429</v>
+      </c>
+      <c r="AD81" s="2">
+        <v>0</v>
+      </c>
       <c r="BJ81" s="2">
         <v>-1032</v>
       </c>
@@ -13092,19 +13405,19 @@
         <v>-942</v>
       </c>
       <c r="BM81" s="2">
-        <f t="shared" si="219"/>
+        <f t="shared" si="220"/>
         <v>-1904</v>
       </c>
       <c r="BN81" s="2">
-        <f t="shared" si="220"/>
+        <f t="shared" si="221"/>
         <v>-1475</v>
       </c>
       <c r="BO81" s="2">
-        <f t="shared" ref="BO81:BO85" si="221">SUM(S81:V81)</f>
+        <f t="shared" ref="BO81:BO85" si="222">SUM(S81:V81)</f>
         <v>-2783</v>
       </c>
       <c r="BP81" s="2">
-        <f t="shared" ref="BP81:BP85" si="222">SUM(W81:Z81)</f>
+        <f t="shared" ref="BP81:BP85" si="223">SUM(W81:Z81)</f>
         <v>-6929</v>
       </c>
     </row>
@@ -13128,7 +13441,7 @@
         <v>-99</v>
       </c>
       <c r="J82" s="5">
-        <f t="shared" si="218"/>
+        <f t="shared" si="219"/>
         <v>-99</v>
       </c>
       <c r="K82" s="5">
@@ -13197,6 +13510,13 @@
         <f>-488-AA82</f>
         <v>-244</v>
       </c>
+      <c r="AC82" s="2">
+        <f>-732-AB82-AA82</f>
+        <v>-244</v>
+      </c>
+      <c r="AD82" s="2">
+        <v>-243</v>
+      </c>
       <c r="BJ82" s="2">
         <v>-371</v>
       </c>
@@ -13207,19 +13527,19 @@
         <v>-395</v>
       </c>
       <c r="BM82" s="2">
-        <f t="shared" si="219"/>
+        <f t="shared" si="220"/>
         <v>-399</v>
       </c>
       <c r="BN82" s="2">
-        <f t="shared" si="220"/>
+        <f t="shared" si="221"/>
         <v>-398</v>
       </c>
       <c r="BO82" s="2">
-        <f t="shared" si="221"/>
+        <f t="shared" si="222"/>
         <v>-395</v>
       </c>
       <c r="BP82" s="2">
-        <f t="shared" si="222"/>
+        <f t="shared" si="223"/>
         <v>-834</v>
       </c>
     </row>
@@ -13241,7 +13561,7 @@
         <v>0</v>
       </c>
       <c r="J83" s="5">
-        <f t="shared" si="218"/>
+        <f t="shared" si="219"/>
         <v>0</v>
       </c>
       <c r="K83" s="5">
@@ -13307,6 +13627,13 @@
         <f>-23815-AA83</f>
         <v>-9720</v>
       </c>
+      <c r="AC83" s="2">
+        <f>-36271-AB83-AA83</f>
+        <v>-12456</v>
+      </c>
+      <c r="AD83" s="2">
+        <v>-3815</v>
+      </c>
       <c r="BJ83" s="2">
         <v>-1579</v>
       </c>
@@ -13317,19 +13644,19 @@
         <v>0</v>
       </c>
       <c r="BM83" s="2">
-        <f t="shared" si="219"/>
+        <f t="shared" si="220"/>
         <v>0</v>
       </c>
       <c r="BN83" s="2">
-        <f t="shared" si="220"/>
+        <f t="shared" si="221"/>
         <v>-10039</v>
       </c>
       <c r="BO83" s="2">
-        <f t="shared" si="221"/>
+        <f t="shared" si="222"/>
         <v>-9533</v>
       </c>
       <c r="BP83" s="2">
-        <f t="shared" si="222"/>
+        <f t="shared" si="223"/>
         <v>-33705</v>
       </c>
     </row>
@@ -13354,7 +13681,7 @@
         <v>0</v>
       </c>
       <c r="J84" s="5">
-        <f t="shared" si="218"/>
+        <f t="shared" si="219"/>
         <v>-4</v>
       </c>
       <c r="K84" s="5">
@@ -13421,6 +13748,12 @@
       <c r="AB84" s="2">
         <v>0</v>
       </c>
+      <c r="AC84" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD84" s="2">
+        <v>0</v>
+      </c>
       <c r="BJ84" s="2">
         <f>-16-5</f>
         <v>-21</v>
@@ -13433,19 +13766,19 @@
         <v>4964</v>
       </c>
       <c r="BM84" s="2">
-        <f t="shared" si="219"/>
+        <f t="shared" si="220"/>
         <v>3977</v>
       </c>
       <c r="BN84" s="2">
-        <f t="shared" si="220"/>
+        <f t="shared" si="221"/>
         <v>-2</v>
       </c>
       <c r="BO84" s="2">
-        <f t="shared" si="221"/>
+        <f t="shared" si="222"/>
         <v>-1250</v>
       </c>
       <c r="BP84" s="2">
-        <f t="shared" si="222"/>
+        <f t="shared" si="223"/>
         <v>-1250</v>
       </c>
     </row>
@@ -13467,7 +13800,7 @@
         <v>0</v>
       </c>
       <c r="J85" s="5">
-        <f t="shared" si="218"/>
+        <f t="shared" si="219"/>
         <v>-17</v>
       </c>
       <c r="K85" s="5">
@@ -13537,6 +13870,14 @@
         <f>-73-AA85</f>
         <v>-21</v>
       </c>
+      <c r="AC85" s="2">
+        <f>-97-AB85-AA85</f>
+        <v>-24</v>
+      </c>
+      <c r="AD85" s="2">
+        <f>-4-9</f>
+        <v>-13</v>
+      </c>
       <c r="BJ85" s="2">
         <v>0</v>
       </c>
@@ -13547,19 +13888,19 @@
         <v>-17</v>
       </c>
       <c r="BM85" s="2">
-        <f t="shared" si="219"/>
+        <f t="shared" si="220"/>
         <v>-90</v>
       </c>
       <c r="BN85" s="2">
-        <f t="shared" si="220"/>
+        <f t="shared" si="221"/>
         <v>-58</v>
       </c>
       <c r="BO85" s="2">
-        <f t="shared" si="221"/>
+        <f t="shared" si="222"/>
         <v>-74</v>
       </c>
       <c r="BP85" s="2">
-        <f t="shared" si="222"/>
+        <f t="shared" si="223"/>
         <v>-129</v>
       </c>
     </row>
@@ -13572,92 +13913,100 @@
       <c r="E86" s="5"/>
       <c r="F86" s="5"/>
       <c r="G86" s="5">
-        <f t="shared" ref="G86:N86" si="223">SUM(G80:G85)</f>
+        <f t="shared" ref="G86:N86" si="224">SUM(G80:G85)</f>
         <v>4744</v>
       </c>
       <c r="H86" s="5">
-        <f t="shared" si="223"/>
+        <f t="shared" si="224"/>
         <v>-297</v>
       </c>
       <c r="I86" s="5">
-        <f t="shared" si="223"/>
+        <f t="shared" si="224"/>
         <v>-301</v>
       </c>
       <c r="J86" s="5">
-        <f t="shared" si="223"/>
+        <f t="shared" si="224"/>
         <v>-342</v>
       </c>
       <c r="K86" s="5">
-        <f t="shared" si="223"/>
+        <f t="shared" si="224"/>
         <v>-471</v>
       </c>
       <c r="L86" s="5">
-        <f t="shared" si="223"/>
+        <f t="shared" si="224"/>
         <v>4501</v>
       </c>
       <c r="M86" s="5">
-        <f t="shared" si="223"/>
+        <f t="shared" si="224"/>
         <v>-1420</v>
       </c>
       <c r="N86" s="5">
-        <f t="shared" si="223"/>
+        <f t="shared" si="224"/>
         <v>-745</v>
       </c>
       <c r="O86" s="5">
-        <f t="shared" ref="O86:S86" si="224">SUM(O80:O85)</f>
+        <f t="shared" ref="O86:S86" si="225">SUM(O80:O85)</f>
         <v>-2446</v>
       </c>
       <c r="P86" s="5">
-        <f t="shared" si="224"/>
+        <f t="shared" si="225"/>
         <v>-3762</v>
       </c>
       <c r="Q86" s="5">
-        <f t="shared" si="224"/>
+        <f t="shared" si="225"/>
         <v>-3753</v>
       </c>
       <c r="R86" s="5">
-        <f t="shared" si="224"/>
+        <f t="shared" si="225"/>
         <v>-1656</v>
       </c>
       <c r="S86" s="5">
-        <f t="shared" si="224"/>
+        <f t="shared" si="225"/>
         <v>-380</v>
       </c>
       <c r="T86" s="5">
-        <f t="shared" ref="T86:AB86" si="225">SUM(T80:T85)</f>
+        <f t="shared" ref="T86:AC86" si="226">SUM(T80:T85)</f>
         <v>-5099</v>
       </c>
       <c r="U86" s="5">
-        <f t="shared" si="225"/>
+        <f t="shared" si="226"/>
         <v>-4524</v>
       </c>
       <c r="V86" s="5">
-        <f t="shared" si="225"/>
+        <f t="shared" si="226"/>
         <v>-3629</v>
       </c>
       <c r="W86" s="5">
-        <f t="shared" si="225"/>
+        <f t="shared" si="226"/>
         <v>-9345</v>
       </c>
       <c r="X86" s="5">
-        <f t="shared" si="225"/>
+        <f t="shared" si="226"/>
         <v>-10320</v>
       </c>
       <c r="Y86" s="5">
-        <f t="shared" si="225"/>
+        <f t="shared" si="226"/>
         <v>-12745</v>
       </c>
       <c r="Z86" s="5">
-        <f t="shared" si="225"/>
+        <f t="shared" si="226"/>
         <v>-9948</v>
       </c>
       <c r="AA86" s="5">
-        <f t="shared" si="225"/>
+        <f t="shared" si="226"/>
         <v>-15553</v>
       </c>
       <c r="AB86" s="5">
-        <f t="shared" si="225"/>
+        <f t="shared" si="226"/>
         <v>-11833</v>
+      </c>
+      <c r="AC86" s="5">
+        <f t="shared" si="226"/>
+        <v>-14880</v>
+      </c>
+      <c r="AD86" s="5">
+        <f>SUM(AD80:AD85)</f>
+        <v>-6210</v>
       </c>
       <c r="AJ86" s="5"/>
       <c r="AK86" s="5"/>
@@ -13681,31 +14030,31 @@
       <c r="BC86" s="5"/>
       <c r="BD86" s="5"/>
       <c r="BJ86" s="2">
-        <f t="shared" ref="BJ86:BP86" si="226">SUM(BJ80:BJ85)</f>
+        <f t="shared" ref="BJ86:BP86" si="227">SUM(BJ80:BJ85)</f>
         <v>-2866</v>
       </c>
       <c r="BK86" s="2">
-        <f t="shared" si="226"/>
+        <f t="shared" si="227"/>
         <v>-792</v>
       </c>
       <c r="BL86" s="2">
-        <f t="shared" si="226"/>
+        <f t="shared" si="227"/>
         <v>3804</v>
       </c>
       <c r="BM86" s="2">
-        <f t="shared" si="226"/>
+        <f t="shared" si="227"/>
         <v>1865</v>
       </c>
       <c r="BN86" s="2">
-        <f t="shared" si="226"/>
+        <f t="shared" si="227"/>
         <v>-11617</v>
       </c>
       <c r="BO86" s="2">
-        <f t="shared" si="226"/>
+        <f t="shared" si="227"/>
         <v>-13632</v>
       </c>
       <c r="BP86" s="2">
-        <f t="shared" si="226"/>
+        <f t="shared" si="227"/>
         <v>-42358</v>
       </c>
     </row>
@@ -13715,92 +14064,100 @@
       </c>
       <c r="F87" s="5"/>
       <c r="G87" s="5">
-        <f t="shared" ref="G87:N87" si="227">G86+G78+G73</f>
+        <f t="shared" ref="G87:N87" si="228">G86+G78+G73</f>
         <v>4598</v>
       </c>
       <c r="H87" s="5">
-        <f t="shared" si="227"/>
+        <f t="shared" si="228"/>
         <v>-12220</v>
       </c>
       <c r="I87" s="5">
-        <f t="shared" si="227"/>
+        <f t="shared" si="228"/>
         <v>-1023</v>
       </c>
       <c r="J87" s="5">
-        <f t="shared" si="227"/>
+        <f t="shared" si="228"/>
         <v>-1404</v>
       </c>
       <c r="K87" s="5">
-        <f t="shared" si="227"/>
+        <f t="shared" si="228"/>
         <v>131</v>
       </c>
       <c r="L87" s="5">
-        <f t="shared" si="227"/>
+        <f t="shared" si="228"/>
         <v>4650</v>
       </c>
       <c r="M87" s="5">
-        <f t="shared" si="227"/>
+        <f t="shared" si="228"/>
         <v>-4340</v>
       </c>
       <c r="N87" s="5">
-        <f t="shared" si="227"/>
+        <f t="shared" si="228"/>
         <v>702</v>
       </c>
       <c r="O87" s="5">
-        <f t="shared" ref="O87:R87" si="228">O86+O78+O73</f>
+        <f t="shared" ref="O87:R87" si="229">O86+O78+O73</f>
         <v>1897</v>
       </c>
       <c r="P87" s="5">
-        <f t="shared" si="228"/>
+        <f t="shared" si="229"/>
         <v>-874</v>
       </c>
       <c r="Q87" s="5">
-        <f t="shared" si="228"/>
+        <f t="shared" si="229"/>
         <v>-213</v>
       </c>
       <c r="R87" s="5">
-        <f t="shared" si="228"/>
+        <f t="shared" si="229"/>
         <v>589</v>
       </c>
       <c r="S87" s="5">
-        <f t="shared" ref="S87:AB87" si="229">S86+S78+S73</f>
+        <f t="shared" ref="S87:AD87" si="230">S86+S78+S73</f>
         <v>1690</v>
       </c>
       <c r="T87" s="5">
-        <f t="shared" si="229"/>
+        <f t="shared" si="230"/>
         <v>803</v>
       </c>
       <c r="U87" s="5">
-        <f t="shared" si="229"/>
+        <f t="shared" si="230"/>
         <v>-362</v>
       </c>
       <c r="V87" s="5">
-        <f t="shared" si="229"/>
+        <f t="shared" si="230"/>
         <v>1761</v>
       </c>
       <c r="W87" s="5">
-        <f t="shared" si="229"/>
+        <f t="shared" si="230"/>
         <v>307</v>
       </c>
       <c r="X87" s="5">
-        <f t="shared" si="229"/>
+        <f t="shared" si="230"/>
         <v>984</v>
       </c>
       <c r="Y87" s="5">
-        <f t="shared" si="229"/>
+        <f t="shared" si="230"/>
         <v>536</v>
       </c>
       <c r="Z87" s="5">
-        <f t="shared" si="229"/>
+        <f t="shared" si="230"/>
         <v>-518</v>
       </c>
       <c r="AA87" s="5">
-        <f t="shared" si="229"/>
+        <f t="shared" si="230"/>
         <v>6645</v>
       </c>
       <c r="AB87" s="5">
-        <f t="shared" si="229"/>
+        <f t="shared" si="230"/>
         <v>-3595</v>
+      </c>
+      <c r="AC87" s="5">
+        <f t="shared" si="230"/>
+        <v>-153</v>
+      </c>
+      <c r="AD87" s="5">
+        <f t="shared" si="230"/>
+        <v>-881</v>
       </c>
       <c r="AJ87" s="5"/>
       <c r="AK87" s="5"/>
@@ -13825,19 +14182,19 @@
       <c r="BD87" s="5"/>
       <c r="BJ87" s="5"/>
       <c r="BK87" s="5">
-        <f t="shared" ref="BK87:BN87" si="230">BK86+BK78+BK73</f>
+        <f t="shared" ref="BK87:BN87" si="231">BK86+BK78+BK73</f>
         <v>10114</v>
       </c>
       <c r="BL87" s="5">
-        <f t="shared" si="230"/>
+        <f t="shared" si="231"/>
         <v>-10049</v>
       </c>
       <c r="BM87" s="5">
-        <f t="shared" si="230"/>
+        <f t="shared" si="231"/>
         <v>1143</v>
       </c>
       <c r="BN87" s="5">
-        <f t="shared" si="230"/>
+        <f t="shared" si="231"/>
         <v>1399</v>
       </c>
       <c r="BO87" s="5">
@@ -13858,52 +14215,68 @@
         <v>18839</v>
       </c>
       <c r="V89" s="2">
-        <f t="shared" ref="V89" si="231">SUM(S73:V73)</f>
+        <f t="shared" ref="V89" si="232">SUM(S73:V73)</f>
         <v>28090</v>
       </c>
       <c r="W89" s="2">
-        <f t="shared" ref="W89" si="232">SUM(T73:W73)</f>
+        <f t="shared" ref="W89" si="233">SUM(T73:W73)</f>
         <v>40524</v>
       </c>
       <c r="X89" s="2">
-        <f t="shared" ref="X89" si="233">SUM(U73:X73)</f>
+        <f t="shared" ref="X89" si="234">SUM(U73:X73)</f>
         <v>48664</v>
       </c>
       <c r="Y89" s="2">
-        <f t="shared" ref="Y89:AA89" si="234">SUM(V73:Y73)</f>
+        <f t="shared" ref="Y89:AA89" si="235">SUM(V73:Y73)</f>
         <v>58959</v>
       </c>
       <c r="Z89" s="2">
-        <f t="shared" si="234"/>
+        <f t="shared" si="235"/>
         <v>64088</v>
       </c>
       <c r="AA89" s="2">
-        <f t="shared" si="234"/>
+        <f t="shared" si="235"/>
         <v>76157</v>
       </c>
       <c r="AB89" s="2">
         <f>SUM(Y73:AB73)</f>
         <v>77034</v>
       </c>
+      <c r="AC89" s="2">
+        <f>SUM(Z73:AC73)</f>
+        <v>83158</v>
+      </c>
+      <c r="AD89" s="2">
+        <f>SUM(AA73:AD73)</f>
+        <v>102720</v>
+      </c>
     </row>
     <row r="90" spans="2:78" x14ac:dyDescent="0.25">
       <c r="X90" s="10"/>
       <c r="Y90" s="10">
-        <f t="shared" ref="Y90" si="235">+Y89/U89-1</f>
+        <f t="shared" ref="Y90" si="236">+Y89/U89-1</f>
         <v>2.1296247146876159</v>
       </c>
       <c r="Z90" s="10">
-        <f t="shared" ref="Z90:AA90" si="236">+Z89/V89-1</f>
+        <f t="shared" ref="Z90:AA90" si="237">+Z89/V89-1</f>
         <v>1.2815236739053044</v>
       </c>
       <c r="AA90" s="10">
-        <f t="shared" si="236"/>
+        <f t="shared" si="237"/>
         <v>0.87930609021814243</v>
       </c>
       <c r="AB90" s="10">
         <f>+AB89/X89-1</f>
         <v>0.58297714943284573</v>
       </c>
+      <c r="AC90" s="10">
+        <f>+AC89/Y89-1</f>
+        <v>0.41043776183449521</v>
+      </c>
+      <c r="AD90" s="10">
+        <f>+AD89/Z89-1</f>
+        <v>0.60279615528648112</v>
+      </c>
     </row>
     <row r="93" spans="2:78" x14ac:dyDescent="0.25">
       <c r="B93" t="s">
@@ -13911,92 +14284,100 @@
       </c>
       <c r="F93" s="5"/>
       <c r="G93" s="5">
-        <f t="shared" ref="G93:N93" si="237">(G46/G24)*90</f>
+        <f t="shared" ref="G93:N93" si="238">(G46/G24)*90</f>
         <v>55.72402597402597</v>
       </c>
       <c r="H93" s="5">
-        <f t="shared" si="237"/>
+        <f t="shared" si="238"/>
         <v>48.51526125193999</v>
       </c>
       <c r="I93" s="5">
-        <f t="shared" si="237"/>
+        <f t="shared" si="238"/>
         <v>48.484976724502751</v>
       </c>
       <c r="J93" s="5">
-        <f t="shared" si="237"/>
+        <f t="shared" si="238"/>
         <v>43.695782530481715</v>
       </c>
       <c r="K93" s="5">
-        <f t="shared" si="237"/>
+        <f t="shared" si="238"/>
         <v>48.076311605723369</v>
       </c>
       <c r="L93" s="5">
-        <f t="shared" si="237"/>
+        <f t="shared" si="238"/>
         <v>49.598893499308438</v>
       </c>
       <c r="M93" s="5">
-        <f t="shared" si="237"/>
+        <f t="shared" si="238"/>
         <v>50.099957764324934</v>
       </c>
       <c r="N93" s="5">
-        <f t="shared" si="237"/>
+        <f t="shared" si="238"/>
         <v>54.755985869423007</v>
       </c>
       <c r="O93" s="5">
-        <f t="shared" ref="O93:AB93" si="238">(O46/O24)*90</f>
+        <f t="shared" ref="O93:AD93" si="239">(O46/O24)*90</f>
         <v>59.051640926640928</v>
       </c>
       <c r="P93" s="5">
-        <f t="shared" si="238"/>
+        <f t="shared" si="239"/>
         <v>71.379773269689736</v>
       </c>
       <c r="Q93" s="5">
-        <f t="shared" si="238"/>
+        <f t="shared" si="239"/>
         <v>74.476479514415786</v>
       </c>
       <c r="R93" s="5">
-        <f t="shared" si="238"/>
+        <f t="shared" si="239"/>
         <v>56.921170054536439</v>
       </c>
       <c r="S93" s="5">
-        <f t="shared" si="238"/>
+        <f t="shared" si="239"/>
         <v>51.056729699666299</v>
       </c>
       <c r="T93" s="5">
-        <f t="shared" si="238"/>
+        <f t="shared" si="239"/>
         <v>47.082253646257499</v>
       </c>
       <c r="U93" s="5">
-        <f t="shared" si="238"/>
+        <f t="shared" si="239"/>
         <v>41.269867549668874</v>
       </c>
       <c r="V93" s="5">
-        <f t="shared" si="238"/>
+        <f t="shared" si="239"/>
         <v>40.714382662986928</v>
       </c>
       <c r="W93" s="5">
-        <f t="shared" si="238"/>
+        <f t="shared" si="239"/>
         <v>42.729611426816156</v>
       </c>
       <c r="X93" s="5">
-        <f t="shared" si="238"/>
+        <f t="shared" si="239"/>
         <v>42.339547270306255</v>
       </c>
       <c r="Y93" s="5">
-        <f t="shared" si="238"/>
+        <f t="shared" si="239"/>
         <v>45.389943560800411</v>
       </c>
       <c r="Z93" s="5">
-        <f t="shared" si="238"/>
+        <f t="shared" si="239"/>
         <v>52.778978413973704</v>
       </c>
       <c r="AA93" s="5">
-        <f t="shared" si="238"/>
+        <f t="shared" si="239"/>
         <v>45.206300213335751</v>
       </c>
       <c r="AB93" s="5">
-        <f t="shared" si="238"/>
+        <f t="shared" si="239"/>
         <v>53.542134651177712</v>
+      </c>
+      <c r="AC93" s="5">
+        <f t="shared" si="239"/>
+        <v>52.71708241237765</v>
+      </c>
+      <c r="AD93" s="5">
+        <f t="shared" si="239"/>
+        <v>50.836123348017622</v>
       </c>
       <c r="AJ93" s="5"/>
       <c r="AK93" s="5"/>
@@ -14334,7 +14715,7 @@
       <c r="BD101" s="5"/>
       <c r="BE101" s="5"/>
       <c r="BP101" s="2">
-        <f t="shared" ref="BP101:BP119" si="239">SUM(W101:Z101)</f>
+        <f t="shared" ref="BP101:BP119" si="240">SUM(W101:Z101)</f>
         <v>100</v>
       </c>
     </row>
@@ -14412,7 +14793,7 @@
       <c r="BD102" s="5"/>
       <c r="BE102" s="5"/>
       <c r="BP102" s="2">
-        <f t="shared" si="239"/>
+        <f t="shared" si="240"/>
         <v>200</v>
       </c>
     </row>
@@ -14490,7 +14871,7 @@
       <c r="BD103" s="5"/>
       <c r="BE103" s="5"/>
       <c r="BP103" s="2">
-        <f t="shared" si="239"/>
+        <f t="shared" si="240"/>
         <v>200</v>
       </c>
     </row>
@@ -14568,7 +14949,7 @@
       <c r="BD104" s="5"/>
       <c r="BE104" s="5"/>
       <c r="BP104" s="2">
-        <f t="shared" si="239"/>
+        <f t="shared" si="240"/>
         <v>100</v>
       </c>
     </row>
@@ -14646,7 +15027,7 @@
       <c r="BD105" s="5"/>
       <c r="BE105" s="5"/>
       <c r="BP105" s="2">
-        <f t="shared" si="239"/>
+        <f t="shared" si="240"/>
         <v>400</v>
       </c>
     </row>
@@ -14724,7 +15105,7 @@
       <c r="BD106" s="5"/>
       <c r="BE106" s="5"/>
       <c r="BP106" s="2">
-        <f t="shared" si="239"/>
+        <f t="shared" si="240"/>
         <v>0</v>
       </c>
     </row>
@@ -14802,7 +15183,7 @@
       <c r="BD107" s="5"/>
       <c r="BE107" s="5"/>
       <c r="BP107" s="2">
-        <f t="shared" si="239"/>
+        <f t="shared" si="240"/>
         <v>400</v>
       </c>
     </row>
@@ -14880,7 +15261,7 @@
       <c r="BD108" s="5"/>
       <c r="BE108" s="5"/>
       <c r="BP108" s="2">
-        <f t="shared" si="239"/>
+        <f t="shared" si="240"/>
         <v>100</v>
       </c>
     </row>
@@ -14958,7 +15339,7 @@
       <c r="BD109" s="5"/>
       <c r="BE109" s="5"/>
       <c r="BP109" s="2">
-        <f t="shared" si="239"/>
+        <f t="shared" si="240"/>
         <v>100</v>
       </c>
     </row>
@@ -15036,7 +15417,7 @@
       <c r="BD110" s="5"/>
       <c r="BE110" s="5"/>
       <c r="BP110" s="2">
-        <f t="shared" si="239"/>
+        <f t="shared" si="240"/>
         <v>210</v>
       </c>
     </row>
@@ -15114,7 +15495,7 @@
       <c r="BD111" s="5"/>
       <c r="BE111" s="5"/>
       <c r="BP111" s="2">
-        <f t="shared" si="239"/>
+        <f t="shared" si="240"/>
         <v>90</v>
       </c>
     </row>
@@ -15192,7 +15573,7 @@
       <c r="BD112" s="5"/>
       <c r="BE112" s="5"/>
       <c r="BP112" s="2">
-        <f t="shared" si="239"/>
+        <f t="shared" si="240"/>
         <v>0</v>
       </c>
     </row>
@@ -15270,7 +15651,7 @@
       <c r="BD113" s="5"/>
       <c r="BE113" s="5"/>
       <c r="BP113" s="2">
-        <f t="shared" si="239"/>
+        <f t="shared" si="240"/>
         <v>95</v>
       </c>
     </row>
@@ -15348,7 +15729,7 @@
       <c r="BD114" s="5"/>
       <c r="BE114" s="5"/>
       <c r="BP114" s="2">
-        <f t="shared" si="239"/>
+        <f t="shared" si="240"/>
         <v>85</v>
       </c>
     </row>
@@ -15426,7 +15807,7 @@
       <c r="BD115" s="5"/>
       <c r="BE115" s="5"/>
       <c r="BP115" s="2">
-        <f t="shared" si="239"/>
+        <f t="shared" si="240"/>
         <v>0</v>
       </c>
     </row>
@@ -15504,7 +15885,7 @@
       <c r="BD116" s="5"/>
       <c r="BE116" s="5"/>
       <c r="BP116" s="2">
-        <f t="shared" si="239"/>
+        <f t="shared" si="240"/>
         <v>190</v>
       </c>
     </row>
@@ -15582,7 +15963,7 @@
       <c r="BD117" s="5"/>
       <c r="BE117" s="5"/>
       <c r="BP117" s="2">
-        <f t="shared" si="239"/>
+        <f t="shared" si="240"/>
         <v>160</v>
       </c>
     </row>
@@ -15660,7 +16041,7 @@
       <c r="BD118" s="5"/>
       <c r="BE118" s="5"/>
       <c r="BP118" s="2">
-        <f t="shared" si="239"/>
+        <f t="shared" si="240"/>
         <v>35</v>
       </c>
     </row>
@@ -15738,7 +16119,7 @@
       <c r="BD119" s="5"/>
       <c r="BE119" s="5"/>
       <c r="BP119" s="2">
-        <f t="shared" si="239"/>
+        <f t="shared" si="240"/>
         <v>35</v>
       </c>
     </row>
@@ -15772,23 +16153,23 @@
         <v>360</v>
       </c>
       <c r="V120" s="9">
-        <f t="shared" ref="V120:Z120" si="240">SUM(V100:V119)</f>
+        <f t="shared" ref="V120:Z120" si="241">SUM(V100:V119)</f>
         <v>460</v>
       </c>
       <c r="W120" s="9">
-        <f t="shared" si="240"/>
+        <f t="shared" si="241"/>
         <v>570</v>
       </c>
       <c r="X120" s="9">
-        <f t="shared" si="240"/>
+        <f t="shared" si="241"/>
         <v>690</v>
       </c>
       <c r="Y120" s="9">
-        <f t="shared" si="240"/>
+        <f t="shared" si="241"/>
         <v>735</v>
       </c>
       <c r="Z120" s="9">
-        <f t="shared" si="240"/>
+        <f t="shared" si="241"/>
         <v>735</v>
       </c>
       <c r="AA120" s="9"/>
@@ -16100,31 +16481,31 @@
         <v>250</v>
       </c>
       <c r="U127" s="2">
-        <f t="shared" ref="U127:AA127" si="241">+U128-U129</f>
+        <f t="shared" ref="U127:AA127" si="242">+U128-U129</f>
         <v>880.00714285714275</v>
       </c>
       <c r="V127" s="2">
-        <f t="shared" si="241"/>
+        <f t="shared" si="242"/>
         <v>-647.79285714285652</v>
       </c>
       <c r="W127" s="2">
-        <f t="shared" si="241"/>
+        <f t="shared" si="242"/>
         <v>-2786.8428571428558</v>
       </c>
       <c r="X127" s="2">
-        <f t="shared" si="241"/>
+        <f t="shared" si="242"/>
         <v>-2171.2428571428572</v>
       </c>
       <c r="Y127" s="2">
-        <f t="shared" si="241"/>
+        <f t="shared" si="242"/>
         <v>-1903.9499999999971</v>
       </c>
       <c r="Z127" s="2">
-        <f t="shared" si="241"/>
+        <f t="shared" si="242"/>
         <v>-361.90000000000146</v>
       </c>
       <c r="AA127" s="2">
-        <f t="shared" si="241"/>
+        <f t="shared" si="242"/>
         <v>-1136.9499999999971</v>
       </c>
     </row>
@@ -16133,27 +16514,27 @@
         <v>249</v>
       </c>
       <c r="U128" s="2">
-        <f t="shared" ref="U128:Z128" si="242">+U131*0.45</f>
+        <f t="shared" ref="U128:Z128" si="243">+U131*0.45</f>
         <v>19000.007142857143</v>
       </c>
       <c r="V128" s="2">
-        <f t="shared" si="242"/>
+        <f t="shared" si="243"/>
         <v>21455.207142857143</v>
       </c>
       <c r="W128" s="2">
-        <f t="shared" si="242"/>
+        <f t="shared" si="243"/>
         <v>23257.157142857144</v>
       </c>
       <c r="X128" s="2">
-        <f t="shared" si="242"/>
+        <f t="shared" si="243"/>
         <v>27868.757142857143</v>
       </c>
       <c r="Y128" s="2">
-        <f t="shared" si="242"/>
+        <f t="shared" si="243"/>
         <v>33178.050000000003</v>
       </c>
       <c r="Z128" s="2">
-        <f t="shared" si="242"/>
+        <f t="shared" si="243"/>
         <v>38969.1</v>
       </c>
       <c r="AA128" s="2">
@@ -16161,48 +16542,48 @@
         <v>42925.05</v>
       </c>
     </row>
-    <row r="129" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="129" spans="2:69" x14ac:dyDescent="0.25">
       <c r="B129" t="s">
         <v>1</v>
       </c>
       <c r="S129" s="2">
-        <f t="shared" ref="S129:AB129" si="243">S24</f>
+        <f t="shared" ref="S129:AB129" si="244">S24</f>
         <v>7192</v>
       </c>
       <c r="T129" s="2">
-        <f t="shared" si="243"/>
+        <f t="shared" si="244"/>
         <v>13507</v>
       </c>
       <c r="U129" s="2">
-        <f t="shared" si="243"/>
+        <f t="shared" si="244"/>
         <v>18120</v>
       </c>
       <c r="V129" s="2">
-        <f t="shared" si="243"/>
+        <f t="shared" si="244"/>
         <v>22103</v>
       </c>
       <c r="W129" s="2">
-        <f t="shared" si="243"/>
+        <f t="shared" si="244"/>
         <v>26044</v>
       </c>
       <c r="X129" s="2">
-        <f t="shared" si="243"/>
+        <f t="shared" si="244"/>
         <v>30040</v>
       </c>
       <c r="Y129" s="2">
-        <f t="shared" si="243"/>
+        <f t="shared" si="244"/>
         <v>35082</v>
       </c>
       <c r="Z129" s="2">
-        <f t="shared" si="243"/>
+        <f t="shared" si="244"/>
         <v>39331</v>
       </c>
       <c r="AA129" s="2">
-        <f t="shared" si="243"/>
+        <f t="shared" si="244"/>
         <v>44062</v>
       </c>
       <c r="AB129" s="2">
-        <f t="shared" si="243"/>
+        <f t="shared" si="244"/>
         <v>46743</v>
       </c>
       <c r="AC129" s="2">
@@ -16218,48 +16599,48 @@
       <c r="AG129" s="2"/>
       <c r="AH129" s="2"/>
     </row>
-    <row r="130" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="130" spans="2:69" x14ac:dyDescent="0.25">
       <c r="B130" t="s">
         <v>22</v>
       </c>
       <c r="S130" s="5">
-        <f t="shared" ref="S130:AB130" si="244">S22</f>
+        <f t="shared" ref="S130:AB130" si="245">S22</f>
         <v>4284</v>
       </c>
       <c r="T130" s="5">
-        <f t="shared" si="244"/>
+        <f t="shared" si="245"/>
         <v>10323</v>
       </c>
       <c r="U130" s="5">
-        <f t="shared" si="244"/>
+        <f t="shared" si="245"/>
         <v>14514</v>
       </c>
       <c r="V130" s="5">
-        <f t="shared" si="244"/>
+        <f t="shared" si="245"/>
         <v>18404</v>
       </c>
       <c r="W130" s="5">
-        <f t="shared" si="244"/>
+        <f t="shared" si="245"/>
         <v>22563</v>
       </c>
       <c r="X130" s="5">
-        <f t="shared" si="244"/>
+        <f t="shared" si="245"/>
         <v>26272</v>
       </c>
       <c r="Y130" s="5">
-        <f t="shared" si="244"/>
+        <f t="shared" si="245"/>
         <v>30771</v>
       </c>
       <c r="Z130" s="5">
-        <f t="shared" si="244"/>
+        <f t="shared" si="245"/>
         <v>35580</v>
       </c>
       <c r="AA130" s="5">
-        <f t="shared" si="244"/>
+        <f t="shared" si="245"/>
         <v>39112</v>
       </c>
       <c r="AB130" s="5">
-        <f t="shared" si="244"/>
+        <f t="shared" si="245"/>
         <v>41096</v>
       </c>
       <c r="AC130" s="5">
@@ -16275,7 +16656,7 @@
       <c r="AG130" s="5"/>
       <c r="AH130" s="5"/>
     </row>
-    <row r="131" spans="2:34" s="11" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+    <row r="131" spans="2:69" s="11" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="B131" s="11" t="s">
         <v>199</v>
       </c>
@@ -16300,43 +16681,43 @@
         <v>36225.571428571428</v>
       </c>
       <c r="T131" s="8">
-        <f t="shared" ref="T131:AE131" si="245">SUM(T132:T140)</f>
+        <f t="shared" ref="T131:AE131" si="246">SUM(T132:T140)</f>
         <v>40929.238095238092</v>
       </c>
       <c r="U131" s="8">
-        <f t="shared" si="245"/>
+        <f t="shared" si="246"/>
         <v>42222.238095238092</v>
       </c>
       <c r="V131" s="8">
-        <f t="shared" si="245"/>
+        <f t="shared" si="246"/>
         <v>47678.238095238092</v>
       </c>
       <c r="W131" s="8">
-        <f t="shared" si="245"/>
+        <f t="shared" si="246"/>
         <v>51682.571428571428</v>
       </c>
       <c r="X131" s="8">
-        <f t="shared" si="245"/>
+        <f t="shared" si="246"/>
         <v>61930.571428571428</v>
       </c>
       <c r="Y131" s="8">
-        <f t="shared" si="245"/>
+        <f t="shared" si="246"/>
         <v>73729</v>
       </c>
       <c r="Z131" s="8">
-        <f t="shared" si="245"/>
+        <f t="shared" si="246"/>
         <v>86598</v>
       </c>
       <c r="AA131" s="8">
-        <f t="shared" si="245"/>
+        <f t="shared" si="246"/>
         <v>95389</v>
       </c>
       <c r="AB131" s="8">
-        <f t="shared" si="245"/>
+        <f t="shared" si="246"/>
         <v>115701</v>
       </c>
       <c r="AC131" s="8">
-        <f t="shared" si="245"/>
+        <f t="shared" si="246"/>
         <v>128162</v>
       </c>
       <c r="AD131" s="8">
@@ -16344,14 +16725,14 @@
         <v>157443.78599999999</v>
       </c>
       <c r="AE131" s="8">
-        <f t="shared" si="245"/>
+        <f t="shared" si="246"/>
         <v>0</v>
       </c>
       <c r="AF131" s="8"/>
       <c r="AG131" s="8"/>
       <c r="AH131" s="8"/>
     </row>
-    <row r="132" spans="2:34" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="2:69" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B132" s="2" t="s">
         <v>195</v>
       </c>
@@ -16390,31 +16771,31 @@
         <v>1500</v>
       </c>
       <c r="Y132" s="2">
-        <f t="shared" ref="Y132:AD132" si="246">+X132+500</f>
+        <f t="shared" ref="Y132:AD132" si="247">+X132+500</f>
         <v>2000</v>
       </c>
       <c r="Z132" s="2">
-        <f t="shared" si="246"/>
+        <f t="shared" si="247"/>
         <v>2500</v>
       </c>
       <c r="AA132" s="2">
-        <f t="shared" si="246"/>
+        <f t="shared" si="247"/>
         <v>3000</v>
       </c>
       <c r="AB132" s="2">
-        <f t="shared" si="246"/>
+        <f t="shared" si="247"/>
         <v>3500</v>
       </c>
       <c r="AC132" s="2">
-        <f t="shared" si="246"/>
+        <f t="shared" si="247"/>
         <v>4000</v>
       </c>
       <c r="AD132" s="2">
-        <f t="shared" si="246"/>
+        <f t="shared" si="247"/>
         <v>4500</v>
       </c>
     </row>
-    <row r="133" spans="2:34" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="2:69" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B133" s="2" t="s">
         <v>91</v>
       </c>
@@ -16471,7 +16852,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="134" spans="2:34" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="2:69" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B134" s="2" t="s">
         <v>196</v>
       </c>
@@ -16527,8 +16908,20 @@
       <c r="AD134" s="2">
         <v>29876</v>
       </c>
-    </row>
-    <row r="135" spans="2:34" x14ac:dyDescent="0.25">
+      <c r="BO134" s="2">
+        <f>SUM(S134:V134)</f>
+        <v>35202</v>
+      </c>
+      <c r="BP134" s="2">
+        <f>SUM(W134:Z134)</f>
+        <v>55552</v>
+      </c>
+      <c r="BQ134" s="2">
+        <f t="shared" ref="BQ134" si="248">SUM(AA134:AD134)</f>
+        <v>83094</v>
+      </c>
+    </row>
+    <row r="135" spans="2:69" x14ac:dyDescent="0.25">
       <c r="B135" t="s">
         <v>197</v>
       </c>
@@ -16576,8 +16969,20 @@
       <c r="AF135" s="2"/>
       <c r="AG135" s="2"/>
       <c r="AH135" s="2"/>
-    </row>
-    <row r="136" spans="2:34" x14ac:dyDescent="0.25">
+      <c r="BO135" s="2">
+        <f t="shared" ref="BO135:BO140" si="249">SUM(S135:V135)</f>
+        <v>32251</v>
+      </c>
+      <c r="BP135" s="2">
+        <f t="shared" ref="BP135:BP140" si="250">SUM(W135:Z135)</f>
+        <v>52535</v>
+      </c>
+      <c r="BQ135" s="2">
+        <f>SUM(AA135:AD135)</f>
+        <v>91447</v>
+      </c>
+    </row>
+    <row r="136" spans="2:69" x14ac:dyDescent="0.25">
       <c r="B136" t="s">
         <v>198</v>
       </c>
@@ -16621,8 +17026,20 @@
       <c r="AF136" s="2"/>
       <c r="AG136" s="2"/>
       <c r="AH136" s="2"/>
-    </row>
-    <row r="137" spans="2:34" x14ac:dyDescent="0.25">
+      <c r="BO136" s="2">
+        <f t="shared" si="249"/>
+        <v>52729</v>
+      </c>
+      <c r="BP136" s="2">
+        <f t="shared" si="250"/>
+        <v>82999</v>
+      </c>
+      <c r="BQ136" s="2">
+        <f t="shared" ref="BQ136:BQ140" si="251">SUM(AA136:AD136)</f>
+        <v>131819</v>
+      </c>
+    </row>
+    <row r="137" spans="2:69" x14ac:dyDescent="0.25">
       <c r="B137" t="s">
         <v>78</v>
       </c>
@@ -16673,8 +17090,20 @@
       <c r="AF137" s="2"/>
       <c r="AG137" s="2"/>
       <c r="AH137" s="2"/>
-    </row>
-    <row r="138" spans="2:34" x14ac:dyDescent="0.25">
+      <c r="BO137" s="2">
+        <f t="shared" si="249"/>
+        <v>5714.2857142857147</v>
+      </c>
+      <c r="BP137" s="2">
+        <f t="shared" si="250"/>
+        <v>9057.1428571428569</v>
+      </c>
+      <c r="BQ137" s="2">
+        <f t="shared" si="251"/>
+        <v>43000</v>
+      </c>
+    </row>
+    <row r="138" spans="2:69" x14ac:dyDescent="0.25">
       <c r="B138" t="s">
         <v>200</v>
       </c>
@@ -16724,8 +17153,20 @@
       <c r="AF138" s="2"/>
       <c r="AG138" s="2"/>
       <c r="AH138" s="2"/>
-    </row>
-    <row r="139" spans="2:34" x14ac:dyDescent="0.25">
+      <c r="BO138" s="2">
+        <f t="shared" si="249"/>
+        <v>2720.9999999999995</v>
+      </c>
+      <c r="BP138" s="2">
+        <f t="shared" si="250"/>
+        <v>8483</v>
+      </c>
+      <c r="BQ138" s="2">
+        <f t="shared" si="251"/>
+        <v>9527.7860000000001</v>
+      </c>
+    </row>
+    <row r="139" spans="2:69" x14ac:dyDescent="0.25">
       <c r="B139" t="s">
         <v>201</v>
       </c>
@@ -16769,8 +17210,20 @@
       <c r="AF139" s="2"/>
       <c r="AG139" s="2"/>
       <c r="AH139" s="2"/>
-    </row>
-    <row r="140" spans="2:34" x14ac:dyDescent="0.25">
+      <c r="BO139" s="2">
+        <f t="shared" si="249"/>
+        <v>27045</v>
+      </c>
+      <c r="BP139" s="2">
+        <f t="shared" si="250"/>
+        <v>37256</v>
+      </c>
+      <c r="BQ139" s="2">
+        <f t="shared" si="251"/>
+        <v>69691</v>
+      </c>
+    </row>
+    <row r="140" spans="2:69" x14ac:dyDescent="0.25">
       <c r="B140" t="s">
         <v>202</v>
       </c>
@@ -16812,34 +17265,46 @@
       <c r="AF140" s="2"/>
       <c r="AG140" s="2"/>
       <c r="AH140" s="2"/>
-    </row>
-    <row r="142" spans="2:34" x14ac:dyDescent="0.25">
+      <c r="BO140" s="2">
+        <f t="shared" si="249"/>
+        <v>4068</v>
+      </c>
+      <c r="BP140" s="2">
+        <f t="shared" si="250"/>
+        <v>14933</v>
+      </c>
+      <c r="BQ140" s="2">
+        <f t="shared" si="251"/>
+        <v>38117</v>
+      </c>
+    </row>
+    <row r="142" spans="2:69" x14ac:dyDescent="0.25">
       <c r="B142" t="s">
         <v>271</v>
       </c>
       <c r="V142" s="10"/>
       <c r="W142" s="10">
-        <f t="shared" ref="W142" si="247">+W131/S131-1</f>
+        <f t="shared" ref="W142" si="252">+W131/S131-1</f>
         <v>0.42668754116074292</v>
       </c>
       <c r="X142" s="10">
-        <f t="shared" ref="X142" si="248">+X131/T131-1</f>
+        <f t="shared" ref="X142" si="253">+X131/T131-1</f>
         <v>0.51311322445009622</v>
       </c>
       <c r="Y142" s="10">
-        <f t="shared" ref="Y142:AB142" si="249">+Y131/U131-1</f>
+        <f t="shared" ref="Y142:AB142" si="254">+Y131/U131-1</f>
         <v>0.74621250142387185</v>
       </c>
       <c r="Z142" s="10">
-        <f t="shared" si="249"/>
+        <f t="shared" si="254"/>
         <v>0.81630033867902219</v>
       </c>
       <c r="AA142" s="10">
-        <f t="shared" si="249"/>
+        <f t="shared" si="254"/>
         <v>0.84567054934241437</v>
       </c>
       <c r="AB142" s="10">
-        <f t="shared" si="249"/>
+        <f t="shared" si="254"/>
         <v>0.86823724262653568</v>
       </c>
       <c r="AC142" s="10">
@@ -16855,7 +17320,7 @@
       <c r="AG142" s="10"/>
       <c r="AH142" s="10"/>
     </row>
-    <row r="144" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="144" spans="2:69" x14ac:dyDescent="0.25">
       <c r="B144" t="s">
         <v>203</v>
       </c>
@@ -16864,7 +17329,7 @@
         <v>0.11825900409734245</v>
       </c>
       <c r="T144" s="7">
-        <f t="shared" ref="T144:Z144" si="250">+T130/T131</f>
+        <f t="shared" ref="T144:Z144" si="255">+T130/T131</f>
         <v>0.25221578706106013</v>
       </c>
       <c r="U144" s="7">
@@ -16872,23 +17337,23 @@
         <v>0.34375250234868338</v>
       </c>
       <c r="V144" s="7">
-        <f t="shared" si="250"/>
+        <f t="shared" si="255"/>
         <v>0.38600419678339826</v>
       </c>
       <c r="W144" s="7">
-        <f t="shared" si="250"/>
+        <f t="shared" si="255"/>
         <v>0.43656883503142813</v>
       </c>
       <c r="X144" s="7">
-        <f t="shared" si="250"/>
+        <f t="shared" si="255"/>
         <v>0.42421698030513433</v>
       </c>
       <c r="Y144" s="7">
-        <f t="shared" si="250"/>
+        <f t="shared" si="255"/>
         <v>0.41735273772870918</v>
       </c>
       <c r="Z144" s="7">
-        <f t="shared" si="250"/>
+        <f t="shared" si="255"/>
         <v>0.41086399224000553</v>
       </c>
       <c r="AA144" s="7">
@@ -16896,15 +17361,15 @@
         <v>0.41002631330656575</v>
       </c>
       <c r="AB144" s="7">
-        <f t="shared" ref="AB144:AD144" si="251">+AB130/AB131</f>
+        <f t="shared" ref="AB144:AD144" si="256">+AB130/AB131</f>
         <v>0.35519139851859532</v>
       </c>
       <c r="AC144" s="7">
-        <f t="shared" si="251"/>
+        <f t="shared" si="256"/>
         <v>0.35</v>
       </c>
       <c r="AD144" s="7">
-        <f t="shared" si="251"/>
+        <f t="shared" si="256"/>
         <v>0.35</v>
       </c>
       <c r="AE144" s="7"/>
@@ -16925,27 +17390,27 @@
         <v>0.33000858624757717</v>
       </c>
       <c r="U145" s="7">
-        <f t="shared" ref="U145:Z145" si="252">+U129/U131</f>
+        <f t="shared" ref="U145:Z145" si="257">+U129/U131</f>
         <v>0.42915773339934837</v>
       </c>
       <c r="V145" s="7">
-        <f t="shared" si="252"/>
+        <f t="shared" si="257"/>
         <v>0.46358676165526252</v>
       </c>
       <c r="W145" s="7">
-        <f t="shared" si="252"/>
+        <f t="shared" si="257"/>
         <v>0.50392229488802531</v>
       </c>
       <c r="X145" s="7">
-        <f t="shared" si="252"/>
+        <f t="shared" si="257"/>
         <v>0.48505930604317277</v>
       </c>
       <c r="Y145" s="7">
-        <f t="shared" si="252"/>
+        <f t="shared" si="257"/>
         <v>0.47582362435405334</v>
       </c>
       <c r="Z145" s="7">
-        <f t="shared" si="252"/>
+        <f t="shared" si="257"/>
         <v>0.45417908034827592</v>
       </c>
       <c r="AA145" s="7">
@@ -16957,7 +17422,7 @@
         <v>0.40399823683459951</v>
       </c>
       <c r="AC145" s="7">
-        <f t="shared" ref="AC145:AD145" si="253">+AC129/AC131</f>
+        <f t="shared" ref="AC145" si="258">+AC129/AC131</f>
         <v>0.43</v>
       </c>
       <c r="AD145" s="7">
@@ -17075,15 +17540,15 @@
         <v>4349</v>
       </c>
       <c r="BN148" s="2">
-        <f t="shared" ref="BN148:BN152" si="254">SUM(O148:R148)</f>
+        <f t="shared" ref="BN148:BN152" si="259">SUM(O148:R148)</f>
         <v>8292</v>
       </c>
       <c r="BO148" s="2">
-        <f t="shared" ref="BO148:BO152" si="255">SUM(S148:V148)</f>
+        <f t="shared" ref="BO148:BO152" si="260">SUM(S148:V148)</f>
         <v>26966</v>
       </c>
       <c r="BP148" s="2">
-        <f t="shared" ref="BP148:BP152" si="256">SUM(W148:Z148)</f>
+        <f t="shared" ref="BP148:BP152" si="261">SUM(W148:Z148)</f>
         <v>61257</v>
       </c>
     </row>
@@ -17187,15 +17652,15 @@
         <v>8544</v>
       </c>
       <c r="BN149" s="2">
-        <f t="shared" si="254"/>
+        <f t="shared" si="259"/>
         <v>6986</v>
       </c>
       <c r="BO149" s="2">
-        <f t="shared" si="255"/>
+        <f t="shared" si="260"/>
         <v>13405</v>
       </c>
       <c r="BP149" s="2">
-        <f t="shared" si="256"/>
+        <f t="shared" si="261"/>
         <v>20573</v>
       </c>
     </row>
@@ -17249,11 +17714,11 @@
         <v>9017</v>
       </c>
       <c r="BO150" s="2">
-        <f t="shared" si="255"/>
+        <f t="shared" si="260"/>
         <v>6831</v>
       </c>
       <c r="BP150" s="2">
-        <f t="shared" si="256"/>
+        <f t="shared" si="261"/>
         <v>23684</v>
       </c>
     </row>
@@ -17357,15 +17822,15 @@
         <v>7111</v>
       </c>
       <c r="BN151" s="2">
-        <f t="shared" si="254"/>
+        <f t="shared" si="259"/>
         <v>5785</v>
       </c>
       <c r="BO151" s="2">
-        <f t="shared" si="255"/>
+        <f t="shared" si="260"/>
         <v>10306</v>
       </c>
       <c r="BP151" s="2">
-        <f t="shared" si="256"/>
+        <f t="shared" si="261"/>
         <v>17108</v>
       </c>
     </row>
@@ -17479,15 +17944,15 @@
         <v>6910</v>
       </c>
       <c r="BN152" s="2">
-        <f t="shared" si="254"/>
+        <f t="shared" si="259"/>
         <v>5911</v>
       </c>
       <c r="BO152" s="2">
-        <f t="shared" si="255"/>
+        <f t="shared" si="260"/>
         <v>3414</v>
       </c>
       <c r="BP152" s="2">
-        <f t="shared" si="256"/>
+        <f t="shared" si="261"/>
         <v>7875</v>
       </c>
     </row>
